--- a/trust_urls.xlsx
+++ b/trust_urls.xlsx
@@ -2900,7 +2900,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.stgeorges.nhs.uk/about-us/board-papers/</t>
+          <t>https://www.stgeorges.nhs.uk/about/our-board/board-meetings/group-board-papers-and-agenda/</t>
         </is>
       </c>
     </row>
@@ -4996,7 +4996,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>https://www.gwh.nhs.uk/about-us/how-we-make-decisions/board-meetings-and-papers/</t>
+          <t>https://www.gwh.nhs.uk/about-us/trust-board/board-meetings/</t>
         </is>
       </c>
     </row>

--- a/trust_urls.xlsx
+++ b/trust_urls.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H208"/>
+  <dimension ref="A1:O208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -428,6 +428,13 @@
     <col width="54" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -471,6 +478,41 @@
           <t>url</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>access_notes</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>needs_playwright</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>pack_pattern_hints</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>exclude_patterns</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>last_validated</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>validation_status</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>validation_notes</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -513,6 +555,13 @@
           <t>https://www.royalsurrey.nhs.uk/board-papers/</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -555,6 +604,13 @@
           <t>https://www.sussexcommunity.nhs.uk/about-us/how-we-are-run/board-of-directors/board-meetings-and-papers</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -597,6 +653,13 @@
           <t>https://www.dgt.nhs.uk/about-us/trust-management/trust-boardmanagement/trust-board-minutesagendas</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -639,6 +702,13 @@
           <t>https://www.medway.nhs.uk/about-us/board-meetings/</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -681,6 +751,13 @@
           <t>https://www.qvh.nhs.uk/about-us/board-of-directors/meetings-in-public/</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -723,6 +800,13 @@
           <t>https://www.ashfordstpeters.nhs.uk/meetings</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -765,6 +849,13 @@
           <t>https://www.surreyandsussex.nhs.uk/about-us/our-board/board-papers</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -807,6 +898,13 @@
           <t>https://www.ekhuft.nhs.uk/about-us/board-of-directors/</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -849,6 +947,39 @@
           <t>https://www.mtw.nhs.uk/about-us/trust-board/board-meetings-and-papers/</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Strategy: /about-us/trust-board/board-meetings-and-papers/ is the correct page (Google indexes it as 'Board meetings and papers'), but the site's WAF returns 404 to non-browser fetchers. Pattern E anti-bot — fetch with a real browser / Playwright; do not treat the 404 as a dead URL.</t>
+        </is>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Boardbook;Board papers</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>needs_playwright</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>WAF returns 404 to bots; Google confirms URL is the live 'Board meetings and papers' page.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -891,6 +1022,13 @@
           <t>https://www.sussexpartnership.nhs.uk/about-us/how-our-trust-run/board-meetings</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -933,6 +1071,39 @@
           <t>https://www.esht.nhs.uk/about-us/trust-board/meetings-in-public/</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Strategy: /about-us/trust-board/meetings-in-public/ is correct (with an /archive/ sub-page of dated agenda-papers PDFs, one per meeting). Site intermittently drops bot connections (ConnectionReset), so a health-check may show it down even though it is live for browsers. Pattern A behind Pattern E anti-bot; retry / use a browser UA.</t>
+        </is>
+      </c>
+      <c r="J12" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Trust Board meeting in public;agenda papers</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>URL confirmed correct (Google index); health-check ConnectionReset is transient anti-bot, not a dead URL.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -975,6 +1146,39 @@
           <t>https://www.sabp.nhs.uk/aboutus/board-of-directors/board-meetings-papers</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Strategy: dated board-pack PDFs listed directly on the landing page (63 found this run), one per meeting. Static fetch works. Prefer 'Public Board Pack' / 'Board Papers' / 'Agenda and Papers'; filter observer notes, Q&amp;A and addendums. Pattern A.</t>
+        </is>
+      </c>
+      <c r="J13" t="b">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Public Board Pack;Board Papers;Agenda and Papers</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Validator (static) found dated_pdfs=63, year_archives=0, meeting_subpages=4.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1013,6 +1217,13 @@
           <t>https://www.kmpt.nhs.uk/about-us/trust-board/</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1055,6 +1266,13 @@
           <t>https://www.uhsussex.nhs.uk/resources/public-board-papers-10-november-2022/</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1097,6 +1315,13 @@
           <t>https://www.kentcht.nhs.uk/about-us/who-we-are/the-board/</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1139,6 +1364,13 @@
           <t>https://www.chesterfieldroyal.nhs.uk/about-us/our-board-directors/board-directors-papers-meetings-and-minutes</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1181,6 +1413,13 @@
           <t>https://www.nottinghamshirehealthcare.nhs.uk/board-of-directors-and-meetings</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1223,6 +1462,39 @@
           <t>https://www.sfh-tr.nhs.uk/about-us/board-of-directors/</t>
         </is>
       </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Strategy: landing shows a weak board-papers signal to a static parser (few dated PDFs found). Papers are likely present but loaded via JS or one click into a 'papers'/'meetings' sub-page. Confirm by following the board-papers / meetings link; prefer the main combined pack. Pattern A/C — review on next pass.</t>
+        </is>
+      </c>
+      <c r="J19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Board Papers;Agenda and Papers;Public Board Pack</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>papers_partial</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Validator (static) weak signal: dated_pdfs=0, year_archives=0, meeting_subpages=1; review.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1265,6 +1537,13 @@
           <t>https://www.kgh.nhs.uk/board-of-directors-and-board-meetings</t>
         </is>
       </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1307,6 +1586,13 @@
           <t>https://www.northamptongeneral.nhs.uk/About/Our-Trust-Board/Meeting-and-papers/Meeting-papers.aspx</t>
         </is>
       </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1349,6 +1635,13 @@
           <t>https://www.nhft.nhs.uk/board/</t>
         </is>
       </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1391,6 +1684,13 @@
           <t>https://www.lpft.nhs.uk/get-involved/meeting-dates-and-minutes/board-directors-meetings</t>
         </is>
       </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1433,6 +1733,13 @@
           <t>https://www.leicspart.nhs.uk/about-us/trust-board/</t>
         </is>
       </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1475,6 +1782,13 @@
           <t>https://www.uhdb.nhs.uk/trust-board-members/</t>
         </is>
       </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1517,6 +1831,13 @@
           <t>https://www.ulh.nhs.uk/about/board-meetings/</t>
         </is>
       </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1559,6 +1880,13 @@
           <t>https://www.uhleicester.nhs.uk/about/board/board-papers-and-meetings/</t>
         </is>
       </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1601,6 +1929,13 @@
           <t>https://www.nuh.nhs.uk/board-and-board-papers/</t>
         </is>
       </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1643,6 +1978,13 @@
           <t>https://www.derbyshirehealthcareft.nhs.uk/about-us/our-board-directors/board-meetings</t>
         </is>
       </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1685,6 +2027,39 @@
           <t>https://lincolnshirecommunityhealthservices.nhs.uk/about-us/our-trust-board/trust-board-papers</t>
         </is>
       </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Strategy: dated board-pack PDFs listed directly on the landing page (57 found this run), one per meeting. Static fetch works. Prefer 'Public Board Pack' / 'Board Papers' / 'Agenda and Papers'; filter observer notes, Q&amp;A and addendums. Pattern A.</t>
+        </is>
+      </c>
+      <c r="J30" t="b">
+        <v>0</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Public Board Pack;Board Papers;Agenda and Papers</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Validator (static) found dated_pdfs=57, year_archives=0, meeting_subpages=0.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1727,6 +2102,13 @@
           <t>https://dchs.nhs.uk/about-us/our-board</t>
         </is>
       </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1769,6 +2151,13 @@
           <t>https://www.hacw.nhs.uk/board-papers/</t>
         </is>
       </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1811,6 +2200,39 @@
           <t>https://www.shropscommunityhealth.nhs.uk/board-meetings-and-papers</t>
         </is>
       </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Strategy: JS-rendered listing — static fetch returns a near-empty body, but Playwright (wait_until=networkidle) reaches dated PDFs such as 'Public Agenda', 'Public Information Pack' and 'Board Meetings in Common' for the current month. Pattern D.</t>
+        </is>
+      </c>
+      <c r="J33" t="b">
+        <v>1</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Public Information Pack;Public Agenda;Board Meetings in Common</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>needs_playwright</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Static body near-empty; Playwright reaches dated PDFs incl 'Public Information Pack 14.05.2026'.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1853,6 +2275,13 @@
           <t>https://www.walsallhealthcare.nhs.uk/about-us/how-we-are-run/board-papers/</t>
         </is>
       </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1895,6 +2324,39 @@
           <t>https://www.swft.nhs.uk/meetings-and-events/board-meetings</t>
         </is>
       </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Strategy: /meetings-and-events/board-meetings is an events calendar (next meeting shown, incl Joint Board with George Eliot). Actual papers are one click away at /about-us/publications/Board-of-Directors-papers-minutes. Pattern C; follow the publications link for dated packs and minutes.</t>
+        </is>
+      </c>
+      <c r="J35" t="b">
+        <v>0</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Board of Directors papers;Agenda and Papers</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>papers_partial</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Landing is a meetings calendar; papers at /about-us/publications/Board-of-Directors-papers-minutes (one click away).</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1937,6 +2399,13 @@
           <t>https://www.uhnm.nhs.uk/about-us/our-board/</t>
         </is>
       </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1979,6 +2448,13 @@
           <t>https://www.uhcw.nhs.uk/our-organisation/trust-board-meetings/</t>
         </is>
       </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2021,6 +2497,13 @@
           <t>https://www.rjah.nhs.uk/about-us/board-of-directors/board-of-directors-meeting-dates</t>
         </is>
       </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2063,6 +2546,13 @@
           <t>https://www.royalwolverhampton.nhs.uk/about-us/our-board/</t>
         </is>
       </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2105,6 +2595,13 @@
           <t>https://www.wyevalley.nhs.uk/about-us/the-trust-board.aspx</t>
         </is>
       </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2147,6 +2644,39 @@
           <t>https://www.geh.nhs.uk/about-us/trust-board/public-board-papers</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Strategy: landing lists per-meeting entries (31 dated meeting links this run); each links to its own sub-page of PDFs (agenda, papers, finance). Filter to the main Board (skip ICP/committee/joint). Prefer the largest 'Agenda and Papers' combined PDF. Static fetch works. Pattern C.</t>
+        </is>
+      </c>
+      <c r="J41" t="b">
+        <v>0</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Agenda and Papers;Combined Pack;Public Board Pack</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Validator (static) found dated_pdfs=26, year_archives=0, meeting_subpages=31.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2189,6 +2719,39 @@
           <t>https://www.combined.nhs.uk/about/our-board/board-meetings/</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Strategy: /about/our-board/board-meetings/ is correct (papers posted before each meeting; previous meetings at /about-us/our-board/previous-board-meetings/; archive from Jan 2014). Site intermittently drops bot connections (ConnectionReset). Pattern C behind Pattern E anti-bot; retry / use a browser.</t>
+        </is>
+      </c>
+      <c r="J42" t="b">
+        <v>0</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Trust Board;board papers</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>URL confirmed correct (Google index); health-check ConnectionReset is transient anti-bot.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2231,6 +2794,13 @@
           <t>https://www.dgft.nhs.uk/about-us/our-board/</t>
         </is>
       </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2273,6 +2843,39 @@
           <t>https://www.bwc.nhs.uk/board-of-directors/</t>
         </is>
       </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Strategy: /board-of-directors/ is an overview hub; the dated agendas and papers are on the related 'Board meetings and minutes' page (linked from this page). Pattern C; follow that link for the per-meeting packs. Trust office: bwc.foundationtrustoffice@nhs.net.</t>
+        </is>
+      </c>
+      <c r="J44" t="b">
+        <v>0</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Board meetings and minutes;agenda and papers</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>papers_partial</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Landing is a board overview; papers on the linked 'Board meetings and minutes' page (one click away).</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2315,6 +2918,13 @@
           <t>https://www.mpft.nhs.uk/about-us/board-papers/</t>
         </is>
       </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2357,6 +2967,13 @@
           <t>https://roh.nhs.uk/about-us/corporate-information/statutory-documents</t>
         </is>
       </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2396,7 +3013,40 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.uhb.nhs.uk/about-us/board-papers/</t>
+          <t>https://www.uhb.nhs.uk/about/trust-management/bod/papers/</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Strategy: correct page is /about/trust-management/bod/papers/ ('Papers from meetings of the Board of Directors'); the board packs load from an embedded online document store, so static fetch returns a near-empty body. Use Playwright (wait_until=networkidle) to reach the listing. Pattern D + F: old /about-us/board-papers/ 404'd; corrected 2026-05-29.</t>
+        </is>
+      </c>
+      <c r="J47" t="b">
+        <v>1</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Board of Directors;papers</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>needs_playwright</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Old URL 404'd; correct papers page renders via embedded JS document store (Playwright needed).</t>
         </is>
       </c>
     </row>
@@ -2441,6 +3091,39 @@
           <t>https://www.worcsacute.nhs.uk/about-us/trust-board/</t>
         </is>
       </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Strategy: landing lists year archives (5 year links this run, e.g. 'Board papers 2025'). Follow each year link to dated PDF listings; main packs typically 5-30MB. Static fetch works. Pattern B.</t>
+        </is>
+      </c>
+      <c r="J48" t="b">
+        <v>0</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Board Papers;Public Board Pack</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Validator (static) found dated_pdfs=0, year_archives=5, meeting_subpages=1.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2483,6 +3166,13 @@
           <t>https://www.swbh.nhs.uk/about-us/trust-board/</t>
         </is>
       </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2525,6 +3215,13 @@
           <t>https://www.bsmhft.nhs.uk/about-us/corporate-documents/trust-board-papers/</t>
         </is>
       </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2567,6 +3264,39 @@
           <t>https://www.sath.nhs.uk/about-us/board-papers/</t>
         </is>
       </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Strategy: dated board-pack PDFs listed directly on the landing page (348 found this run), one per meeting. Static fetch works. Prefer 'Public Board Pack' / 'Board Papers' / 'Agenda and Papers'; filter observer notes, Q&amp;A and addendums. Pattern A.</t>
+        </is>
+      </c>
+      <c r="J51" t="b">
+        <v>0</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Public Board Pack;Board Papers;Agenda and Papers</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Validator (static) found dated_pdfs=348, year_archives=2, meeting_subpages=1.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2609,6 +3339,39 @@
           <t>https://www.covwarkpt.nhs.uk/trust-board-dates-and-papers</t>
         </is>
       </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Strategy: landing lists per-meeting entries (18 dated meeting links this run); each links to its own sub-page of PDFs (agenda, papers, finance). Filter to the main Board (skip ICP/committee/joint). Prefer the largest 'Agenda and Papers' combined PDF. Static fetch works. Pattern C.</t>
+        </is>
+      </c>
+      <c r="J52" t="b">
+        <v>0</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Agenda and Papers;Combined Pack;Public Board Pack</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Validator (static) found dated_pdfs=27, year_archives=0, meeting_subpages=18.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2651,6 +3414,13 @@
           <t>https://www.bhamcommunity.nhs.uk/our-board/</t>
         </is>
       </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2693,6 +3463,39 @@
           <t>https://www.blackcountryhealthcare.nhs.uk/about-us/our-board-of-directors</t>
         </is>
       </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Strategy: dated board-pack PDFs listed directly on the landing page (59 found this run), one per meeting. Static fetch works. Prefer 'Public Board Pack' / 'Board Papers' / 'Agenda and Papers'; filter observer notes, Q&amp;A and addendums. Pattern A.</t>
+        </is>
+      </c>
+      <c r="J54" t="b">
+        <v>0</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Public Board Pack;Board Papers;Agenda and Papers</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Validator (static) found dated_pdfs=59, year_archives=0, meeting_subpages=6.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2735,6 +3538,13 @@
           <t>https://www.kingstonhospital.nhs.uk/about-us/board-papers/</t>
         </is>
       </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2777,6 +3587,13 @@
           <t>https://www.guysandstthomas.nhs.uk/about-us/our-board/agenda-and-papers</t>
         </is>
       </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2819,6 +3636,13 @@
           <t>https://www.lewishamandgreenwich.nhs.uk/board-papers/</t>
         </is>
       </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2861,6 +3685,13 @@
           <t>https://www.croydonhealthservices.nhs.uk/board-timetable-and-papers</t>
         </is>
       </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2903,6 +3734,13 @@
           <t>https://www.stgeorges.nhs.uk/about/our-board/board-meetings/group-board-papers-and-agenda/</t>
         </is>
       </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2945,6 +3783,13 @@
           <t>https://www.kch.nhs.uk/about/how-we-are-organised/board-of-directors/minutes-and-agendas/</t>
         </is>
       </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2984,7 +3829,40 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.epsom-sthelier.nhs.uk/about-us/board-papers/</t>
+          <t>https://www.epsom-sthelier.nhs.uk/our-board</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Strategy: /our-board is the board hub; follow the 'Board papers and agendas' link to dated meeting papers. Static fetch works for the hub. Pattern F: old /about-us/board-papers/ went stale and resolved to the generic About-us page; corrected to /our-board 2026-05-29.</t>
+        </is>
+      </c>
+      <c r="J61" t="b">
+        <v>0</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Board papers and agendas;Public Board</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>papers_partial</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Old board-papers URL resolved to generic about-us; /our-board hub links to 'Board papers and agendas'.</t>
         </is>
       </c>
     </row>
@@ -3029,6 +3907,13 @@
           <t>https://www.moorfields.nhs.uk/about-us/our-organisation/corporate-publications/board-reports</t>
         </is>
       </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3071,6 +3956,13 @@
           <t>https://www.royalmarsden.nhs.uk/board-meetings/</t>
         </is>
       </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3113,6 +4005,13 @@
           <t>https://www.hrch.nhs.uk/</t>
         </is>
       </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3151,6 +4050,39 @@
           <t>https://www.clch.nhs.uk/about-us/our-board/</t>
         </is>
       </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Strategy: landing shows a weak board-papers signal to a static parser (few dated PDFs found). Papers are likely present but loaded via JS or one click into a 'papers'/'meetings' sub-page. Confirm by following the board-papers / meetings link; prefer the main combined pack. Pattern A/C — review on next pass.</t>
+        </is>
+      </c>
+      <c r="J65" t="b">
+        <v>0</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Board Papers;Agenda and Papers;Public Board Pack</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>papers_partial</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Validator (static) weak signal: dated_pdfs=1, year_archives=0, meeting_subpages=0; review.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3193,6 +4125,39 @@
           <t>https://www.bradfordhospitals.nhs.uk/our-trust/bod-meetings/</t>
         </is>
       </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Strategy: 'Board of Directors Meetings' page renders via JS (static body near-empty). Even rendered, the landing shows no direct PDFs — papers are reached by selecting a year / opening a per-meeting entry. Use Playwright and drill into the meeting list. Pattern C/D.</t>
+        </is>
+      </c>
+      <c r="J66" t="b">
+        <v>1</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Board of Directors;Agenda and Papers</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>needs_playwright</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Renders via JS; landing has no direct PDFs, papers nested behind year/meeting selection.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3235,6 +4200,13 @@
           <t>https://www.yorkhospitals.nhs.uk/about-us/board-of-directors/board-of-directors-meetings/</t>
         </is>
       </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3277,6 +4249,13 @@
           <t>https://www.hdft.nhs.uk/about/board-meeting/</t>
         </is>
       </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3319,6 +4298,13 @@
           <t>https://www.airedale-trust.nhs.uk/about-us/our-board-and-leadership/</t>
         </is>
       </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3361,6 +4347,13 @@
           <t>https://www.sheffieldchildrens.nhs.uk/about-us/board-of-directors/</t>
         </is>
       </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3403,6 +4396,13 @@
           <t>https://www.barnsleyhospital.nhs.uk/about/how-we-are-run/board-of-directors/meetings-and-papers</t>
         </is>
       </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3445,6 +4445,39 @@
           <t>https://www.therotherhamft.nhs.uk/about-us/board-meetings</t>
         </is>
       </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Strategy: dated board-pack PDFs listed directly on the landing page (29 found this run), one per meeting. Static fetch works. Prefer 'Public Board Pack' / 'Board Papers' / 'Agenda and Papers'; filter observer notes, Q&amp;A and addendums. Pattern A.</t>
+        </is>
+      </c>
+      <c r="J72" t="b">
+        <v>0</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Public Board Pack;Board Papers;Agenda and Papers</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Validator (static) found dated_pdfs=29, year_archives=0, meeting_subpages=0.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3487,6 +4520,13 @@
           <t>https://www.leedsandyorkpft.nhs.uk/about-us/board-of-directors/board-of-directors-meetings/</t>
         </is>
       </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3529,6 +4569,39 @@
           <t>https://www.sth.nhs.uk/about-us/board-meetings/</t>
         </is>
       </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Strategy: landing lists year archives (4 year links this run, e.g. 'Board papers 2025'). Follow each year link to dated PDF listings; main packs typically 5-30MB. Static fetch works. Pattern B.</t>
+        </is>
+      </c>
+      <c r="J74" t="b">
+        <v>0</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Board Papers;Public Board Pack</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Validator (static) found dated_pdfs=0, year_archives=4, meeting_subpages=0.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3571,6 +4644,13 @@
           <t>https://www.nlg.nhs.uk/resources/board-papers-archive-2021/</t>
         </is>
       </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3613,6 +4693,13 @@
           <t>https://www.dbth.nhs.uk/board/</t>
         </is>
       </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3655,6 +4742,13 @@
           <t>https://www.leedsth.nhs.uk/about-us/board-papers/</t>
         </is>
       </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3697,6 +4791,13 @@
           <t>https://www.humber.nhs.uk/about/trust-board/</t>
         </is>
       </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3739,6 +4840,13 @@
           <t>https://www.hey.nhs.uk/about-us/board-papers/</t>
         </is>
       </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3781,6 +4889,13 @@
           <t>https://www.cht.nhs.uk/publications/board-of-directors-meeting-dates-and-papers</t>
         </is>
       </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3823,6 +4938,13 @@
           <t>https://www.rdash.nhs.uk/about-us/governance/board-of-directors/board-of-directors-meetings/</t>
         </is>
       </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3865,6 +4987,13 @@
           <t>https://www.midyorks.nhs.uk/board-meetings/</t>
         </is>
       </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3907,6 +5036,13 @@
           <t>https://www.southwestyorkshire.nhs.uk/about-us-2/how-were-run/our-trust-board/meeting-papers/</t>
         </is>
       </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3949,6 +5085,13 @@
           <t>https://leedscommunityhealthcare.nhs.uk/about-us/board-of-directors/board-papers-and-meetings/</t>
         </is>
       </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3991,6 +5134,39 @@
           <t>https://www.bdct.nhs.uk/about-us/board-meetings-and-papers/</t>
         </is>
       </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Strategy: dated board-pack PDFs listed directly on the landing page (89 found this run), one per meeting. Static fetch works. Prefer 'Public Board Pack' / 'Board Papers' / 'Agenda and Papers'; filter observer notes, Q&amp;A and addendums. Pattern A.</t>
+        </is>
+      </c>
+      <c r="J85" t="b">
+        <v>0</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Public Board Pack;Board Papers;Agenda and Papers</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>Validator (static) found dated_pdfs=89, year_archives=0, meeting_subpages=1.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4033,6 +5209,39 @@
           <t>https://www.shsc.nhs.uk/about-us/board-directors</t>
         </is>
       </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Strategy: landing shows a weak board-papers signal to a static parser (few dated PDFs found). Papers are likely present but loaded via JS or one click into a 'papers'/'meetings' sub-page. Confirm by following the board-papers / meetings link; prefer the main combined pack. Pattern A/C — review on next pass.</t>
+        </is>
+      </c>
+      <c r="J86" t="b">
+        <v>0</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Board Papers;Agenda and Papers;Public Board Pack</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>papers_partial</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>Validator (static) weak signal: dated_pdfs=0, year_archives=1, meeting_subpages=0; review.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4075,6 +5284,13 @@
           <t>https://www.qehkl.nhs.uk/about-us/meetings-of-the-board-of-directors/</t>
         </is>
       </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4117,6 +5333,13 @@
           <t>https://www.esneft.nhs.uk/about-us/how-we-work/board-of-directors-meetings/</t>
         </is>
       </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4159,6 +5382,13 @@
           <t>https://royalpapworth.nhs.uk/our-hospital/how-we-are-run/our-board-directors/board-directors-meetings</t>
         </is>
       </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4201,6 +5431,13 @@
           <t>https://www.nwangliaft.nhs.uk/trust-board/</t>
         </is>
       </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4243,6 +5480,13 @@
           <t>https://www.jpaget.nhs.uk/about-us/our-board-and-governors/our-board-of-directors/</t>
         </is>
       </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4285,6 +5529,13 @@
           <t>https://www.wsh.nhs.uk/our-organisation/how-we-are-run/trust-board</t>
         </is>
       </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4327,6 +5578,13 @@
           <t>https://www.cuh.nhs.uk/about-us/board-directors/board-of-directors-meetings/</t>
         </is>
       </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4369,6 +5627,13 @@
           <t>https://www.nnuh.nhs.uk/about-us/trust-board-meetings/</t>
         </is>
       </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4411,6 +5676,13 @@
           <t>https://www.nsft.nhs.uk/board-papers/</t>
         </is>
       </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4453,6 +5725,13 @@
           <t>https://www.cpft.nhs.uk/board-of-directors/</t>
         </is>
       </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4495,6 +5774,13 @@
           <t>https://eastofenglandcommunityhealthandcare.nhs.uk/about-us/our-board/board-meetings-and-reports/</t>
         </is>
       </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4537,6 +5823,13 @@
           <t>https://www.uhd.nhs.uk/about-us/our-performance/board-papers</t>
         </is>
       </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4579,6 +5872,13 @@
           <t>https://www.uhbw.nhs.uk/about-us/board-papers/</t>
         </is>
       </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4621,6 +5921,13 @@
           <t>https://www.torbayandsouthdevon.nhs.uk/about-us/board-meetings/</t>
         </is>
       </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4663,6 +5970,13 @@
           <t>https://www.dchft.nhs.uk/about-us/trust-board/</t>
         </is>
       </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4705,6 +6019,13 @@
           <t>https://www.ruh.nhs.uk/about/trustboard/index.asp</t>
         </is>
       </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4747,6 +6068,39 @@
           <t>https://www.dorsethealthcare.nhs.uk/about-us/trust-board</t>
         </is>
       </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Strategy: dated board-pack PDFs listed directly on the landing page (14 found this run), one per meeting. Static fetch works. Prefer 'Public Board Pack' / 'Board Papers' / 'Agenda and Papers'; filter observer notes, Q&amp;A and addendums. Pattern A.</t>
+        </is>
+      </c>
+      <c r="J103" t="b">
+        <v>0</v>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Public Board Pack;Board Papers;Agenda and Papers</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>Validator (static) found dated_pdfs=14, year_archives=0, meeting_subpages=0.</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4789,6 +6143,39 @@
           <t>https://www.royalcornwall.nhs.uk/our-organisation/about/your-trust-board/</t>
         </is>
       </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Strategy: board papers reachable from this landing; confirm navigation on next deep pass. Prefer the main combined board pack.</t>
+        </is>
+      </c>
+      <c r="J104" t="b">
+        <v>0</v>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Public Board Pack;Board Papers;Agenda and Papers</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>broken</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>Validator classification: broken.</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4831,6 +6218,13 @@
           <t>https://www.somersetft.nhs.uk/about-us/trust-board-meetings/</t>
         </is>
       </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4873,6 +6267,13 @@
           <t>https://www.royaldevon.nhs.uk/about-us/board-of-directors/board-meetings-papers-minutes/</t>
         </is>
       </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4915,6 +6316,13 @@
           <t>https://www.cornwallft.nhs.uk/board-papers/</t>
         </is>
       </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4957,6 +6365,13 @@
           <t>https://www.plymouthhospitals.nhs.uk/trust-board-meetings-and-papers/</t>
         </is>
       </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4999,6 +6414,13 @@
           <t>https://www.gwh.nhs.uk/about-us/trust-board/board-meetings/</t>
         </is>
       </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5041,6 +6463,13 @@
           <t>https://www.salisbury.nhs.uk/about-us/the-trust-board/trust-board-meetings/</t>
         </is>
       </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5083,6 +6512,13 @@
           <t>https://www.gloshospitals.nhs.uk/about-us/our-board/board-papers/</t>
         </is>
       </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5125,6 +6561,39 @@
           <t>https://www.ghc.nhs.uk/who-we-are/board-and-governors/</t>
         </is>
       </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Strategy: dated board-pack PDFs listed directly on the landing page (25 found this run), one per meeting. Static fetch works. Prefer 'Public Board Pack' / 'Board Papers' / 'Agenda and Papers'; filter observer notes, Q&amp;A and addendums. Pattern A.</t>
+        </is>
+      </c>
+      <c r="J112" t="b">
+        <v>0</v>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Public Board Pack;Board Papers;Agenda and Papers</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>Validator (static) found dated_pdfs=25, year_archives=0, meeting_subpages=1.</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5167,6 +6636,13 @@
           <t>https://www.nbt.nhs.uk/about-us/meet-our-board/trust-board-meetings-20252026</t>
         </is>
       </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5209,6 +6685,13 @@
           <t>https://www.awp.nhs.uk/about-us/publications/board-papers</t>
         </is>
       </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5251,6 +6734,39 @@
           <t>https://www.dpt.nhs.uk/publications/</t>
         </is>
       </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Strategy: landing lists year archives (3 year links this run, e.g. 'Board papers 2025'). Follow each year link to dated PDF listings; main packs typically 5-30MB. Static fetch works. Pattern B.</t>
+        </is>
+      </c>
+      <c r="J115" t="b">
+        <v>0</v>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Board Papers;Public Board Pack</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>Validator (static) found dated_pdfs=0, year_archives=3, meeting_subpages=0.</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -5293,6 +6809,13 @@
           <t>https://www.oxleas.nhs.uk/board-papers/</t>
         </is>
       </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -5332,7 +6855,40 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>https://www.stgeorges.nhs.uk/about-us/board-papers/</t>
+          <t>https://swlstg.nhs.uk/our-board</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Strategy: board papers, agendas and minutes are listed directly on the trust-board landing page (swlstg.nhs.uk/our-board), grouped by year, one entry per bi-monthly meeting. Prefer the 'Trust Board Part A' main pack (skip Part B / private). Static fetch works. Pattern F: DB URL was previously the wrong domain (stgeorges.nhs.uk = St George's University Hospitals, a different trust); corrected 2026-05-29.</t>
+        </is>
+      </c>
+      <c r="J117" t="b">
+        <v>0</v>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Trust Board Part A;main pack;supplementary pack</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>Part B;Minutes only;private</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>Corrected from wrong domain; new page shows 2025-2026 Trust Board Part A main + supplementary packs.</t>
         </is>
       </c>
     </row>
@@ -5377,6 +6933,13 @@
           <t>https://www.slam.nhs.uk/about-us/trust-board/</t>
         </is>
       </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5419,6 +6982,13 @@
           <t>https://www.bartshealth.nhs.uk/board-meetings</t>
         </is>
       </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5461,6 +7031,13 @@
           <t>https://www.nwl-acute-provider-group.nhs.uk/publications</t>
         </is>
       </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -5503,6 +7080,39 @@
           <t>https://www.royalfree.nhs.uk/about-us/trust-board/trust-board-meetings</t>
         </is>
       </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Strategy: /about-us/trust-board/trust-board-meetings is correct (archive at /about-us/trust-board/archived-board-papers; also hosts former North Middlesex board papers). Site WAF returns 403/500 to non-browser fetchers. Pattern E anti-bot — use a browser/Playwright; bi-monthly meetings.</t>
+        </is>
+      </c>
+      <c r="J121" t="b">
+        <v>1</v>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Board papers;Agenda</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>needs_playwright</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>WAF returns 403/500 to bots; Google confirms URL is the live 'Trust board meetings' page.</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -5545,6 +7155,13 @@
           <t>https://www.nwl-acute-provider-group.nhs.uk/about-us/board-in-common</t>
         </is>
       </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5587,6 +7204,13 @@
           <t>https://www.bhrhospitals.nhs.uk/papers-minutes/</t>
         </is>
       </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5629,6 +7253,13 @@
           <t>https://www.whittington.nhs.uk/default.asp?c=20208</t>
         </is>
       </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5671,6 +7302,39 @@
           <t>https://www.chelwest.nhs.uk/about-us/board-of-directors/</t>
         </is>
       </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Strategy: landing lists year archives (5 year links this run, e.g. 'Board papers 2025'). Follow each year link to dated PDF listings; main packs typically 5-30MB. Static fetch works. Pattern B.</t>
+        </is>
+      </c>
+      <c r="J125" t="b">
+        <v>0</v>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Board Papers;Public Board Pack</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>Validator (static) found dated_pdfs=0, year_archives=5, meeting_subpages=2.</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5713,6 +7377,13 @@
           <t>https://www.homerton.nhs.uk/board-papers/</t>
         </is>
       </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5755,6 +7426,39 @@
           <t>https://www.uclh.nhs.uk/about-us/who-we-are/board-directors/board-meetings-and-papers</t>
         </is>
       </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Strategy: dated board-pack PDFs listed directly on the landing page (12 found this run), one per meeting. Static fetch works. Prefer 'Public Board Pack' / 'Board Papers' / 'Agenda and Papers'; filter observer notes, Q&amp;A and addendums. Pattern A.</t>
+        </is>
+      </c>
+      <c r="J127" t="b">
+        <v>0</v>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Public Board Pack;Board Papers;Agenda and Papers</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>Validator (static) found dated_pdfs=12, year_archives=17, meeting_subpages=6.</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5797,6 +7501,13 @@
           <t>https://www.imperial.nhs.uk/about-us/board-papers/</t>
         </is>
       </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5839,6 +7550,39 @@
           <t>https://www.rnoh.nhs.uk/about-us/corporate-information/board-meetings</t>
         </is>
       </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Strategy: dated board-pack PDFs listed directly on the landing page (34 found this run), one per meeting. Static fetch works. Prefer 'Public Board Pack' / 'Board Papers' / 'Agenda and Papers'; filter observer notes, Q&amp;A and addendums. Pattern A.</t>
+        </is>
+      </c>
+      <c r="J129" t="b">
+        <v>0</v>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Public Board Pack;Board Papers;Agenda and Papers</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>Validator (static) found dated_pdfs=34, year_archives=0, meeting_subpages=1.</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5881,6 +7625,13 @@
           <t>https://www.gosh.nhs.uk/about-us/who-we-are/organisational-structure/trust-board/trust-board-meetings/</t>
         </is>
       </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
+      <c r="O130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5923,6 +7674,13 @@
           <t>https://www.londonambulance.nhs.uk/about-us/how-we-are-run/trust-board/</t>
         </is>
       </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5965,6 +7723,13 @@
           <t>https://www.nelft.nhs.uk/about-us-board-papers/</t>
         </is>
       </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
+      <c r="O132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -6007,6 +7772,39 @@
           <t>https://www.westlondon.nhs.uk/about-us/trust-board/board-papers</t>
         </is>
       </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Strategy: dated board-pack PDFs listed directly on the landing page (55 found this run), one per meeting. Static fetch works. Prefer 'Public Board Pack' / 'Board Papers' / 'Agenda and Papers'; filter observer notes, Q&amp;A and addendums. Pattern A.</t>
+        </is>
+      </c>
+      <c r="J133" t="b">
+        <v>0</v>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Public Board Pack;Board Papers;Agenda and Papers</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>Validator (static) found dated_pdfs=55, year_archives=0, meeting_subpages=0.</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -6049,6 +7847,13 @@
           <t>https://tavistockandportman.nhs.uk/about-us/our-board/</t>
         </is>
       </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
+      <c r="O134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -6091,6 +7896,13 @@
           <t>https://www.cnwl.nhs.uk/about/planning-performance-and-reports</t>
         </is>
       </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
+      <c r="O135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -6133,6 +7945,13 @@
           <t>https://www.elft.nhs.uk/information-about-elft/our-board/trust-board-meetings</t>
         </is>
       </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
+      <c r="O136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -6175,6 +7994,13 @@
           <t>https://www.stsft.nhs.uk/about-us/our-people/our-board/board-papers</t>
         </is>
       </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
+      <c r="O137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -6217,6 +8043,13 @@
           <t>https://www.ncic.nhs.uk/trust/how-we-are-run/board-meetings</t>
         </is>
       </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
+      <c r="O138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -6259,6 +8092,13 @@
           <t>https://www.gatesheadhealth.nhs.uk/news/resources_type/board-papers/</t>
         </is>
       </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
+      <c r="O139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -6301,6 +8141,13 @@
           <t>https://www.newcastle-hospitals.nhs.uk/about/board-of-directors-2/board-of-directors-papers/</t>
         </is>
       </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
+      <c r="O140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -6343,6 +8190,13 @@
           <t>https://www.northumbria.nhs.uk/about-us/corporate-information/strategies-and-reports/board-papers</t>
         </is>
       </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
+      <c r="O141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -6385,6 +8239,13 @@
           <t>https://www.southtees.nhs.uk/resources/board-of-directors-agenda-1-february-2022/</t>
         </is>
       </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
+      <c r="O142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -6427,6 +8288,13 @@
           <t>https://www.nth.nhs.uk/about/board-meetings/</t>
         </is>
       </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
+      <c r="O143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -6469,6 +8337,39 @@
           <t>https://www.tewv.nhs.uk/about/board/papers-previous-board-meetings/</t>
         </is>
       </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Strategy: dated board-pack PDFs listed directly on the landing page (53 found this run), one per meeting. Static fetch works. Prefer 'Public Board Pack' / 'Board Papers' / 'Agenda and Papers'; filter observer notes, Q&amp;A and addendums. Pattern A.</t>
+        </is>
+      </c>
+      <c r="J144" t="b">
+        <v>0</v>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Public Board Pack;Board Papers;Agenda and Papers</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>Validator (static) found dated_pdfs=53, year_archives=0, meeting_subpages=0.</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -6511,6 +8412,13 @@
           <t>https://www.cntw.nhs.uk/about/publications/board-papers-27-may-2015/agenda-item-10-i-trust-board-models-of-care-front-sheet/</t>
         </is>
       </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
+      <c r="O145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -6553,6 +8461,13 @@
           <t>https://www.cddft.nhs.uk/about-us/corporate-information/trust-board/board-meetings-and-papers</t>
         </is>
       </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
+      <c r="O146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -6595,6 +8510,13 @@
           <t>https://hiowhealthcare.nhs.uk/about-us/our-board/meetings-and-papers</t>
         </is>
       </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
+      <c r="O147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -6633,6 +8555,13 @@
           <t>https://www.iow.nhs.uk/about-us/our-trust-board</t>
         </is>
       </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
+      <c r="O148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -6675,6 +8604,13 @@
           <t>https://www.fhft.nhs.uk/about-us/how-we-are-run/trust-board</t>
         </is>
       </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
+      <c r="O149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -6717,6 +8653,13 @@
           <t>https://www.uhs.nhs.uk/about-the-trust/how-the-trust-is-run/trust-board</t>
         </is>
       </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
+      <c r="O150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -6759,6 +8702,39 @@
           <t>https://www.porthosp.nhs.uk/about-us/our-trust/our-trust-board</t>
         </is>
       </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Strategy: landing lists year archives (3 year links this run, e.g. 'Board papers 2025'). Follow each year link to dated PDF listings; main packs typically 5-30MB. Static fetch works. Pattern B.</t>
+        </is>
+      </c>
+      <c r="J151" t="b">
+        <v>0</v>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Board Papers;Public Board Pack</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>Validator (static) found dated_pdfs=3, year_archives=3, meeting_subpages=0.</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -6801,6 +8777,13 @@
           <t>http://www.royalberkshire.nhs.uk/about-us/governance/open-meetings</t>
         </is>
       </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
+      <c r="O152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -6843,6 +8826,13 @@
           <t>https://www.hampshirehospitals.nhs.uk/about-us/our-publications/board-directors-papers</t>
         </is>
       </c>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
+      <c r="O153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -6885,6 +8875,13 @@
           <t>https://www.oxfordhealth.nhs.uk/about-us/board-papers/</t>
         </is>
       </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
+      <c r="O154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -6927,6 +8924,13 @@
           <t>https://www.ouh.nhs.uk/about/trust-board/meetings-and-papers/</t>
         </is>
       </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
+      <c r="O155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6969,6 +8973,13 @@
           <t>https://hiowhealthcare.nhs.uk/about-us/our-board/meetings-and-papers</t>
         </is>
       </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
+      <c r="O156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -7011,6 +9022,13 @@
           <t>https://www.berkshirehealthcare.nhs.uk/about-us/our-board-meetings</t>
         </is>
       </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
+      <c r="O157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -7053,6 +9071,13 @@
           <t>https://www.buckshealthcare.nhs.uk/publications/trust-board-papers/</t>
         </is>
       </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
+      <c r="O158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -7095,6 +9120,13 @@
           <t>https://www.mft.nhs.uk/about-us/board-of-directors/</t>
         </is>
       </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
+      <c r="O159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -7137,6 +9169,13 @@
           <t>https://www.christie.nhs.uk/about-us/the-foundation-trust/about-the-trust/board-of-directors-meetings</t>
         </is>
       </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
+      <c r="O160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -7179,6 +9218,13 @@
           <t>https://www.northerncarealliance.nhs.uk/about-us/board-directors/board-dates-and-papers</t>
         </is>
       </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
+      <c r="O161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -7221,6 +9267,13 @@
           <t>https://www.boltonft.nhs.uk/about-us/our-board/</t>
         </is>
       </c>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
+      <c r="O162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -7263,6 +9316,13 @@
           <t>https://tamesideandglossopicft.nhs.uk/about-us/trust-oversight/trust-board</t>
         </is>
       </c>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
+      <c r="O163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -7305,6 +9365,39 @@
           <t>https://www.wwl.nhs.uk/about-us/board-papers/</t>
         </is>
       </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Strategy: /about-us/board-papers/ is correct and working — it lists upcoming meetings, a '&lt;year&gt; Board Papers' section with per-meeting 'Meeting papers' PDF bundles, and an archive. The 'Meeting papers' links load via JS, which is why a static parser sees no PDFs. Pattern A/C; prefer the public bundle PDF.</t>
+        </is>
+      </c>
+      <c r="J164" t="b">
+        <v>1</v>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Meeting papers;public bundle;Board Papers</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>Working page with 2026 'Meeting papers' bundles; static parser missed JS-loaded PDF links (false no_papers_visible).</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -7347,6 +9440,13 @@
           <t>https://www.penninecare.nhs.uk/boardmeetings</t>
         </is>
       </c>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
+      <c r="O165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -7389,6 +9489,13 @@
           <t>https://www.stockport.nhs.uk/about/board/board-meetings/</t>
         </is>
       </c>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
+      <c r="O166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -7431,6 +9538,13 @@
           <t>https://www.gmmh.nhs.uk/board-meetings/</t>
         </is>
       </c>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
+      <c r="O167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -7473,6 +9587,39 @@
           <t>https://eput.nhs.uk/about-us/board-of-directors/board-meetings/board-papers/</t>
         </is>
       </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Strategy: dated board-pack PDFs listed directly on the landing page (28 found this run), one per meeting. Static fetch works. Prefer 'Public Board Pack' / 'Board Papers' / 'Agenda and Papers'; filter observer notes, Q&amp;A and addendums. Pattern A.</t>
+        </is>
+      </c>
+      <c r="J168" t="b">
+        <v>0</v>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Public Board Pack;Board Papers;Agenda and Papers</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>Validator (static) found dated_pdfs=28, year_archives=0, meeting_subpages=0.</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -7515,6 +9662,13 @@
           <t>https://www.mse.nhs.uk/board-meetings/</t>
         </is>
       </c>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
+      <c r="O169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -7557,6 +9711,13 @@
           <t>https://www.bedfordshirehospitals.nhs.uk/corporate-information/board-meetings-and-directors/board-meetings/</t>
         </is>
       </c>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
+      <c r="O170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -7599,6 +9760,13 @@
           <t>https://www.mkuh.nhs.uk/about-us/our-structure/board-of-directors/agendas-and-meetings</t>
         </is>
       </c>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
+      <c r="O171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -7641,6 +9809,13 @@
           <t>https://www.pah.nhs.uk/about/board/board-papers/</t>
         </is>
       </c>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
+      <c r="O172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -7683,6 +9858,13 @@
           <t>https://www.westhertshospitals.nhs.uk/about-us/our-board/board-meetings</t>
         </is>
       </c>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" t="inlineStr"/>
+      <c r="N173" t="inlineStr"/>
+      <c r="O173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -7725,6 +9907,39 @@
           <t>https://www.enherts-tr.nhs.uk/gp-professionals/publications/board-papers-september-2023/</t>
         </is>
       </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Strategy: landing shows a weak board-papers signal to a static parser (few dated PDFs found). Papers are likely present but loaded via JS or one click into a 'papers'/'meetings' sub-page. Confirm by following the board-papers / meetings link; prefer the main combined pack. Pattern A/C — review on next pass.</t>
+        </is>
+      </c>
+      <c r="J174" t="b">
+        <v>0</v>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Board Papers;Agenda and Papers;Public Board Pack</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>papers_partial</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>Validator (static) weak signal: dated_pdfs=1, year_archives=0, meeting_subpages=2; review.</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -7767,6 +9982,13 @@
           <t>https://www.hpft.nhs.uk/about-us/corporate-information-and-governance/</t>
         </is>
       </c>
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
+      <c r="O175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -7809,6 +10031,39 @@
           <t>https://www.hct.nhs.uk/our-board/</t>
         </is>
       </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Strategy: landing lists per-meeting entries (97 dated meeting links this run); each links to its own sub-page of PDFs (agenda, papers, finance). Filter to the main Board (skip ICP/committee/joint). Prefer the largest 'Agenda and Papers' combined PDF. Static fetch works. Pattern C.</t>
+        </is>
+      </c>
+      <c r="J176" t="b">
+        <v>0</v>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Agenda and Papers;Combined Pack;Public Board Pack</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>Validator (static) found dated_pdfs=13, year_archives=0, meeting_subpages=97.</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -7851,6 +10106,13 @@
           <t>https://www.wuth.nhs.uk/about-us/who-we-are/board-meetings/</t>
         </is>
       </c>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr"/>
+      <c r="N177" t="inlineStr"/>
+      <c r="O177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -7893,6 +10155,13 @@
           <t>https://www.merseywestlancs.nhs.uk/trust-board-meetings-and-papers</t>
         </is>
       </c>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
+      <c r="O178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -7935,6 +10204,13 @@
           <t>https://www.lhch.nhs.uk/board-of-directors-meetings</t>
         </is>
       </c>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
+      <c r="O179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -7977,6 +10253,13 @@
           <t>https://www.alderhey.nhs.uk/about-us/trust-board/</t>
         </is>
       </c>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" t="inlineStr"/>
+      <c r="N180" t="inlineStr"/>
+      <c r="O180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -8019,6 +10302,13 @@
           <t>https://www.mcht.nhs.uk/about-us/board-directors/board-papers-and-minutes</t>
         </is>
       </c>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" t="inlineStr"/>
+      <c r="N181" t="inlineStr"/>
+      <c r="O181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -8061,6 +10351,13 @@
           <t>https://www.uhliverpool.nhs.uk/about-us/meet-our-board/trust-board-meetings</t>
         </is>
       </c>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" t="inlineStr"/>
+      <c r="N182" t="inlineStr"/>
+      <c r="O182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -8103,6 +10400,39 @@
           <t>https://www.clatterbridgecc.nhs.uk/about-us/how-were-run/trust-board/board-meetings</t>
         </is>
       </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Strategy: landing lists year archives (3 year links this run, e.g. 'Board papers 2025'). Follow each year link to dated PDF listings; main packs typically 5-30MB. Static fetch works. Pattern B.</t>
+        </is>
+      </c>
+      <c r="J183" t="b">
+        <v>0</v>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Board Papers;Public Board Pack</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>Validator (static) found dated_pdfs=0, year_archives=3, meeting_subpages=0.</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -8145,6 +10475,13 @@
           <t>https://www.liverpoolwomens.nhs.uk/about-us/board-papers/</t>
         </is>
       </c>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" t="inlineStr"/>
+      <c r="N184" t="inlineStr"/>
+      <c r="O184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -8187,6 +10524,13 @@
           <t>https://www.thewaltoncentre.nhs.uk/trust-board/</t>
         </is>
       </c>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr"/>
+      <c r="N185" t="inlineStr"/>
+      <c r="O185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -8229,6 +10573,13 @@
           <t>https://www.eastcheshire.nhs.uk/trust/board/reports-and-meetings/agm</t>
         </is>
       </c>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" t="inlineStr"/>
+      <c r="N186" t="inlineStr"/>
+      <c r="O186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -8268,7 +10619,40 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>https://www.coch.nhs.uk/about-us/board-papers/</t>
+          <t>https://www.coch.nhs.uk/corporate-information/board-of-directors/board-of-directors-meeting-packs.aspx</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Strategy: meeting packs page (/corporate-information/board-of-directors/board-of-directors-meeting-packs.aspx) lists ~54 dated PDFs under /media/, titled 'Agenda and Papers - &lt;Month Year&gt;', plus per-item Integrated Performance Reports. Older packs under .../meeting-packs/archive.aspx. Pattern A + F: old /about-us/board-papers/ was an error page; corrected 2026-05-29.</t>
+        </is>
+      </c>
+      <c r="J187" t="b">
+        <v>0</v>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Agenda and Papers;Public Board of Directors</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>Council of Governors;Minutes only;Confidential</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>Old URL was an error page; corrected page shows 54 dated 'Agenda and Papers' PDFs (2023-2026).</t>
         </is>
       </c>
     </row>
@@ -8313,6 +10697,39 @@
           <t>https://www.uhmb.nhs.uk/our-trust/trust-board-and-council-governor-meetings</t>
         </is>
       </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Strategy: landing lists per-meeting entries (42 dated meeting links this run); each links to its own sub-page of PDFs (agenda, papers, finance). Filter to the main Board (skip ICP/committee/joint). Prefer the largest 'Agenda and Papers' combined PDF. Static fetch works. Pattern C.</t>
+        </is>
+      </c>
+      <c r="J188" t="b">
+        <v>0</v>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Agenda and Papers;Combined Pack;Public Board Pack</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>Validator (static) found dated_pdfs=17, year_archives=1, meeting_subpages=42.</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -8355,6 +10772,13 @@
           <t>https://www.merseycare.nhs.uk/board-papers</t>
         </is>
       </c>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" t="inlineStr"/>
+      <c r="N189" t="inlineStr"/>
+      <c r="O189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -8397,6 +10821,13 @@
           <t>https://www.lscft.nhs.uk/about-us/board/board-papers</t>
         </is>
       </c>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" t="inlineStr"/>
+      <c r="N190" t="inlineStr"/>
+      <c r="O190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -8439,6 +10870,13 @@
           <t>https://whh.nhs.uk/about-us/how-we-work/board-meetings-and-papers/</t>
         </is>
       </c>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" t="inlineStr"/>
+      <c r="N191" t="inlineStr"/>
+      <c r="O191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -8481,6 +10919,39 @@
           <t>https://www.cwp.nhs.uk/about-us/our-board-and-governors/</t>
         </is>
       </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Strategy: board papers reachable from this landing; confirm navigation on next deep pass. Prefer the main combined board pack.</t>
+        </is>
+      </c>
+      <c r="J192" t="b">
+        <v>0</v>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Public Board Pack;Board Papers;Agenda and Papers</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>broken</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>Validator classification: broken.</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -8523,6 +10994,39 @@
           <t>https://www.blackpoolteachinghospitals.nhs.uk/about-us/meet-board/board-meetings-public</t>
         </is>
       </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Strategy: 'Board Meetings in Public' page renders via JS (static body near-empty). Landing shows no direct PDFs; papers are reached through per-meeting sub-pages. Use Playwright (wait_until=networkidle) and follow the meeting links. Pattern C/D.</t>
+        </is>
+      </c>
+      <c r="J193" t="b">
+        <v>1</v>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Board Meetings in Public;Agenda and Papers</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>needs_playwright</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>Renders via JS; landing lists meetings, papers on per-meeting sub-pages.</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -8565,6 +11069,13 @@
           <t>https://www.lancsteachinghospitals.nhs.uk/board-of-directors</t>
         </is>
       </c>
+      <c r="I194" t="inlineStr"/>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" t="inlineStr"/>
+      <c r="N194" t="inlineStr"/>
+      <c r="O194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -8604,7 +11115,40 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>https://elht.nhs.uk/about-us/board-meetings-including-agenda-and-papers</t>
+          <t>https://elht.nhs.uk/about-us/our-trust-board/board-meetings-including-agenda-and-papers</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Strategy: board page moved under /about-us/our-trust-board/. The papers page (/about-us/our-trust-board/board-meetings-including-agenda-and-papers) lists current-year meetings and links to per-year archive sub-pages (archive-2022, archive-2023, ...). Papers load via JS, so use Playwright. Pattern C/D + F: old /about-us/board-meetings-... path 404'd after restructure; corrected 2026-05-29.</t>
+        </is>
+      </c>
+      <c r="J195" t="b">
+        <v>1</v>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Trust Board;Agenda and Papers;Part 1</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>Part 2;private;Minutes only</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>needs_playwright</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>Old path 404'd after site restructure; papers now under /our-trust-board/, JS-rendered with year archives.</t>
         </is>
       </c>
     </row>
@@ -8649,6 +11193,13 @@
           <t>https://bridgewater.nhs.uk/about-us/how-we-work/board-meetings-and-papers/</t>
         </is>
       </c>
+      <c r="I196" t="inlineStr"/>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" t="inlineStr"/>
+      <c r="N196" t="inlineStr"/>
+      <c r="O196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -8691,6 +11242,13 @@
           <t>https://www.wchc.nhs.uk/about/board-governors/board-meetings-papers/</t>
         </is>
       </c>
+      <c r="I197" t="inlineStr"/>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr"/>
+      <c r="M197" t="inlineStr"/>
+      <c r="N197" t="inlineStr"/>
+      <c r="O197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -8733,6 +11291,13 @@
           <t>https://www.neas.nhs.uk/about-us/trust-board</t>
         </is>
       </c>
+      <c r="I198" t="inlineStr"/>
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr"/>
+      <c r="M198" t="inlineStr"/>
+      <c r="N198" t="inlineStr"/>
+      <c r="O198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -8775,6 +11340,13 @@
           <t>https://www.nwas.nhs.uk/publications/board-papers-26-april-2023/</t>
         </is>
       </c>
+      <c r="I199" t="inlineStr"/>
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" t="inlineStr"/>
+      <c r="N199" t="inlineStr"/>
+      <c r="O199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -8817,6 +11389,13 @@
           <t>https://www.yas.nhs.uk/about-us/the-trust-board/</t>
         </is>
       </c>
+      <c r="I200" t="inlineStr"/>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr"/>
+      <c r="M200" t="inlineStr"/>
+      <c r="N200" t="inlineStr"/>
+      <c r="O200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -8859,6 +11438,13 @@
           <t>https://www.emas.nhs.uk/about-us/trust-board/next-board-meeting/archive-board-papers</t>
         </is>
       </c>
+      <c r="I201" t="inlineStr"/>
+      <c r="J201" t="inlineStr"/>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr"/>
+      <c r="M201" t="inlineStr"/>
+      <c r="N201" t="inlineStr"/>
+      <c r="O201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -8901,6 +11487,13 @@
           <t>https://www.wmas.nhs.uk/about-us/board-papers/</t>
         </is>
       </c>
+      <c r="I202" t="inlineStr"/>
+      <c r="J202" t="inlineStr"/>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr"/>
+      <c r="M202" t="inlineStr"/>
+      <c r="N202" t="inlineStr"/>
+      <c r="O202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -8943,6 +11536,13 @@
           <t>https://www.eastamb.nhs.uk/about-us/trust-board/public-board-meetings-and-papers</t>
         </is>
       </c>
+      <c r="I203" t="inlineStr"/>
+      <c r="J203" t="inlineStr"/>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr"/>
+      <c r="M203" t="inlineStr"/>
+      <c r="N203" t="inlineStr"/>
+      <c r="O203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -8985,6 +11585,13 @@
           <t>https://www.secamb.nhs.uk/about-us/board-papers/</t>
         </is>
       </c>
+      <c r="I204" t="inlineStr"/>
+      <c r="J204" t="inlineStr"/>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr"/>
+      <c r="M204" t="inlineStr"/>
+      <c r="N204" t="inlineStr"/>
+      <c r="O204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -9027,6 +11634,13 @@
           <t>https://www.scas.nhs.uk/about-us/board-of-directors/</t>
         </is>
       </c>
+      <c r="I205" t="inlineStr"/>
+      <c r="J205" t="inlineStr"/>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr"/>
+      <c r="M205" t="inlineStr"/>
+      <c r="N205" t="inlineStr"/>
+      <c r="O205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -9069,6 +11683,13 @@
           <t>https://www.swast.nhs.uk/our-board/board-meeting-schedule-and-public-papers</t>
         </is>
       </c>
+      <c r="I206" t="inlineStr"/>
+      <c r="J206" t="inlineStr"/>
+      <c r="K206" t="inlineStr"/>
+      <c r="L206" t="inlineStr"/>
+      <c r="M206" t="inlineStr"/>
+      <c r="N206" t="inlineStr"/>
+      <c r="O206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -9111,6 +11732,13 @@
           <t>https://www.northlondonmentalhealth.nhs.uk/meetings-and-papers/</t>
         </is>
       </c>
+      <c r="I207" t="inlineStr"/>
+      <c r="J207" t="inlineStr"/>
+      <c r="K207" t="inlineStr"/>
+      <c r="L207" t="inlineStr"/>
+      <c r="M207" t="inlineStr"/>
+      <c r="N207" t="inlineStr"/>
+      <c r="O207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -9141,6 +11769,13 @@
         </is>
       </c>
       <c r="H208" t="inlineStr"/>
+      <c r="I208" t="inlineStr"/>
+      <c r="J208" t="inlineStr"/>
+      <c r="K208" t="inlineStr"/>
+      <c r="L208" t="inlineStr"/>
+      <c r="M208" t="inlineStr"/>
+      <c r="N208" t="inlineStr"/>
+      <c r="O208" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/trust_urls.xlsx
+++ b/trust_urls.xlsx
@@ -2399,13 +2399,39 @@
           <t>https://www.uhnm.nhs.uk/about-us/our-board/</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Strategy: landing /about-us/our-board/ is a governance overview, NOT the archive. Follow the 'Board papers' link on the page to /board-papers/ which uses a year-tab archive layout. WARNING: /board-papers/ also exposes FOI request responses mixed into the same listing — filter to 'Trust Board Part 1' / 'Part-1 Trust Board' to isolate genuine board packs. The follow_subpage + interactive_dom Python strategy handles this correctly in the risk-tracker discoverer.</t>
+        </is>
+      </c>
+      <c r="J36" t="b">
+        <v>0</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Trust Board Part 1; Part-1 Trust Board; Wednesday Trust Board</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>FOI; Freedom of Information; DPIA; P&amp;O Services; Part 2; Confidential; Privacy Impact</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>papers_partial</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Landing is OK but is 1 click away from the archive at /board-papers/. Latest 2026 packs Feb (7.8MB, BAF score 624) and Apr (11.3MB) confirmed.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4047,12 +4073,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.clch.nhs.uk/about-us/our-board/</t>
+          <t>https://clch.nhs.uk/about-us/publications/board-papers-and-committee-tor</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Strategy: landing shows a weak board-papers signal to a static parser (few dated PDFs found). Papers are likely present but loaded via JS or one click into a 'papers'/'meetings' sub-page. Confirm by following the board-papers / meetings link; prefer the main combined pack. Pattern A/C — review on next pass.</t>
+          <t>Strategy: papers under /publications/ NOT under /our-board/. Static HTML list of /download_file/ links with dates in adjacent text spans. URL pattern split: older items at /download_file/{id}/0 (no /view), newer at /download_file/view/{id}/785 — BOTH 302-redirect to the PDF. Two streams on the same page: (a) CLCH Trust Board monthly-ish meetings, and (b) Board-in-Common jointly with CNWL + West London NHS Trust (twice yearly). Multiple PDFs per meeting — typically a main agenda+papers pack PLUS an Annexes A-X pack, occasionally a third (eg Fire Safety Statement). Grab all to capture the complete pack. Old DB URL /about-us/our-board/ is a director-bios page; the only PDF it shows is the declarations of interest. Trust secretary contact for missing/older packs: clcht.trust.secretary@nhs.net.</t>
         </is>
       </c>
       <c r="J65" t="b">
@@ -4060,12 +4086,12 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Board Papers;Agenda and Papers;Public Board Pack</t>
+          <t>agenda and papers; meeting papers; agenda + papers; Board-in-Common agenda</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+          <t>declaration of interests; Questions for the board; annexes only; ToR</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -4075,12 +4101,12 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>papers_partial</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Validator (static) weak signal: dated_pdfs=1, year_archives=0, meeting_subpages=0; review.</t>
+          <t>Live archive at /publications/board-papers-and-committee-tor. Confirmed PDFs 28 May 2026, 30 Apr 2026, 26 Mar 2026 (Trust Board) + Board-in-Common 29 Apr 2026 + 22 Oct 2025.</t>
         </is>
       </c>
     </row>
@@ -6140,12 +6166,12 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>https://www.royalcornwall.nhs.uk/our-organisation/about/your-trust-board/</t>
+          <t>https://royalcornwallhospitals.nhs.uk/organisation/board-meetings/</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Strategy: board papers reachable from this landing; confirm navigation on next deep pass. Prefer the main combined board pack.</t>
+          <t>Strategy: NEW DOMAIN. Trust migrated to royalcornwallhospitals.nhs.uk (the legacy royalcornwall.nhs.uk URL has WAF/Cloudflare protection that blocks direct fetch with HTTP 403, even from headless Chromium). The new landing page links to year-archive .aspx pages on a SEPARATE document-library subdomain: doclibrary-rcht.cornwall.nhs.uk/.../BoardMeetings/BoardMeetings{FY}.aspx (eg BoardMeetings2526.aspx, BoardMeetings2627.aspx) — the doc-library subdomain has NO WAF and serves PDFs cleanly over plain HTTP. PDFs live at /DocumentsLibrary/RoyalCornwallHospitalsTrust/ChiefExecutive/TrustBoard/Minutes/{FYYY}/{YYYYMM}/ where FYYY is the 4-digit FY (2526) and YYYYMM is meeting month. The current-FY link on the landing page is wrapped in an Outlook safelinks redirect — unwrap via the url= query parameter to recover the real archive URL. Six meetings/year cadence (May, Jul, Sep, Nov, Jan, Mar).</t>
         </is>
       </c>
       <c r="J104" t="b">
@@ -6153,12 +6179,12 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Public Board Pack;Board Papers;Agenda and Papers</t>
+          <t>Agenda Pack Trust Board Public; Agenda Pack Trust Board in Public; Trust Board Agenda Pack</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+          <t>Confidential; Part B; Private; Minutes only; Annual Report only</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -6168,12 +6194,12 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>broken</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>Validator classification: broken.</t>
+          <t>24 in-window meetings found via doclibrary-rcht subdomain year-archive .aspx pages. Two largest packs March 2026 (12MB) and May 2026 (23MB) both contain clean BAF sections (locator scores 599 + 537).</t>
         </is>
       </c>
     </row>
@@ -9117,16 +9143,42 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>https://www.mft.nhs.uk/about-us/board-of-directors/</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
-      <c r="L159" t="inlineStr"/>
-      <c r="M159" t="inlineStr"/>
-      <c r="N159" t="inlineStr"/>
-      <c r="O159" t="inlineStr"/>
+          <t>https://mft.nhs.uk/the-trust/the-board/board-meetings/</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Strategy: landing has a year-selector dropdown; each meeting has its OWN page at /board-meetings/{month}-{year}/ (lowercase month, hyphen-separated, eg /board-meetings/november-2025/, /board-meetings/may-2026/). Each meeting page contains 1-2 PDFs labelled 'Download board paper' / 'Download agenda'. Brute-force enumeration of {month}-{year} slugs across the 24-month window finds ~13 valid meeting pages. Old DB URL /about-us/board-of-directors/ exists but redirects to a single old (Jan 2021) meeting page — wrong. WARNING: landing page also has a Google Translate language selector — do not click that thinking it's the year dropdown.</t>
+        </is>
+      </c>
+      <c r="J159" t="b">
+        <v>0</v>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Download board paper; board paper; agenda</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>Confidential; Part 2; Private; Minutes only</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>13 in-window meetings via brute-force /board-meetings/{month-year}/ probe. May 2026 and March 2026 packs (15MB + 11MB) both have detectable BAF sections.</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -9662,13 +9714,39 @@
           <t>https://www.mse.nhs.uk/board-meetings/</t>
         </is>
       </c>
-      <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
-      <c r="K169" t="inlineStr"/>
-      <c r="L169" t="inlineStr"/>
-      <c r="M169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
-      <c r="O169" t="inlineStr"/>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Strategy: landing lists year folders ('Board papers 2020', 'Board papers 2025', etc) but each year link is a share-my-box embedded folder at /board-meetings?smbfolder={NNN}. The share-my-box folder is JS-rendered — direct static fetch returns 0 PDFs. Requires Playwright with networkidle wait; year-tab interactive click reveals the month's PDFs. Found 1 in-window meeting (Feb 2026, 14.3MB pack) via interactive_dom strategy in the risk-tracker discoverer; gallery may show more on a longer wait.</t>
+        </is>
+      </c>
+      <c r="J169" t="b">
+        <v>1</v>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Board of Directors meeting in public papers; agenda and papers; combined papers</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>Confidential; Part 2; Private; Minutes only</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>needs_playwright</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>Year archives are share-my-box JS galleries. Playwright + year-tab click required; one Feb 2026 pack recovered (BAF score 236).</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -10250,16 +10328,42 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>https://www.alderhey.nhs.uk/about-us/trust-board/</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr"/>
-      <c r="J180" t="inlineStr"/>
-      <c r="K180" t="inlineStr"/>
-      <c r="L180" t="inlineStr"/>
-      <c r="M180" t="inlineStr"/>
-      <c r="N180" t="inlineStr"/>
-      <c r="O180" t="inlineStr"/>
+          <t>https://www.alderhey.nhs.uk/publications_type/board-papers/</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Strategy: WordPress publications-type taxonomy archive. Each meeting is a card linking to a wrapper page at /about/publications/trust-board-meeting-{ordinal-day}-{month}-{year}/. The wrapper page embeds the PDF hosted under /wp-content/uploads/{YYYY}/{MM}/. IMPORTANT: upload-month != meeting-month — PDFs are uploaded 1-3 months after the meeting they document, so do not date-mine from the URL path; use the wrapper slug for the meeting date. Board meets 11 times a year (typically first Thursday of each month except August). Filename patterns shifted in 2024: older 'Trust-Board-Meeting-{Xth}-{month}-{year}.pdf', newer 'Agenda-Documentation-Trust-Board-P1-{d.m.yy}-Website-Version.pdf'. Always follow the wrapper to the actual PDF link rather than guessing filenames. Alternate URL with the same content: /about/publications/?type=board-papers&amp;range=all (filtered view). Old DB URL /about-us/trust-board/ (note the '-us') exists but is a stub that doesn't link to the archive.</t>
+        </is>
+      </c>
+      <c r="J180" t="b">
+        <v>0</v>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Agenda Documentation Trust Board Public; Trust Board Meeting; P1 Website Version</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>P2; Private; Confidential; Annexes only; declarations of interest</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>WP taxonomy archive lists 115 publications filtered to Board papers. 13 meeting wrappers confirmed in 2025-26. Static HTML, no JS rendering required.</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -11683,13 +11787,39 @@
           <t>https://www.swast.nhs.uk/our-board/board-meeting-schedule-and-public-papers</t>
         </is>
       </c>
-      <c r="I206" t="inlineStr"/>
-      <c r="J206" t="inlineStr"/>
-      <c r="K206" t="inlineStr"/>
-      <c r="L206" t="inlineStr"/>
-      <c r="M206" t="inlineStr"/>
-      <c r="N206" t="inlineStr"/>
-      <c r="O206" t="inlineStr"/>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Strategy: DB URL /our-board/board-meeting-schedule-and-public-papers is JS-rendered (SPA shell, no PDF links in static DOM). The plain path WITHOUT /our-board/ — https://www.swast.nhs.uk/board-meeting-schedule-and-public-papers — is a static HTML page with all dated board pack PDFs ('Board in Public' / 'Board in Public Pack' titles). 12 in-window meetings found. Risk-tracker's follow_subpage strategy hits this correctly.</t>
+        </is>
+      </c>
+      <c r="J206" t="b">
+        <v>0</v>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Board in Public; Board in Public Pack</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>Confidential; Part 2; Private; Minutes only; Annual Report</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>Real archive at /board-meeting-schedule-and-public-papers (drop /our-board/ prefix). May 2026 and March 2026 packs (15MB + 10MB) both have BAF sections — scores 1299 and 680 are the cleanest BAFs in the entire pilot.</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">

--- a/trust_urls.xlsx
+++ b/trust_urls.xlsx
@@ -604,13 +604,39 @@
           <t>https://www.sussexcommunity.nhs.uk/about-us/how-we-are-run/board-of-directors/board-meetings-and-papers</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Pattern A + B. The landing page loads fine (DB 'broken' flag was a transient health-check failure / WebFetch socket drop; confirmed live via Playwright). It surfaces the latest meeting's papers as direct document links on the landing page itself (e.g. 'View the 28 May 2026 Board papers' -&gt; /documents/461-board-paper-28-may-2026/file), with a 'View previous Board meeting papers' child link to /board-of-directors/board-meetings-and-papers/board-papers which lists the rolling last-12-months archive (each meeting has its own /board-papers/board-paper-DD-month-YYYY child page). Board meets in public every other month. Crawler should take the latest dated document links on landing, then follow the 'board-papers' archive child for prior meetings. Documents are served via /documents/{id}-...{slug}/file rather than .pdf extensions.</t>
+        </is>
+      </c>
+      <c r="J3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Board paper DD month YYYY;View the ... Board papers;Strategic Improvement Report</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Board and Executive Team;Minutes only;Governors</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Live page links to the 28 May 2026 Board papers PDF plus a 'previous Board meeting papers' archive; board meets in public bi-monthly.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -751,13 +777,39 @@
           <t>https://www.qvh.nhs.uk/about-us/board-of-directors/meetings-in-public/</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Pattern D (JS-rendered). The page is correct and current but presents 'Meeting papers' and 'Meeting minutes' as JavaScript dropdown/accordion menus listing each meeting by date (April 2014 through May 2026 confirmed). Static WebFetch sees the dropdown labels but not the underlying PDF hrefs, so a crawler must render JS (Playwright) to expand the 'Meeting papers' selector and harvest the dated PDF links. QVH board meets first Thursday on alternate months. Most recent papers: 14 May 2026, prior 12 March 2026. Filter to 'Meeting papers' (the agenda+papers pack) and skip the separate 'Meeting minutes' dropdown.</t>
+        </is>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Meeting papers: DD Month YYYY;Board of Directors meeting papers</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Meeting minutes;Minutes only</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Confirmed dated meeting papers in a JS dropdown spanning 2014-May 2026 (latest 14 May 2026, next 2 July 2026).</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -800,13 +852,39 @@
           <t>https://www.ashfordstpeters.nhs.uk/meetings</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Pattern D (JS-rendered): a static fetch of /meetings returns a near-empty body (0 chars) because the meeting timetable and links are injected client-side; under Playwright the rendered page (location.host www.ashfordstpeters.nhs.uk, ~4.6k chars) shows the next/upcoming Public Board Meeting timetable and a 'Download the agenda and supporting documentation' link that points to a per-meeting sub-page at /board-meetings/{id}-trust-board-{date} (e.g. /board-meetings/3617-trust-board-3rd-june-2026). That per-meeting sub-page is where the dated board pack lives: ~37 individually-numbered PDFs (Agenda, Paper 1.3 Minutes, Paper 1.6 CEO Report, Performance, Finance, BAF, etc.) hosted on the sibling domain ashfordstpeters.info under /images/board-papers/{YYYY-MM-DD}/. A crawler must JS-render /meetings, follow the current per-meeting link (and the 'Past Meetings' index at /board-meetings for prior dates), then harvest the dated PDFs from ashfordstpeters.info; the dedicated /about-us/trust-executive/board-papers page is an alternative entry. Static fetch misses the entire timetable and every PDF link.</t>
+        </is>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>ashfordstpeters.info/images/board-papers/{YYYY-MM-DD}/;Agenda-{Mon}-{YYYY}.pdf;Paper{N}-{n}-{Title}-{Mon}-{YYYY}.pdf;/board-meetings/{id}-trust-board-{ordinal}-{month}-{year}</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>UnpaidCarersSupport;register-of-interests;board-member-expenses;#reciteme;communityday;annual-members-meeting</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Playwright reached the 03 June 2026 per-meeting sub-page exposing ~37 dated 2026 board-pack PDFs on the ashfordstpeters.info document domain.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -849,13 +927,39 @@
           <t>https://www.surreyandsussex.nhs.uk/about-us/our-board/board-papers</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Pattern B: the landing page lists year-archive links (/board-papers/2026, /board-papers/2025, etc.) rather than packs directly; a crawler must follow the year link, where each public board meeting (5 Feb, 2 Apr, 4 Jun 2026; 6 Feb, 3 Apr, 5 Jun, 7 Aug, 2 Oct, 4 Dec 2025) is exploded into many individual document PDFs (agenda numbered 00/0.0, plus separate minutes, BAF, committee key-issues, IPR, etc.) served as static HTML via /download_file/view/{ID}/{suffix} links. There is no single combined pack PDF; the agenda PDF is the entry point and the date is in the link text not the URL. Occasional extraordinary meetings appear (e.g. 20 Feb 2025). All static, no JS.</t>
+        </is>
+      </c>
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>/board-papers/{year};/download_file/view/{id}/{suffix};agenda link text begins 00 or 0.0 with the meeting date;Public Board</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>committee;key issues;minutes;extraordinary;register of interests;patient story</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2026 and 2025 year-archive pages each list multiple dated public board meetings with agenda and paper PDFs as static download_file links.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -898,13 +1002,39 @@
           <t>https://www.ekhuft.nhs.uk/about-us/board-of-directors/</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Pattern C (per-meeting sub-pages on landing). DB 'broken' flag was a transient health-check failure; page loads fine. The Board of Directors landing page lists each public Board meeting by date, each expanding to a full meeting pack plus individual papers (agenda, standing items, patient story, regulatory/governance, quality/safety). Confirmed meetings: 4 June 2026 (full meeting pack), 4 December 2025, 9 October 2025, 31 July 2025, 5 June 2025, plus 2024 dates. Crawler should pick each meeting's combined/full meeting pack PDF; older papers are by email request only. This is the Trust Board (single board), no ICP/cluster ambiguity.</t>
+        </is>
+      </c>
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>full meeting pack;Agenda and papers;Board of Directors DD Month YYYY</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Council of Governors;FOI;Minutes only</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Confirmed per-meeting packs for 4 June 2026, Dec 2025, Oct 2025, Jul 2025 and earlier on the Board of Directors page.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -944,40 +1074,40 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.mtw.nhs.uk/about-us/trust-board/board-meetings-and-papers/</t>
+          <t>https://www.mtw.nhs.uk/board-meetings-and-papers</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Strategy: /about-us/trust-board/board-meetings-and-papers/ is the correct page (Google indexes it as 'Board meetings and papers'), but the site's WAF returns 404 to non-browser fetchers. Pattern E anti-bot — fetch with a real browser / Playwright; do not treat the 404 as a dead URL.</t>
+          <t>Pattern A + F (wrong-url-fixed). The old DB URL https://www.mtw.nhs.uk/about-us/trust-board/board-meetings-and-papers/ now returns a hard 404 (confirmed in a real browser) because the site migrated to a new VerseOne CMS with a flat URL scheme; the board now lives at /board and the papers at /board-meetings-and-papers (no trailing slash, not under /about-us/). The new landing page lists monthly 'Board papers MONTH YYYY' combined packs as direct .pdf downloads right on the page (Pattern A), e.g. April 2026, January 2026, and the full 2024-2025 run, plus extraordinary meetings. PDFs are served via /download/board-papers-month-yyyypdf.pdf?ver=...&amp;doc=... Crawler should take the topmost dated 'Board papers {month} {year}' link as the latest pack. Note duplicate listings (two copies of some 2024 months) appear in the page DOM.</t>
         </is>
       </c>
       <c r="J10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Boardbook;Board papers</t>
+          <t>Board papers MONTH YYYY [pdf];Board papers extraordinary meeting</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+          <t>Minutes only;AGM;Part 2;Boardbook (old path)</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>needs_playwright</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>WAF returns 404 to bots; Google confirms URL is the live 'Board meetings and papers' page.</t>
+          <t>New /board-meetings-and-papers page lists monthly combined Board papers PDFs incl April 2026 and January 2026 plus full 2024-25 history; old /about-us/trust-board/ path is dead (404).</t>
         </is>
       </c>
     </row>
@@ -1214,16 +1344,42 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.kmpt.nhs.uk/about-us/trust-board/</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+          <t>https://www.kentmedwaymentalhealth.nhs.uk/about-us/trust-board/board-meetings/</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Pattern C (per-meeting sub-pages). The org has rebranded to Kent and Medway Mental Health NHS Trust and the domain kmpt.nhs.uk now redirects to kentmedwaymentalhealth.nhs.uk. The old DB url (/about-us/trust-board/) is the board landing page with no papers; its one-click child /about-us/trust-board/board-meetings/ lists each Board meeting as a dated sub-page (e.g. 'Board Meeting Thursday 28th May 2026' -&gt; /about-us/trust-board/board-meetings/board-28-may-2026/). Each sub-page has a Downloads section containing a single combined 'Public Board Meeting Pack DD.MM.YYYY' PDF (e.g. /media/l2yjpajs/public-board-meeting-pack-28052026-v1.pdf). Crawler: load this landing, follow the dated board-* sub-page links, then grab the public board meeting pack PDF from the meeting page.</t>
+        </is>
+      </c>
+      <c r="J14" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Public Board Meeting Pack;Board Meeting [date]</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Council of Governors;Committee;Minutes only;AGM</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>board-meetings page lists 2025 and 2026 dated meeting sub-pages; confirmed the 28 May 2026 sub-page links a combined Public Board Meeting Pack PDF.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1263,16 +1419,42 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.uhsussex.nhs.uk/resources/public-board-papers-10-november-2022/</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
+          <t>https://www.uhsussex.nhs.uk/about/board/board-meetings/</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Pattern C/F (wrong-url-fixed -&gt; per-meeting sub-pages). Old DB url was a single stale meeting page (public-board-papers-10-november-2022) with only one 2022 PDF and no navigation. New url /about/board/board-meetings/ is the live board meetings archive listing each meeting chronologically as a /resources/...board-papers... sub-page (e.g. 'Trust public board papers: 31 March 2026' -&gt; /resources/trust-public-board-papers-31-march-2026/). Each resource sub-page holds the combined public board papers PDF (also directly under /wp-content/uploads/YYYY/MM/...PAPERS.pdf). Skip the separate 'Questions and Answers' resource pages. Crawler: load board-meetings, follow the dated 'Trust (public) board papers' resource links, fetch the combined papers PDF.</t>
+        </is>
+      </c>
+      <c r="J15" t="b">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Trust public board papers;Public Board Agenda;PAPERS</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Questions and Answers;Q&amp;A;Western Sussex Hospitals Board Papers 2018-2021;Council of Governors</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>board-meetings archive lists 14 May 2026, 31 March 2026 and 5 February 2026 meetings; confirmed direct 2026 papers PDFs under /wp-content/uploads/2026/.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1459,12 +1641,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.sfh-tr.nhs.uk/about-us/board-of-directors/</t>
+          <t>https://www.sfh-tr.nhs.uk/about-us/board-of-directors/board-meetings/</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Strategy: landing shows a weak board-papers signal to a static parser (few dated PDFs found). Papers are likely present but loaded via JS or one click into a 'papers'/'meetings' sub-page. Confirm by following the board-papers / meetings link; prefer the main combined pack. Pattern A/C — review on next pass.</t>
+          <t>Pattern A (dated PDFs on landing) / F (wrong-url-fixed). Old DB url (/about-us/board-of-directors/) is just the board membership page; its one-click child /about-us/board-of-directors/board-meetings/ lists the combined bi-monthly 'Board Meeting Papers - [Month Year]' PDFs directly on the page (hosted under /media/...). No per-meeting sub-pages or year archives - all current-year and prior PDFs are inline. Crawler: load this page and harvest the dated 'Board Meeting Papers - Month Year' PDF links directly.</t>
         </is>
       </c>
       <c r="J19" t="b">
@@ -1472,27 +1654,27 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Board Papers;Agenda and Papers;Public Board Pack</t>
+          <t>Board Meeting Papers - [Month Year];Board of Directors</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+          <t>Minutes only;Council of Governors;Committee</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>papers_partial</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Validator (static) weak signal: dated_pdfs=0, year_archives=0, meeting_subpages=1; review.</t>
+          <t>page lists direct combined board-meeting-papers PDFs through June 2026 (e.g. 0-board-meeting-papers-v3-june-2026.pdf, april-2026, february-2026).</t>
         </is>
       </c>
     </row>
@@ -1929,13 +2111,39 @@
           <t>https://www.nuh.nhs.uk/board-and-board-papers/</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Pattern B+D (year archives inside a JS/AJAX media browser - needs Playwright). The landing /board-and-board-papers/ shows upcoming meeting dates and links to /board-papers/ which is a VerseOne 'Media browser': a left-hand folder tree by fiscal year (2012/13 ... 2025/26, 2026/27). Clicking a year folder (e.g. /board-papers?media_folder=1466&amp;root_folder=2026/27) reveals dated meeting subfolders (e.g. '1. Thursday 14th May 2026', media_folder=1467), and the meeting folder finally lists the actual PDFs. Static WebFetch only sees the folder shell, not the documents, so Playwright (wait for networkidle, click into year then meeting folder) is required to reach the PDFs. Store the /board-and-board-papers/ landing; crawler should hop to /board-papers/ then drill year -&gt; meeting folder.</t>
+        </is>
+      </c>
+      <c r="J28" t="b">
+        <v>1</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Trust Board;agenda;papers;[Month Year] folder</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Council of Governors;Committee;Minutes only;older fiscal-year folders</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>needs_playwright</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Playwright confirmed live 2025/26 and 2026/27 folders; drilled into '1. Thursday 14th May 2026' meeting folder showing 'Total results: 2' documents, but PDFs only render via the AJAX media browser.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2151,13 +2359,39 @@
           <t>https://www.hacw.nhs.uk/board-papers/</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Pattern A with a major quirk: dated meetings are listed directly on the landing page (Jan/Mar/May 2026; Jan/Mar/May/Jul/Sep/Nov 2025) but the papers are distributed as ZIP archives, not PDFs, via relative /download/...zip?ver=&amp;doc= links that resolve against https://www.hacw.nhs.uk. Each row also has a per-meeting summary sub-page (e.g. /board-may-26) and YouTube recording links. A crawler should grab the ZIP (filenames embed the meeting month, e.g. trust-board-papers-may-2026.zip) and unpack it to reach the individual board-pack documents; there is no plain combined PDF on the site. Static HTML, no JS needed. Future dated meetings (Jul/Sep/Nov 2026) are listed without papers yet.</t>
+        </is>
+      </c>
+      <c r="J32" t="b">
+        <v>0</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>/download/trust-board-papers-{month}-{year}.zip;/download/...zip?ver={n}&amp;doc=docm...zip;summary sub-page /board-{mon}-{yy}</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>youtu.be;youtube.com;/board-;summary</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Landing page lists 2025 and 2026 board meetings each with a downloadable ZIP papers archive (e.g. trust-board-papers-may-2026.zip).</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2202,7 +2436,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Strategy: JS-rendered listing — static fetch returns a near-empty body, but Playwright (wait_until=networkidle) reaches dated PDFs such as 'Public Agenda', 'Public Information Pack' and 'Board Meetings in Common' for the current month. Pattern D.</t>
+          <t>Pattern D (JS-rendered listing): a static fetch returns a near-empty body, but under Playwright (location.host www.shropscommunityhealth.nhs.uk) the page renders a &lt;select name="bdts"&gt; 'Meeting dates' dropdown whose options span the current and past five years (e.g. December 2026, October 2026, August 2026, June 2026, May 2026, ... December 2025, AGM September 2025, ... April 2025). Selecting a month triggers a client-side swap that lists that meeting's dated PDFs; the default (most recent) selection currently shows the May 2026 set — '00 Public Agenda 14.05.2026', '01 Board Meetings in Common - 14.05.2026 - Combined papers' and '02 Public Information Pack 14.05.2026' — hosted at /content/doclib/{id}.pdf. A crawler must JS-render the page, enumerate the dropdown option values and, for each, capture the resulting /content/doclib/{id}.pdf links (the trust runs Board Meetings in Common, so packs are combined). Static fetch misses the dropdown and every PDF.</t>
         </is>
       </c>
       <c r="J33" t="b">
@@ -2210,27 +2444,27 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Public Information Pack;Public Agenda;Board Meetings in Common</t>
+          <t>/content/doclib/{id}.pdf;Public Agenda {DD.MM.YYYY};Board Meetings in Common - {DD.MM.YYYY} - Combined papers;Public Information Pack {DD.MM.YYYY};select[name=bdts] option values drive the listing</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+          <t>cookies;accessibility;Select meeting</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>needs_playwright</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Static body near-empty; Playwright reaches dated PDFs incl 'Public Information Pack 14.05.2026'.</t>
+          <t>Playwright rendered the meeting-date dropdown and the default May 2026 selection exposed three dated 14.05.2026 PDFs (Agenda, Combined papers, Information Pack).</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2555,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.swft.nhs.uk/meetings-and-events/board-meetings</t>
+          <t>https://www.swft.nhs.uk/about-us/publications/Board-of-Directors-papers-minutes</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Strategy: /meetings-and-events/board-meetings is an events calendar (next meeting shown, incl Joint Board with George Eliot). Actual papers are one click away at /about-us/publications/Board-of-Directors-papers-minutes. Pattern C; follow the publications link for dated packs and minutes.</t>
+          <t>Pattern B+F (wrong-url-fixed): old DB url /meetings-and-events/board-meetings only lists future dates ('No upcoming events') and links onward to the real archive at /about-us/publications/Board-of-Directors-papers-minutes, so point the crawler at the archive. The archive is organised by year tabs/sections (2026, 2025, 2024...). Within each year are per-meeting download links served via /download_file/{guid}/{n} (no readable extension) titled e.g. 'Public SWFT and GEH Boards Combined Meeting Pack - 07.10.2025' — take the single largest combined meeting-pack PDF per date. Quirk: South Warwickshire (SWFT) now meets as a JOINT board in common with George Eliot Hospital (GEH); the only public pack is the combined SWFT/GEH pack, so do not filter it out as a Joint board. Download URLs lack a .pdf suffix.</t>
         </is>
       </c>
       <c r="J35" t="b">
@@ -2334,27 +2568,27 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Board of Directors papers;Agenda and Papers</t>
+          <t>Combined Meeting Pack;Public SWFT and GEH Boards;Board of Directors papers;Meeting Pack</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+          <t>Minutes only;Council of Governors;Charitable Funds;AGM;future meeting dates</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>papers_partial</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Landing is a meetings calendar; papers at /about-us/publications/Board-of-Directors-papers-minutes (one click away).</t>
+          <t>Archive page lists a dated 2025 combined board pack (07.10.2025) plus year sections; 2026/27 joint board dates listed with packs to follow.</t>
         </is>
       </c>
     </row>
@@ -2396,12 +2630,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.uhnm.nhs.uk/about-us/our-board/</t>
+          <t>https://www.uhnm.nhs.uk/about-us/our-board/trust-board-papers/</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Strategy: landing /about-us/our-board/ is a governance overview, NOT the archive. Follow the 'Board papers' link on the page to /board-papers/ which uses a year-tab archive layout. WARNING: /board-papers/ also exposes FOI request responses mixed into the same listing — filter to 'Trust Board Part 1' / 'Part-1 Trust Board' to isolate genuine board packs. The follow_subpage + interactive_dom Python strategy handles this correctly in the risk-tracker discoverer.</t>
+          <t>Pattern A+F (wrong-url-fixed): old DB url /about-us/our-board/ is the board-membership page (no papers) and links to the dedicated /about-us/our-board/trust-board-papers/ page, which is the correct landing. That page lists individual dated public/Part 1 board-pack PDFs served from /media/{slug}/...pdf, one per meeting (e.g. 'Part 1 Trust Board 11 02 26', 'Public Trust Board 8th October 2025'). Take the Part 1 / Public / Open pack for each date. Quirk: naming is inconsistent (mix of 'Part 1', 'Open', 'Public', date formats dd-mm-yy and 'July 2025'); ignore Part 2 / confidential. Static WebFetch reaches the PDFs directly.</t>
         </is>
       </c>
       <c r="J36" t="b">
@@ -2409,27 +2643,27 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Trust Board Part 1; Part-1 Trust Board; Wednesday Trust Board</t>
+          <t>Trust Board Part 1;Public Trust Board;Trust Board Open;Public Board</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>FOI; Freedom of Information; DPIA; P&amp;O Services; Part 2; Confidential; Privacy Impact</t>
+          <t>Part 2;Confidential;Rules of Procedure;Minutes only;future dates without papers</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>papers_partial</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Landing is OK but is 1 click away from the archive at /board-papers/. Latest 2026 packs Feb (7.8MB, BAF score 624) and Apr (11.3MB) confirmed.</t>
+          <t>Trust-board-papers page lists multiple dated 2025 and 2026 board-pack PDFs (Jan 2025 through Apr 2026) directly downloadable.</t>
         </is>
       </c>
     </row>
@@ -2520,16 +2754,42 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.rjah.nhs.uk/about-us/board-of-directors/board-of-directors-meeting-dates</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
+          <t>https://www.rjah.nhs.uk/about-us/publications/trust-board-meeting-papers/</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Pattern B+F (wrong-url-fixed): old DB url /about-us/board-of-directors/board-of-directors-meeting-dates lists only future meeting dates with NO paper links. The correct archive is /about-us/publications/trust-board-meeting-papers/, a click-through index of academic-year sub-pages: /.../2025-2026-trust-board-meeting-papers/ and /.../2026-2027-trust-board-meeting-papers/. Each year sub-page lists per-meeting combined board packs as PDFs served from /media/{slug}/...pdf, named 'Board of Directors {dd.mm.yyyy}.pdf' or 'Board of Directors Public Meeting {date}.pdf' (single combined pack ~8-18MB; some dates split Part 1/Part 2 e.g. 02.07.2025 — grab both). Crawler must go landing -&gt; year sub-page -&gt; PDF (two clicks). Static WebFetch works.</t>
+        </is>
+      </c>
+      <c r="J38" t="b">
+        <v>0</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Board of Directors Public Meeting;Board of Directors;Public Meeting;combined board pack</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Council of Governors;Meeting Dates;Part 2;Annual Report;Minutes only</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>2025-2026 year sub-page lists seven dated combined board packs (07.05.2025 through 04.03.2026); 2026-2027 sub-page already created.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2747,7 +3007,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Strategy: /about/our-board/board-meetings/ is correct (papers posted before each meeting; previous meetings at /about-us/our-board/previous-board-meetings/; archive from Jan 2014). Site intermittently drops bot connections (ConnectionReset). Pattern C behind Pattern E anti-bot; retry / use a browser.</t>
+          <t>Pattern A+C: landing page lists the next upcoming meeting with its full board pack as a single PDF under /wp-content/uploads/{yyyy}/{mm}/PUBLIC-TRUST-BOARD-PACK...pdf or PUBLIC-TRUST-BOARD-PAPERS...pdf (e.g. 14.05.26, 15.01.26). It also lists 'Previous Board Meetings' as per-meeting sub-pages (Trust board meeting - May 2026, March 2026, Jan 2026, Nov 2025...) each carrying that meeting's pack, plus a 'Board meeting archive' link at /about/our-board/board-meetings/board-meeting-archive/. Take the single combined PUBLIC TRUST BOARD PACK/PAPERS PDF per date. Quirk: the /about/ path is canonical; the /about-us/ variant returns 404. Initial WebFetch hit a transient socket close but retry succeeded — not anti-bot.</t>
         </is>
       </c>
       <c r="J42" t="b">
@@ -2755,17 +3015,17 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Trust Board;board papers</t>
+          <t>PUBLIC TRUST BOARD PACK;PUBLIC TRUST BOARD PAPERS;Trust board meeting;board pack</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+          <t>Ask the Board;AGM;Annual General Meeting;template/change date;Minutes only</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -2775,7 +3035,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>URL confirmed correct (Google index); health-check ConnectionReset is transient anti-bot.</t>
+          <t>Landing shows 14 May 2026 board pack PDF plus a previous-meetings list spanning Jan 2025 to May 2026 and a board-meeting archive.</t>
         </is>
       </c>
     </row>
@@ -2817,16 +3077,42 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.dgft.nhs.uk/about-us/our-board/</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
+          <t>https://www.dgft.nhs.uk/about-our-trust/our-board/</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Pattern C/F. Landing 'Our Board' page is a profiles hub (validator saw only 1 stray PDF). From it follow the one-click child link 'Board Meetings' -&gt; https://www.dgft.nhs.uk/about-our-trust/our-board/board-meetings/ which lists current-year (2025/26 and 2026/27) public board meetings, each a directly linked dated PDF on the trust's own /wp-content/uploads/ path (e.g. 26-05-20_Board_pblc_papersV2-1.pdf). Crawler should grab the 'Public Board Agenda - DD Month YYYY' PDFs. Note: full packs for periods prior to 2025/26 are only available by emailing the Foundation Trust Office, so only ~current year is web-accessible. Static WebFetch reaches everything.</t>
+        </is>
+      </c>
+      <c r="J43" t="b">
+        <v>0</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Public Board Agenda;Board_pblc_papers;Public Board</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Council of Governors;Committee;Minutes only;prior to 2025/26 (email only)</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Confirmed dated public board agenda/papers PDFs for Jan, Mar and May 2026 on the org's own domain via the 'Board Meetings' child page.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2866,12 +3152,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.bwc.nhs.uk/board-of-directors/</t>
+          <t>https://www.bwc.nhs.uk/board-meetings-and-minutes</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Strategy: /board-of-directors/ is an overview hub; the dated agendas and papers are on the related 'Board meetings and minutes' page (linked from this page). Pattern C; follow that link for the per-meeting packs. Trust office: bwc.foundationtrustoffice@nhs.net.</t>
+          <t>Pattern A/F. Old URL https://www.bwc.nhs.uk/board-of-directors/ is only the board-member directory (validator saw no papers). Changed to the dedicated papers page https://www.bwc.nhs.uk/board-meetings-and-minutes which lists a single combined 'Board Meeting Pack - &lt;Month YYYY&gt;' PDF per meeting (bi-monthly: Jan, Mar, May, Jul, Sep, Nov), served from the trust's own /download/ path with ?ver=&amp;doc= query params. Crawler should take the largest 'Board Meeting Pack' link per month; ignore separate appendix/'Reading Room' files. Static WebFetch reaches the listing and PDFs.</t>
         </is>
       </c>
       <c r="J44" t="b">
@@ -2879,27 +3165,27 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Board meetings and minutes;agenda and papers</t>
+          <t>Board Meeting Pack;Public Board Meeting Pack;in Public</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+          <t>Reading Room;appendix;Minutes only;Council of Governors</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>papers_partial</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Landing is a board overview; papers on the linked 'Board meetings and minutes' page (one click away).</t>
+          <t>Confirmed combined public Board Meeting Pack PDFs for Jan, Mar and May 2026 (plus full 2025 set) on bwc.nhs.uk /download/ paths.</t>
         </is>
       </c>
     </row>
@@ -2944,13 +3230,39 @@
           <t>https://www.mpft.nhs.uk/about-us/board-papers/</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Pattern A: dated board-pack PDFs are linked directly on the landing page, grouped by year, as single combined Trust Board Papers documents (2026: 09 Apr, 12 Feb; 2025: 11 Dec, 09 Oct, 14 Aug, 12 Jun, 27 Mar, 30 Jan). The meeting date is in the link text (YYYY-MM-DD MPFT Trust Board Papers) but URLs are opaque /download_file/{uuid}/256 with no date in them. Some months also have a separate short Trust Board Summary Document alongside the full pack; prefer the larger combined Papers file. Static HTML, no JS required.</t>
+        </is>
+      </c>
+      <c r="J45" t="b">
+        <v>0</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>/download_file/{uuid}/256;link text 'YYYY-MM-DD MPFT Trust Board Papers';combined Trust Board Papers PDF</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Summary Document;summary</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Landing page directly lists combined Trust Board Papers PDFs for multiple 2025 and 2026 meetings via download_file links.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3044,7 +3356,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Strategy: correct page is /about/trust-management/bod/papers/ ('Papers from meetings of the Board of Directors'); the board packs load from an embedded online document store, so static fetch returns a near-empty body. Use Playwright (wait_until=networkidle) to reach the listing. Pattern D + F: old /about-us/board-papers/ 404'd; corrected 2026-05-29.</t>
+          <t>Pattern D. Current URL is the canonical official 'Papers from meetings of the Board of Directors' landing page (confirmed top hit on uhb.nhs.uk). It contains no inline PDFs; instead a single link 'View papers from meetings of the Board of Directors' points to a JS-rendered Nextcloud document store at https://docs.uhb.nhs.uk/index.php/s/prTEizKrRnYnjaD. Static WebFetch of that store renders 'No files in here' but exposes a 'Download all files (831.6 MB)' control, proving the file tree is populated but only via the JS Nextcloud client. A crawler must drive the doc store with Playwright (wait_until networkidle) to enumerate the dated meeting folders/PDFs. Note: shared-browser contention prevented a clean live folder enumeration this run, but presence of papers is confirmed by the bulk-download size.</t>
         </is>
       </c>
       <c r="J47" t="b">
@@ -3052,17 +3364,17 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Board of Directors;papers</t>
+          <t>Board of Directors;public;agenda and papers;papers pack</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+          <t>Council of Governors;Committee;Minutes only;private/confidential</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3072,7 +3384,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Old URL 404'd; correct papers page renders via embedded JS document store (Playwright needed).</t>
+          <t>Landing page confirmed canonical; papers live in a JS-rendered Nextcloud store (docs.uhb.nhs.uk) whose 831.6MB bulk-download confirms files present but requires Playwright to list.</t>
         </is>
       </c>
     </row>
@@ -3189,16 +3501,42 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.swbh.nhs.uk/about-us/trust-board/</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
+          <t>https://www.swbh.nhs.uk/our-trust/trust-board/</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Pattern B/C/F. Landing Trust Board hub (validator saw no papers) links one-click to 'Public Trust Board Papers' -&gt; https://www.swbh.nhs.uk/our-trust/trust-board/public-trust-board-papers/ which gives per-year archive links (2026, 2025, 2024). Each year page lists per-month meeting subpages (e.g. /trust-board-paper/may-2/) and each subpage carries ONE combined 'Agenda and papers' PDF on the trust's own /wp-content/uploads/ path (e.g. 26-05-20_BoardAGENDA_pblc_papers.pdf, ~25MB). Crawler: landing -&gt; Public Trust Board Papers -&gt; current year -&gt; month subpage -&gt; take the single large 'BoardAGENDA_pblc_papers' PDF. Static WebFetch reaches all levels.</t>
+        </is>
+      </c>
+      <c r="J49" t="b">
+        <v>0</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>BoardAGENDA_pblc_papers;Public Trust Board Papers;agenda and papers</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Board Meeting Dates;Board Sub-Committees;Minutes only;Council of Governors</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Confirmed a combined public board agenda+papers PDF for the 20 May 2026 meeting via year(2026)-&gt;month subpage navigation on swbh.nhs.uk.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3437,16 +3775,42 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.bhamcommunity.nhs.uk/our-board/</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
+          <t>https://www.bhamcommunity.nhs.uk/our-board-papers</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Pattern A (dated PDFs on landing) + F (wrong-url-fixed). Old DB url /our-board/ is only a board overview page that links onward to /our-board-papers; the validator saw no papers because they were one click away. The new url /our-board-papers lists direct combined PDF packs grouped by year, each labelled with month/year, e.g. 'BCHC Public Board Papers Pack 4 June 2026'. Crawler should take the most recent dated 'public board papers pack' PDF under /download/. Static WebFetch reaches it fine.</t>
+        </is>
+      </c>
+      <c r="J53" t="b">
+        <v>0</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Public Board Papers Pack;Board Meeting Papers;BCHC Public Board</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Minutes only;Committee;AGM</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Confirmed multiple dated combined board packs including a 42MB 'BCHC Public Board Papers Pack 4 June 2026' and packs through Feb 2025.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3561,16 +3925,42 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.kingstonhospital.nhs.uk/about-us/board-papers/</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
+          <t>https://www.kingstonandrichmond.nhs.uk/about-us/trust-board/board-meetings</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Pattern A/B + F (wrong-url-fixed; org renamed). Kingston Hospital NHS FT merged into Kingston and Richmond NHS Foundation Trust (KRFT), and the old kingstonhospital.nhs.uk board page now redirects to the new domain. New board-meetings page lists 2026 meeting dates and the current combined 'KRFT Trust Board Part 1' pack as a force-download file; older packs are under a linked 'Board paper archive' sub-page (/about-us/trust-board/board-meetings/board-paper-archive). Crawler should take the latest 'Trust Board Part 1' pack (the public part), skipping Part 2/private. Static WebFetch reaches it.</t>
+        </is>
+      </c>
+      <c r="J55" t="b">
+        <v>0</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>KRFT Trust Board Part 1;Trust Board Part 1;Board papers</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Part 2;Private;Confidential;Minutes only</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Confirmed 2026 board dates and a downloadable '2026-05-07 KRFT Trust Board Part 1 - May 2026' pack on the new Kingston and Richmond domain.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3809,13 +4199,39 @@
           <t>https://www.kch.nhs.uk/about/how-we-are-organised/board-of-directors/minutes-and-agendas/</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Pattern A, ideal case: single combined 'BoD Agenda and Papers' board-pack PDFs are linked directly on the landing page, one per public meeting, with the meeting date in both the link text and the WordPress /wp-content/uploads/{YYYY}/{MM}/ URL path and filename (2026: 14 May, 12 Mar, 15 Jan; 2025: 13 Nov, 11 Sep, 17 Jul, 08 May, 13 Mar, 16 Jan). Filenames vary (KCH-PUBLIC-Board-meeting-pack, ...meeting-pack, ...Board-Bundle) and are large (5-19 MB). Static HTML, no JS. Crawl just the PUBLIC Board packs and ignore any committee/private items.</t>
+        </is>
+      </c>
+      <c r="J60" t="b">
+        <v>0</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>/wp-content/uploads/{YYYY}/{MM}/...Board...pack...pdf;PUBLIC Board meeting pack;Board Bundle;BoD Agenda and Papers {date}</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>committee;private;confidential</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Landing page directly links combined public Board of Directors agenda+papers PDFs for every 2025 and 2026 meeting with dates in the URL.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3855,12 +4271,12 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.epsom-sthelier.nhs.uk/our-board</t>
+          <t>https://www.epsom-sthelier.nhs.uk/board-papers-and-agendas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Strategy: /our-board is the board hub; follow the 'Board papers and agendas' link to dated meeting papers. Static fetch works for the hub. Pattern F: old /about-us/board-papers/ went stale and resolved to the generic About-us page; corrected to /our-board 2026-05-29.</t>
+          <t>Pattern A (dated PDFs on landing) + F (wrong-url-fixed). Old DB url /our-board is just a board overview; the actual papers live at /board-papers-and-agendas. Epsom and St Helier now boards jointly as the 'gesh Group' (with Epsom and St Helier + St George's), so recent packs are titled 'gesh Group Board (public)' with a month/year; this group board is the trust's public board and is the only board pack published here, so it is the correct target. Crawler should take the most recent dated 'gesh Group Board (public)' PDF under /download/. Older years are in year-based archive folders. Static WebFetch reaches it.</t>
         </is>
       </c>
       <c r="J61" t="b">
@@ -3868,27 +4284,27 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Board papers and agendas;Public Board</t>
+          <t>gesh Group Board (public);Group Board Public;Group Board Agenda (public)</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+          <t>Private;Part 2;Minutes only;Committee</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>papers_partial</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Old board-papers URL resolved to generic about-us; /our-board hub links to 'Board papers and agendas'.</t>
+          <t>Confirmed dated public group board packs from 1 May 2025 through 8 May 2026 as direct PDF downloads.</t>
         </is>
       </c>
     </row>
@@ -3933,13 +4349,39 @@
           <t>https://www.moorfields.nhs.uk/about-us/our-organisation/corporate-publications/board-reports</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Pattern B: the landing page is a hub of static text links to per-year archive pages (Board papers 2026, 2025, 2024 ...) at /board-reports/board-papers-&lt;year&gt;. Each year page lists one combined Part I public board meeting pack PDF per meeting, by month, directly linked (no per-meeting sub-pages, no JavaScript needed). To reach the latest 2025-26 packs a crawler must follow 'Board papers 2026' / 'Board papers 2025' from the landing hub then take the dated 'Combined board meeting pack' PDFs. Quirk: pack PDFs live under /mediaLocal/&lt;hash&gt;/ with date-coded filenames (e.g. 260604-tb-part-i-...) so filenames are unstable; the Moorfields Eye Hospital Trust Board is the only board listed (no committees/joint meetings to filter out).</t>
+        </is>
+      </c>
+      <c r="J62" t="b">
+        <v>0</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Combined board meeting pack;tb-part-i;tb-part-1;meeting-pack;meeting-bundle;agenda-bundle;/mediaLocal/;Part I</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Part II;part-ii;confidential;council-of-governors;committee;terms-of-reference</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>2026 archive lists combined board packs for Feb/Mar/Jun 2026 and the 2025 archive lists Jan/Mar/Jun/Jul/Oct/Nov 2025, all as directly-linked PDFs.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3979,16 +4421,42 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.royalmarsden.nhs.uk/board-meetings/</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
+          <t>https://www.royalmarsden.nhs.uk/about-royal-marsden/governance/board-meetings/board-papers</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Pattern A (dated PDFs on landing) + E (anti-bot 403) + F (wrong-url-fixed). Old DB url /board-meetings/ no longer resolves to the listing; the canonical board-papers page is /about-royal-marsden/governance/board-meetings/board-papers (the /how-we-run-ourselves/ path redirects here). Static WebFetch returns HTTP 403 (anti-bot), so a headless browser is required. The page lists one combined PDF per meeting, labelled by month/year ('Public Board papers' / 'Public Board Pack'), hosted on the trust's S3 bucket (rm-live-drupal-files.s3...amazonaws.com). Crawler should take the most recent dated public board pack PDF.</t>
+        </is>
+      </c>
+      <c r="J63" t="b">
+        <v>1</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Public Board papers;Public Board Pack;Public Board</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Council of Governors;COG;Private;Minutes only</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Via Playwright confirmed dated public board packs incl. 'Public Board papers - 19 Nov 2025' and 'Public Board Pack 26.03.2025'; 2026 meeting dates (Mar/Jul/Sep/Nov 2026) also scheduled.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4028,16 +4496,42 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.hrch.nhs.uk/</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
+          <t>https://www.kingstonandrichmond.nhs.uk/about-us/trust-board/board-meetings</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Pattern F (wrong-url-fixed) + C (per-meeting/dated combined PDFs). Old url www.hrch.nhs.uk now 301-redirects to www.kingstonandrichmond.nhs.uk because Hounslow and Richmond Community Healthcare NHS Trust merged into Kingston Hospital NHS FT to form Kingston and Richmond NHS Foundation Trust on 1 November 2024 (note: Hounslow community services moved to West London NHS Trust). The successor board is the Kingston and Richmond Trust Board. From the landing page the crawler finds the latest combined pack as a dated download link (e.g. '2026-05-07 KRFT Trust Board Part 1 - May 2026' -&gt; /download_file/force/&lt;uuid&gt;/&lt;n&gt;); older meetings live behind the 'Board paper archive' one-click child at /about-us/trust-board/board-meetings/board-paper-archive. Prefer the largest combined 'Part 1'/public pack PDF per meeting; PDFs are served via opaque /download_file/force/ UUID URLs rather than dated filenames.</t>
+        </is>
+      </c>
+      <c r="J64" t="b">
+        <v>0</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>KRFT Trust Board;Trust Board Part 1;Board meeting &lt;Month Year&gt;;Kingston and Richmond</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Council of Governors;Part 2;Hounslow community;committee</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Landing page links a dated May 2026 combined Trust Board Part 1 pack plus a 'Board paper archive' child page on the org's own (successor) domain.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4153,7 +4647,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Strategy: 'Board of Directors Meetings' page renders via JS (static body near-empty). Even rendered, the landing shows no direct PDFs — papers are reached by selecting a year / opening a per-meeting entry. Use Playwright and drill into the meeting list. Pattern C/D.</t>
+          <t>Pattern C/D (JS-rendered landing + year-archive drill-down): a static fetch returns a near-empty body and even when JS-rendered (location.host www.bradfordhospitals.nhs.uk) the /our-trust/bod-meetings/ landing has NO direct PDFs — it only lists upcoming meeting dates and a column of per-year archive links 'Previous meetings - {YEAR}' at /our-trust/bod-meetings/previous-meetings-{YEAR}/ (2017 through 2026). The dated board packs live one level down on those year sub-pages: e.g. /previous-meetings-2026/ lists '29 January meeting - Papers', '29 January meeting - Confirmed minutes', '31 March meeting - Papers' and '21 May meeting - Papers', each a WordPress-uploaded PDF under /wp-content/uploads/{YYYY}/{MM}/ (e.g. Boardpack-public-board-29.1.26.pdf, Public-BOD-boardbook-21.5.26.pdf). A crawler must JS-render the landing, follow the current-year 'Previous meetings - {YEAR}' link, then harvest the dated /wp-content/uploads PDFs. Static fetch misses both the year-archive links and all PDFs.</t>
         </is>
       </c>
       <c r="J66" t="b">
@@ -4161,27 +4655,27 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Board of Directors;Agenda and Papers</t>
+          <t>/our-trust/bod-meetings/previous-meetings-{YYYY}/;/wp-content/uploads/{YYYY}/{MM}/*.pdf;Boardpack-public-board-{DD.M.YY}.pdf;Public-BOD-boardbook-{DD.M.YY}.pdf;open-BOD-boardbook-{DD.M.YY}.pdf;confirmed-BOD-open-minutes-{DD.MM.YY}.pdf</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+          <t>annual-members-meeting;Select Language;#content</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>needs_playwright</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Renders via JS; landing has no direct PDFs, papers nested behind year/meeting selection.</t>
+          <t>Playwright drilled into /previous-meetings-2026/ and confirmed dated 2026 board-pack PDFs for the 29 Jan, 31 Mar and 21 May meetings (papers plus confirmed minutes).</t>
         </is>
       </c>
     </row>
@@ -4226,13 +4720,39 @@
           <t>https://www.yorkhospitals.nhs.uk/about-us/board-of-directors/board-of-directors-meetings/</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Pattern C (per-meeting dated agenda/papers links) reached via one obvious child link. The current landing page itself is mostly schedule text (validator saw no papers), but it links to the child page /about-us/board-of-directors/board-of-directors-papers/ which lists every Board of Directors meeting by date with a direct combined agenda+papers download per meeting (e.g. '30 April 2025', '28 January 2026', '25 March 2026', '29 April 2026', '27 May 2026'). Each link is an opaque /seecmsfile/?id=&lt;n&gt; download serving the combined pack PDF. Crawler should follow the 'board-of-directors-papers' child then take the dated combined pack link; future meetings show 'Agenda (available nearer the time)' with no link until published.</t>
+        </is>
+      </c>
+      <c r="J67" t="b">
+        <v>0</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Board of Directors Agendas and Papers;&lt;DD Month YYYY&gt;;Agenda and papers;York and Scarborough</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Council of Governors;Quality Committee;available nearer the time;Late paper</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Child page board-of-directors-papers lists 2025/26 and 2026/27 dated combined agenda+papers downloads (seecmsfile ids) on the org's own domain.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4324,13 +4844,39 @@
           <t>https://www.airedale-trust.nhs.uk/about-us/our-board-and-leadership/</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Pattern D (JS-rendered + WAF): the current leadership URL IS the board-papers location, but a static fetch returns empty because (a) the page is JS-rendered and (b) it sits behind a Sucuri WAF that intermittently serves a '.well-known/sgcaptcha' Robot Challenge Screen blocking headless Chromium — Playwright must retry until the challenge clears (it did, location.host www.airedale-trust.nhs.uk, ~25k chars). Once rendered, a 'Trust Board meetings' accordion exposes per-YEAR tabs (#tab-2026, #tab-2025 ... #tab-2018); under the 2026 tab the dated combined board packs are linked directly as single PDFs — '06 May 2026 Public Board of Directors papers', '04 March 2026 ...', '14 January 2026 ...' — hosted as WordPress uploads at /wp-content/uploads/{YYYY}/{MM}/, with 2025 packs (05.11.25, 3.9.25, 30-05-25, 2 April 2025, 5 February 2025) under the 2025 tab. A crawler must JS-render the page (handling the WAF challenge), open each year tab, and harvest the /wp-content/uploads PDFs. Static fetch misses the WAF, the year tabs and every PDF.</t>
+        </is>
+      </c>
+      <c r="J69" t="b">
+        <v>1</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>#tab-{YYYY} year tabs in the 'Trust Board meetings' accordion;/wp-content/uploads/{YYYY}/{MM}/*.pdf;{DD}-{Month}-{YYYY}-Public-Board-of-Directors...papers.pdf;Combined-...papers-Board-of-Directors-{DD-MM-YY}...pdf;Combined-BoD-PUBLIC-agenda_papers-{DD.M.YY}...pdf</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>ToR;Audit-Risk-Committee;declaration-of-interests;safelinks.protection.outlook.com;code-of-governance;sgcaptcha;Annual-Report-and-Accounts</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>After the Sucuri challenge cleared, Playwright rendered year tabs and confirmed dated 2026 combined board-pack PDFs (06 May, 04 March, 14 January 2026) plus 2025 packs as WordPress uploads.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4373,13 +4919,39 @@
           <t>https://www.sheffieldchildrens.nhs.uk/about-us/board-of-directors/</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Patterns C+D: the board papers area is rendered by the WP File Download (WPFD) plugin as a JavaScript file tree, so a static fetch returns only the year tab labels (2026, 2025 ...) and committee Terms-of-Reference PDFs, NOT the meeting packs. Each year tab is an anchor a.catlink with data-idcat (2026=2113, 2025=1937) that AJAX-loads a category; the year category contains per-meeting sub-folders named by month (2026: February=2114, April=2131, June=2154; 2025: February=1938, April=1967, June=1999, September=2054, November=2081), and each month sub-folder holds exactly ONE combined PDF titled 'Board of Directors - &lt;Month&gt; &lt;Year&gt;'. A crawler should hit the WPFD AJAX endpoint /wp-admin/admin-ajax.php?juwpfisadmin=false&amp;action=wpfd&amp;task=categories.display&amp;view=categories&amp;id=&lt;yearCatId&gt; to enumerate month sub-categories, then task=files.display&amp;view=files&amp;id=&lt;monthCatId&gt;&amp;rootcat=241 to get each file's ID, then download via the clean URL /download/&lt;catid&gt;/&lt;month&gt;/&lt;fileid&gt;/board-of-directors-&lt;month&gt;-&lt;year&gt;.pdf (verified HTTP 200, application/pdf). Quirk: these are single combined packs (one per meeting, no separate agenda/papers split) and only the Sheffield Children's Board of Directors is published here; ignore the committee ToR/structure PDFs under /download/347/board/ which are not meeting packs.</t>
+        </is>
+      </c>
+      <c r="J70" t="b">
+        <v>1</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Board of Directors - &lt;Month&gt; &lt;Year&gt;;/download/&lt;catid&gt;/&lt;month&gt;/&lt;fileid&gt;/board-of-directors-;action=wpfd&amp;task=files.display;rootcat=241;catlink data-idcat</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>/download/347/board/;terms-of-reference;committee-structure;Committees in Common;Council of Governors;nominations-remuneration</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Via the WPFD AJAX endpoint each 2025-26 month sub-folder returns one combined board pack and the June 2026 download URL was verified live (HTTP 200, application/pdf, 4.7MB).</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4419,16 +4991,42 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.barnsleyhospital.nhs.uk/about/how-we-are-run/board-of-directors/meetings-and-papers</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
+          <t>https://www.barnsleyhospital.nhs.uk/taxonomy/term/37</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Pattern C (per-meeting news/sub-pages) with combined-pack PDFs. The old landing page /about/.../meetings-and-papers only describes the schedule and points readers to the news section; the actual papers index is the Drupal taxonomy listing /taxonomy/term/37 ('Board Meeting' term), which lists each dated meeting as a news sub-page (e.g. '/news/board-directors-meeting-thursday-2-april-2026', '/news/board-directors-meeting-thursday-5-february-2026', and 2025 meetings back to February 2025). Each sub-page carries the combined public pack PDF stored under /sites/default/files/&lt;YYYY-MM&gt;/combined_pack_board_of_directors_public_meeting_&lt;month_year&gt;.pdf. Crawler should list term/37, open the latest dated meeting sub-page, then take the 'combined_pack...public_meeting' PDF. Quirk: meeting dates appear in news-style slugs, not a year archive.</t>
+        </is>
+      </c>
+      <c r="J71" t="b">
+        <v>0</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Board of Directors meeting - Thursday &lt;date&gt;;combined_pack_board_of_directors_public_meeting;Board of Directors: Public</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Council of Governors;Audit and Assurance Committee;Part 2;private</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>taxonomy/term/37 lists dated 2025-2026 board meeting sub-pages; search confirmed a Feb 2026 combined public pack PDF under /sites/default/files/2026-02/ on the org's own domain.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4667,16 +5265,42 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.nlg.nhs.uk/resources/board-papers-archive-2021/</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
+          <t>https://www.nlg.nhs.uk/resources/?resources_type=board-papers</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Pattern B (year archives) + Boards-in-Common. Northern Lincolnshire and Goole runs Trust Boards-in-Common with Hull (HUTH) under the NHS Humber Health Partnership; combined packs are published on the NLG site. Landing lists year cards ("Board papers 2026", "Board papers 2025", ...); click a year card (e.g. https://www.nlg.nhs.uk/resources/board-papers-2026/) to reach a table of one combined PDF per bi-monthly meeting under /wp-content/uploads/. The previous DB URL (/resources/board-papers-archive-2021/) still resolves but is a stale year-specific page; this hub auto-surfaces the current year. Prefer the largest combined "Board papers {Month} {Year}" PDF; these cover both NLG and Hull.</t>
+        </is>
+      </c>
+      <c r="J75" t="b">
+        <v>0</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Board papers {Month} {Year};Trust Boards-in-Common Papers;Combined board packs</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Council of Governors;AGM;committee papers;2021 archive</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Live NLG Boards-in-Common hub lists 2026 year card with Feb/Mar/Apr/May 2026 combined packs; replaced stale 2021 archive URL.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4765,16 +5389,42 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://www.leedsth.nhs.uk/about-us/board-papers/</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
+          <t>https://www.leedsth.nhs.uk/about/board/meetings/</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Pattern C/F. Old url /about-us/board-papers/ is a stub with no papers; the live board meetings index is /about/board/meetings/, which lists each dated meeting and, for published meetings, a downloadable combined pack. Quirk: packs are served as a single ZIP of the public board papers, e.g. 'Thursday 28 May 2026' -&gt; /wp-content/uploads/2026/05/LTHT-PUBLIC-Board-280526.zip, and there are also individual document pages at /documents/board-meeting-&lt;date&gt;/ (e.g. /documents/board-meeting-26-march-2026/). A 'View All Board Papers' filter link goes to /about/documents/?department=all&amp;type=board-papers&amp;sort=all. Crawler should take the latest dated meeting's LTHT-PUBLIC-Board ZIP (or open the /documents/board-meeting-&lt;date&gt;/ page) for the combined public pack.</t>
+        </is>
+      </c>
+      <c r="J77" t="b">
+        <v>0</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>LTHT-PUBLIC-Board;Board Meeting - &lt;date&gt;;Agenda - Board Meeting - &lt;Month Year&gt;;PUBLIC Board</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Annual General Meeting;private;Part 2;committee</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Board meetings index lists a 28 May 2026 public-board ZIP pack and a 26 March 2026 board-meeting document page on the org's own domain.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4863,16 +5513,42 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://www.hey.nhs.uk/about-us/board-papers/</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
+          <t>https://www.nlg.nhs.uk/resources/?resources_type=board-papers</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Pattern F (wrong-url-fixed) + B (year archives). OLD url https://www.hey.nhs.uk/about-us/board-papers/ 301-redirects off-domain to https://www.hull.nhs.uk/ (homepage) and the legacy /about-us/trust-board-meetings/ path 404s on the new domain. Since 2024 Hull University Teaching Hospitals (HUTH) and Northern Lincolnshire and Goole operate as 'Trust Boards-in-Common' under the NHS Humber Health Partnership group, and the combined board packs are published on the NLG website. NEW landing https://www.nlg.nhs.uk/resources/?resources_type=board-papers lists year cards ('Board papers 2026', 'Board papers 2025', ...); a crawler clicks the year card (e.g. https://www.nlg.nhs.uk/resources/board-papers-2025/) to reach a table of one combined PDF per bi-monthly meeting (Feb/Apr/Jun/Aug/Oct/Dec) under /wp-content/uploads/2025/01/. These packs explicitly cover BOTH NLG and Hull (the only board for Hull now), so the largest combined 'Board-papers-{Month}-{Year}.pdf' is the right pack. Quirk: all year-folder uploads sit in the /2025/01/ path regardless of meeting month; hey.nhs.uk only retains pre-2024 Hull-only archives.</t>
+        </is>
+      </c>
+      <c r="J79" t="b">
+        <v>0</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Board papers {Month} {Year};Trust Boards-in-Common Papers;Boards-in-Common;Combined board papers</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Council of Governors;CoG meeting papers;Annual General Meeting;AGM;committee papers;pre-2024 Hull-only archive</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>NLG board-papers year page lists six 2025 Boards-in-Common combined PDFs (Feb-Dec 2025) plus a 'Board papers 2026' archive, explicitly covering Hull University Teaching Hospitals under the group structure.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4915,13 +5591,39 @@
           <t>https://www.cht.nhs.uk/publications/board-of-directors-meeting-dates-and-papers</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Pattern A (dated PDFs on landing). The current url IS the correct live board-papers page for Calderdale and Huddersfield NHS Foundation Trust (title 'Board of Directors Meeting Dates and Papers - CHFT'). It lists each public Board of Directors meeting by date with a single combined 'Agenda and Papers' PDF per meeting, covering full 2026 (Jan/Mar/May with papers; Jul/Sep/Nov scheduled) and all of 2025, plus an in-page archive back to 2015. PDFs live under /fileadmin/site_setup/contentUploads/About_us/Publications/BoardPapers/{year}/Combined_*_Public_Board_of_Directors_*.pdf (TYPO3 fileadmin path). A crawler reads the dated rows directly on the landing page; no click-through needed. Validator missed it because the combined PDF filenames are long and not surfaced as simple dated-PDF links by the heuristic. Quirk: 2026 filenames use 'Combined_-_...WEBSITE.pdf' convention.</t>
+        </is>
+      </c>
+      <c r="J80" t="b">
+        <v>0</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Combined Public Board of Directors;Agenda and Papers;Public Board of Directors {weekday} {date}</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>minutes;committee;Council of Governors;AGM</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>Landing page lists combined agenda-and-papers PDFs for Jan/Mar/May 2026 and all 2025 meetings, e.g. the 15 January 2026 and 14 May 2026 Public Board of Directors PDFs.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4961,16 +5663,42 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://www.rdash.nhs.uk/about-us/governance/board-of-directors/board-of-directors-meetings/</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
+          <t>https://www.rdash.nhs.uk/document-sections/board-of-directors/</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Pattern C (per-meeting sub-pages) + F (wrong-url-fixed). OLD url https://www.rdash.nhs.uk/about-us/governance/board-of-directors/board-of-directors-meetings/ is a meetings-overview page that contains NO papers itself; it only schedules dates and points to a separate document repository plus a YouTube playlist (it states packs are emailed on request 5 working days ahead). NEW landing https://www.rdash.nhs.uk/document-sections/board-of-directors/ is the document section that lists per-meeting 'Board of directors packs {Month} {Year}' sub-pages (e.g. May/March/January 2026) and separate 'minutes' entries. A crawler opens the latest 'packs' sub-page (e.g. https://www.rdash.nhs.uk/documents/board-of-directors-packs-may-2026/) to reach the combined agenda pack PDF for that meeting; the section is paginated ('Next: 2 of 4'). Quirk: packs and minutes are separate entries - follow the 'packs' (not 'minutes') link for the full board pack.</t>
+        </is>
+      </c>
+      <c r="J81" t="b">
+        <v>0</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Board of directors packs {Month} {Year};Agenda packs for the {Month} {Year} board of directors meeting</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>minutes;Council of Governors;committee;AGM;YouTube playlist</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Document section lists 2026 board pack sub-pages (May/March/January 2026) each linking the meeting's combined agenda pack, plus matching minutes entries.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5062,13 +5790,39 @@
           <t>https://www.southwestyorkshire.nhs.uk/about-us-2/how-were-run/our-trust-board/meeting-papers/</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Pattern A (dated PDFs on landing). The current url is the correct live 'Board meetings and papers' page for South West Yorkshire Partnership NHS Foundation Trust. It lists each public Trust Board meeting by date with a combined 'Public Board agenda and papers' PDF (plus separate approved minutes) for 2026 (Jan/Mar/Apr) and all of 2025, archive back to 2008. PDFs sit under /wp-content/uploads/{yyyy}/{mm}/Public-*-agenda-and-papers-*.pdf (WordPress). A crawler reads the dated rows directly on the landing page. The validator flagged this as 403/broken (likely transient anti-bot on the health-check request), but WebFetch retrieved the full listing fine - if a crawler hits a 403, retry with a browser User-Agent. Quirk: filename date format varies (e.g. 28.04.26) and upload month-folder can lag the meeting month (Dec 2025 pack under /2025/11/).</t>
+        </is>
+      </c>
+      <c r="J83" t="b">
+        <v>0</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Public Board agenda and papers;Public agenda and papers TB;Board agenda and papers {dd.mm.yy}</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>minutes;committee;Council of Governors;AGM;Members' Council</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>Despite the 403 health-check flag, the page loads via WebFetch and lists combined agenda-and-papers PDFs for 28 Apr 2026, 31 Mar 2026, 27 Jan 2026 and all 2025 meetings.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5232,12 +5986,12 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://www.shsc.nhs.uk/about-us/board-directors</t>
+          <t>https://www.sheffieldpartnership.nhs.uk/about-us/board-directors/meeting-minutes-and-agendas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Strategy: landing shows a weak board-papers signal to a static parser (few dated PDFs found). Papers are likely present but loaded via JS or one click into a 'papers'/'meetings' sub-page. Confirm by following the board-papers / meetings link; prefer the main combined pack. Pattern A/C — review on next pass.</t>
+          <t>Pattern A/F (wrong-url-fixed): the trust rebranded and the old shsc.nhs.uk domain 301-redirects to sheffieldpartnership.nhs.uk. The old DB url pointed at the directors bio page (/about-us/board-directors) which only lists members and meeting dates plus a link 'Agenda papers for meetings can be found here'. The correct landing page is the child /about-us/board-directors/meeting-minutes-and-agendas, where each meeting is listed newest-first with individual links to an 'Agenda' PDF and 'Unconfirmed minutes' PDF stored under /sites/default/files/YYYY-MM/. There are no combined packs — a crawler follows each per-meeting Agenda/minutes PDF link directly. Quirk: filenames are URL-encoded with spaces (e.g. '00 Agenda Public BoD May 2026 .pdf').</t>
         </is>
       </c>
       <c r="J86" t="b">
@@ -5245,27 +5999,27 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Board Papers;Agenda and Papers;Public Board Pack</t>
+          <t>Agenda Public BoD;Public BoD;unconfirmed minutes public BoD;Board of Directors</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+          <t>Council of Governors;Gifts Hospitality;Declarations of Interests;register</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>papers_partial</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>Validator (static) weak signal: dated_pdfs=0, year_archives=1, meeting_subpages=0; review.</t>
+          <t>Confirmed dated agenda/minutes PDFs for the 28 May 2026 public Board of Directors meeting plus March 2026, January 2026 and November 2025 on the meeting-minutes-and-agendas page on the live sheffieldpartnership.nhs.uk domain.</t>
         </is>
       </c>
     </row>
@@ -5457,13 +6211,39 @@
           <t>https://www.nwangliaft.nhs.uk/trust-board/</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Pattern B+D: the current /trust-board/ landing page is valid — it lists 2026 board meeting dates (14 July, 13 Oct, 8 Dec 2026) and a link 'Our Board Papers' to /our-board-papers. That page is a JS-rendered media browser with year folders ('Board Papers 2025', 'Board Papers 2026'); each year expands to monthly subfolders (January/March/May 2026) and only then to the individual agenda/minutes/report PDFs. A static crawler can reach the year/month folder URLs via querystring (?media_folder=ID&amp;root_folder=Board Papers 2026) but the actual PDF list inside each month folder is loaded by JavaScript, so Playwright is needed to enumerate the dated PDFs. Quirk: papers are split into many individual documents per meeting rather than one combined pack.</t>
+        </is>
+      </c>
+      <c r="J90" t="b">
+        <v>1</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Board Papers 2026;Board Papers 2025;Trust Board;agenda;minutes</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Council of Governors;Gifts Hospitality;Declarations of Interests</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>papers_partial</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>Confirmed live 'Our Board Papers' media browser with Board Papers 2025 and 2026 year folders containing January/March/May 2026 monthly subfolders, but the individual dated PDFs inside the folders are JS-loaded and not enumerable statically.</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5503,16 +6283,42 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://www.jpaget.nhs.uk/about-us/our-board-and-governors/our-board-of-directors/</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr"/>
+          <t>https://www.jpaget.nhs.uk/about-us/our-board-and-governors/board-and-governors-meetings/</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Pattern A/F (wrong-url-fixed): the old DB url (/about-us/our-board-and-governors/our-board-of-directors/) is just director biographies with no papers, and the previously linked /about-us/board-of-directors/meetings path now 404s (confirmed dead in Playwright too). The correct live archive is /about-us/our-board-and-governors/board-and-governors-meetings/, which lists meetings newest-first with a single large combined 'Part A complete pack' PDF per public meeting stored under /media/&lt;hash&gt;/. A crawler grabs the per-meeting '...part-a-complete-pack.pdf' link. Quirk: the trust is transitioning to a Norfolk and Waveney University Hospitals Group Board (shared with Norfolk and Norwich and QEH King's Lynn) from April 2026, so 2026 packs may appear under the new Group Board section on this same page; prefer the JPUH/Group 'in public' Part A complete pack and skip Council of Governors items.</t>
+        </is>
+      </c>
+      <c r="J91" t="b">
+        <v>0</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>board-of-directors-meeting-in-public-part-a-complete-pack;Part A complete pack;Board of Directors in public;Group Board</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Council of Governors;Part B;private;Integrated Board Report;Chief Nurse Report;Declarations of Interest</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>Confirmed dated combined public board packs for 26 September 2025 and 25 July 2025 on the board-and-governors-meetings page, with a noted transition to Norfolk and Waveney Group Board meetings from April 2026.</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5800,13 +6606,39 @@
           <t>https://eastofenglandcommunityhealthandcare.nhs.uk/about-us/our-board/board-meetings-and-reports/</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
-      <c r="O97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Patterns A+C: a single landing page lists all 2025-26 meetings in date order, each meeting expanding to the individual papers for that meeting as directly-linked PDFs (an agenda numbered 00-...-agenda plus separately numbered item PDFs); there are no year archives or separate sub-pages. The page briefly shows 'Content is loading...' but all PDF links are present in the static HTML, so JavaScript is not strictly required. Quirk: PDFs live under /media/&lt;hash&gt;/ with date-coded, item-numbered filenames (e.g. 00-2026-05-20-trust-board-meeting-in-public-agenda-final.pdf); this is a newly-merged GROUP trust so recent agendas are titled 'Group Trust Board meeting in public' - keep these but skip any committee or partnership/joint papers; there is no single combined bundle, so a crawler should collect all per-item PDFs under each dated meeting, anchored by the 00-...-agenda file.</t>
+        </is>
+      </c>
+      <c r="J97" t="b">
+        <v>0</v>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>trust-board-meeting-in-public;group-trust-board-meeting-in-public;00-...-agenda;/media/;&lt;yyyy-mm-dd&gt;-trust-board;meeting in public</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>committee;Part II;confidential;private;in-private;joint;partnership;/media/.*-agm-</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>Landing page directly lists dated meetings with agenda and item PDFs for 28 Jan, 18 Mar, 1 Apr and 20 May 2026 plus Sep and Nov 2025.</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5846,16 +6678,42 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>https://www.uhd.nhs.uk/about-us/our-performance/board-papers</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
-      <c r="O98" t="inlineStr"/>
+          <t>https://www.uhd.nhs.uk/about-us/our-performance</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Pattern A/F (wrong-url-fixed): the old DB url /about-us/our-performance/board-papers is only a navigation hub that links onward to /about-us/our-performance, the real board-meetings listing. That page shows 2026 meeting dates and, newest-first, a single combined 'Board of Director Part 1 Meeting Pack &lt;date&gt;' PDF per public meeting plus separate Agenda and 'Reading room' PDFs, all stored under /uploads/about/docs/bod/&lt;year&gt;/. A crawler follows the per-meeting 'bod-&lt;mon&gt;&lt;yy&gt;.pdf' combined pack link. Quirk: combined pack filenames are short codes (bod-may26.pdf) while agenda/appendix files use longer descriptive names; only Part 1 (public) packs are published.</t>
+        </is>
+      </c>
+      <c r="J98" t="b">
+        <v>0</v>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Board of Director Part 1 Meeting Pack;bod-;Part 1 Meeting Pack;Board of Directors</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>Part 2;private;Reading room;agenda;appendix;Council of Governors</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>Confirmed combined 'Board of Director Part 1 Meeting Pack 13 May 2026' PDF and supporting agenda/reading-room files on the our-performance page, with 2026 meeting dates listed through November 2026.</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5993,16 +6851,42 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>https://www.dchft.nhs.uk/about-us/trust-board/</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
-      <c r="O101" t="inlineStr"/>
+          <t>https://www.dchft.nhs.uk/about-us/trust-board/trust-board-meetings/</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Pattern A. From the landing /about-us/trust-board/ a crawler follows the one-click child 'Trust Board Meetings' link to /about-us/trust-board/trust-board-meetings/, which lists each public meeting by date with a direct link to the full Part 1 paper pack PDF hosted under /wp-content/uploads/YYYY/MM/. Dorset County Hospital now meets as part of a Dorset 'Board in Common', so recent packs are named 'Board-in-Common-Part-1-Paper-Pack' alongside older 'Board-of-Directors-part-1-papers' naming; both are the trust's own board papers. The original landing /about-us/trust-board/ shows no papers itself (validator was right) but the dated PDFs live one click down on the meetings sub-page. Only Part 1 (public) packs are published; Part 2 is confidential.</t>
+        </is>
+      </c>
+      <c r="J101" t="b">
+        <v>0</v>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Board-in-Common-Part-1-Paper-Pack;Board-of-Directors-part-1-papers;Part-1-Board-papers;/wp-content/uploads/;part-1</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>part-2;confidential;Front-sheet;Annual-Safe-Staffing-Report</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>Trust Board Meetings sub-page lists dated 2025 and 2026 Part 1 board paper pack PDFs (e.g. Feb, Apr, Jun, Aug, Oct, Dec 2025 and Feb, Apr 2026).</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -6171,35 +7055,35 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Strategy: NEW DOMAIN. Trust migrated to royalcornwallhospitals.nhs.uk (the legacy royalcornwall.nhs.uk URL has WAF/Cloudflare protection that blocks direct fetch with HTTP 403, even from headless Chromium). The new landing page links to year-archive .aspx pages on a SEPARATE document-library subdomain: doclibrary-rcht.cornwall.nhs.uk/.../BoardMeetings/BoardMeetings{FY}.aspx (eg BoardMeetings2526.aspx, BoardMeetings2627.aspx) — the doc-library subdomain has NO WAF and serves PDFs cleanly over plain HTTP. PDFs live at /DocumentsLibrary/RoyalCornwallHospitalsTrust/ChiefExecutive/TrustBoard/Minutes/{FYYY}/{YYYYMM}/ where FYYY is the 4-digit FY (2526) and YYYYMM is meeting month. The current-FY link on the landing page is wrapped in an Outlook safelinks redirect — unwrap via the url= query parameter to recover the real archive URL. Six meetings/year cadence (May, Jul, Sep, Nov, Jan, Mar).</t>
+          <t>Pattern D (JS-rendered landing). A static fetch of this URL returns a near-empty body, so the year-archive links and the rendered 'Board meeting papers' accordion section are invisible to a static crawler. Under headless Chromium the page renders on royalcornwallhospitals.nhs.uk (the legacy royalcornwall.nhs.uk domain is WAF/Cloudflare-blocked) and exposes a set of per-financial-year links to a SEPARATE document-library subdomain: doclibrary-rcht.cornwall.nhs.uk/RoyalCornwallHospitalsTrust/Internet/DocumentsLibrary/BoardMeetings/BoardMeetings{FY}.aspx (e.g. BoardMeetings2526.aspx for 2025/26, BoardMeetings2627.aspx for 2026/27, plus a BoardMeetingsIndex.aspx). The current-FY (26/27) link is wrapped in an Outlook safelinks redirect — unwrap via the url= query parameter to recover the real .aspx archive URL; the 25/26 and earlier links are direct. Each .aspx year page is the doc library that lists the dated board-pack PDFs, which live at /DocumentsLibrary/RoyalCornwallHospitalsTrust/ChiefExecutive/TrustBoard/Minutes/{FYYY}/{YYYYMM}/ (FYYY = 4-digit FY e.g. 2526, YYYYMM = meeting month) — confirmed by a direct link on the rendered landing page to Minutes/2526/202509/AnnualReportAndAccounts202425.pdf. Six meetings/year cadence (May, Jul, Sep, Nov, Jan, Mar). NOTE: the doclibrary subdomain serves over plain HTTP and was not reachable from this sandbox (HTTPS refused / HTTP connection timed out), so the individual board-pack PDFs could not be opened here, but the navigation path and PDF path pattern are confirmed from the rendered landing page.</t>
         </is>
       </c>
       <c r="J104" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Agenda Pack Trust Board Public; Agenda Pack Trust Board in Public; Trust Board Agenda Pack</t>
+          <t>doclibrary-rcht.cornwall.nhs.uk/RoyalCornwallHospitalsTrust/Internet/DocumentsLibrary/BoardMeetings/BoardMeetings{FY}.aspx;doclibrary-rcht.cornwall.nhs.uk/DocumentsLibrary/RoyalCornwallHospitalsTrust/ChiefExecutive/TrustBoard/Minutes/{FY}/{YYYYMM}/*.pdf;BoardMeetings2526.aspx / BoardMeetings2627.aspx / BoardMeetingsIndex.aspx;unwrap gbr01.safelinks.protection.outlook.com via url= query parameter;Minutes path FY is 4-digit (2526), YYYYMM is meeting year+month</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>Confidential; Part B; Private; Minutes only; Annual Report only</t>
+          <t>royalcornwall.nhs.uk (legacy WAF-blocked domain);/board-members-and-committees/;DeclarationsOfInterest;GiftsHospitalitySponsorship;language/translate anchors (#);bit.ly join-the-meeting links</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>papers_found</t>
+          <t>needs_playwright</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>24 in-window meetings found via doclibrary-rcht subdomain year-archive .aspx pages. Two largest packs March 2026 (12MB) and May 2026 (23MB) both contain clean BAF sections (locator scores 599 + 537).</t>
+          <t>Rendered landing confirms FY year-archive .aspx links plus a dated Minutes/2526/202509 PDF, but the plain-HTTP doclibrary subdomain that hosts the individual board packs was unreachable from this sandbox so the dated packs could not be directly opened.</t>
         </is>
       </c>
     </row>
@@ -6293,13 +7177,39 @@
           <t>https://www.royaldevon.nhs.uk/about-us/board-of-directors/board-meetings-papers-minutes/</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
-      <c r="O106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Pattern A + E. The current URL is correct and live; it returns HTTP 403 to WebFetch/server-side bots (anti-bot/WAF) but renders fully in a real browser (verified via Playwright, location.host www.royaldevon.nhs.uk). On the page, the 'Board papers and minutes' section lists each public meeting by date with direct 'Papers' (and 'Minutes') PDF links hosted under /media/&lt;hash&gt;/, plus Vimeo recording links. A crawler must use a browser/JS-capable fetcher (or spoof a browser User-Agent) to bypass the 403; once loaded, dated 2026 packs are immediately present. Older years are behind the one-click 'Archive' link (/about-us/board-of-directors/board-meetings-papers-minutes/archive/). Pick the 'Papers' link (full meeting pack) for each date; skip the Vimeo recordings and the acronyms glossary.</t>
+        </is>
+      </c>
+      <c r="J106" t="b">
+        <v>1</v>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>/media/;rduh-board-public;rduh-public-board-meeting;meeting-pack;meeting-book;pack-for-governors;Papers</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>vimeo.com;Recording;glossary_of_acronyms;minutes-action-tracker;minutes-board-public</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>Page rendered in browser shows direct PDF paper packs for 27 May 2026, 25 March 2026, 28 January 2026 and 9 January 2026; 403 to WebFetch is anti-bot only, not a broken URL.</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -6486,16 +7396,42 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>https://www.salisbury.nhs.uk/about-us/the-trust-board/trust-board-meetings/</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
-      <c r="O110" t="inlineStr"/>
+          <t>https://www.salisbury.nhs.uk/about-us/the-trust-board/board-papers/</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Pattern B + C. The original landing /trust-board-meetings/ only lists upcoming meeting dates (no papers, validator correct). The papers live one click away at /about-us/the-trust-board/board-papers/, which is a year-archive index (Board papers 2026, Board papers 2025, etc.). Each year folder lists per-meeting sub-pages (e.g. '8 January 2026 Public Trust Board', '5 March 2026', '13 May Trust Board') and each year folder reportedly contains ~89 files. A crawler follows board-papers -&gt; board-papers-YYYY -&gt; per-meeting page -&gt; individual paper/agenda PDFs. Papers are split into many individual item PDFs per meeting rather than one combined pack, so collect all PDFs under each per-meeting sub-page (prefer an 'agenda'/'papers' combined item if present).</t>
+        </is>
+      </c>
+      <c r="J110" t="b">
+        <v>0</v>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>board-papers-2026;board-papers-2025;public-trust-board;trust-board;agenda;papers</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>governors;council-of-governors;minutes-of-previous</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>board-papers page exposes Board papers 2025 and 2026 year archives, and the 2026 archive lists dated per-meeting sub-pages (8 Jan, 5 Mar, 13 May 2026).</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -7181,13 +8117,39 @@
           <t>https://www.nwl-acute-provider-group.nhs.uk/about-us/board-in-common</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
-      <c r="O122" t="inlineStr"/>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Pattern C/F. The Hillingdon Hospitals no longer holds a standalone board; it is governed via the North West London Acute Provider Collaborative 'Board in Common' (shared across NWL acute trusts including Hillingdon). The board-in-common landing page describes the body but the dated papers are reached one click via the Events section (/events, anchor #bic), which lists each Board in Common meeting by date with a direct 'Agenda and meeting papers' PDF under /-/media/website/nwl-acute-provider-group/documents/board-in-common/. Historical packs are also on /publications. Because this is a combined Board in Common, the single published pack covers all member trusts (no separate Hillingdon-only board); take the main 'Agenda and meeting papers' combined PDF per meeting and skip the supplementary reading-room item PDFs.</t>
+        </is>
+      </c>
+      <c r="J122" t="b">
+        <v>0</v>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>/documents/board-in-common/;board_in_common;public;agenda-and-meeting-papers;bic</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>reading-room;register-of-interests;register_of_interests;learning-from-death</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>Events section lists dated Board in Common meetings (28 April 2026 with a direct public agenda+papers PDF; 28 Jul, 20 Oct 2026 and 26 Jan 2027 scheduled).</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -7651,13 +8613,39 @@
           <t>https://www.gosh.nhs.uk/about-us/who-we-are/organisational-structure/trust-board/trust-board-meetings/</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
-      <c r="O130" t="inlineStr"/>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Pattern A (dated PDFs on landing). The current URL was flagged broken (health_broken) by the validator but WebFetch confirms it is LIVE and serves the Trust Board meetings page directly. The landing page lists per-meeting 'Download meeting papers [Month Year]' links to combined agenda-and-papers PDFs at /documents/{id}/PUBLIC_Trust_Board_agenda_and_papers_{ddmmyy}.pdf, plus separate minutes PDFs. Recent entries include March 2026 and May 2026. The page also has 'Trust Board Dates 20xx' archive sections (mild pattern B) and an 'Archived meetings 2011 to 2020' link. A crawler should take the most recent 'Download meeting papers' PDF, which is already the largest combined pack. The earlier broken flag was likely a transient fetch/timeout; the URL is correct.</t>
+        </is>
+      </c>
+      <c r="J130" t="b">
+        <v>0</v>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Download meeting papers;Trust_Board_agenda_and_papers;PUBLIC_Trust_Board;Trust Board Dates</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>minutes;Archived meetings 2011 to 2020</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>Landing page directly lists combined agenda-and-papers PDFs including March 2026 and May 2026.</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -7870,16 +8858,42 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>https://tavistockandportman.nhs.uk/about-us/our-board/</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
-      <c r="O134" t="inlineStr"/>
+          <t>https://tavistockandportman.nhs.uk/publications/?publication-types=board-papers</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Pattern C/F (per-meeting sub-pages; wrong-url-fixed). Old URL was the /about-us/our-board/ profile page which only links out and has no dated papers. New URL is the publications listing filtered to board-papers, which lists per-meeting entries 'Board papers - {Month Year}' each linking to a sub-page (e.g. /publications/board-papers-march-2026/) that holds the combined pack PDF. Most recent entries: March 2026, January 2026 (plus an Extraordinary board papers - January 2026), November 2025. IMPORTANT QUIRK: Tavistock and Portman NHS FT merged into North London NHS Foundation Trust on 1 April 2026 and this website is now archived (banner: 'This website has been archived'); historical board papers remain accessible here but future packs will move to the North London FT site. A crawler should follow the latest 'Board papers' entry to its sub-page and take the combined pack; skip 'Extraordinary' unless that is the only recent meeting.</t>
+        </is>
+      </c>
+      <c r="J134" t="b">
+        <v>0</v>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Board papers - {Month Year};board-papers-{month}-{year}</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>Extraordinary board papers;archived website</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>Publications board-papers filter lists dated meeting sub-pages through March 2026 (site archived post-merger but papers still live).</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -7968,16 +8982,42 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>https://www.elft.nhs.uk/information-about-elft/our-board/trust-board-meetings</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
-      <c r="O136" t="inlineStr"/>
+          <t>https://www.elft.nhs.uk/information-about-elft/our-board/trust-board-meetings/trust-board-papers</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Pattern A/F (dated combined PDFs on the corrected sub-page; wrong-url-fixed). Old URL (/trust-board-meetings) is a hub page that only links out ('You can find our Board Meeting papers here') with no dated PDFs, hence no_papers_visible. New URL is the trust-board-papers sub-page which lists each meeting date with a 'Combined board papers' link to a single combined PDF under /sites/default/files/{yyyy-mm}/. Recent entries run May 2026, March 2026, January 2026, December 2025, September 2025, etc. A crawler should take the most recent date's 'Combined board papers' PDF (the full pack). Older years are under a separate 'papers-previous-years' sub-page. Note: org is East London NHS Foundation Trust (ELFT); the names list also mentions NELFT but that is a different trust.</t>
+        </is>
+      </c>
+      <c r="J136" t="b">
+        <v>0</v>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Combined board papers;TBD PUBLIC;Combined Papers;Trust Board in Public</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>previous years;Acronyms.pdf;minutes</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>Corrected sub-page lists Combined board paper PDFs through 21 May 2026.</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -8020,13 +9060,39 @@
           <t>https://www.stsft.nhs.uk/about-us/our-people/our-board/board-papers</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
-      <c r="O137" t="inlineStr"/>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Pattern B/A (fiscal-year sections with per-meeting dated PDFs on landing). The current URL is correct; the validator missed it (likely JS-light rendering of the lists). The page groups meetings by fiscal year ('2026/27', '2025/26', '2024/25' ... back to '2019/20'), each entry formatted '[Date] - [Agenda and papers]' linking to a combined pack PDF. Most recent listed includes 5 February 2026 and 2026/27 dates (June/April 2026). A crawler should pick the latest fiscal-year block and take the newest 'Agenda and papers' link (the combined pack). This is the org's own Board (single trust board, no ICP/cluster ambiguity).</t>
+        </is>
+      </c>
+      <c r="J137" t="b">
+        <v>0</v>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Agenda and papers;2026/27;2025/26</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>minutes</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>Landing page lists fiscal-year sections with 'Agenda and papers' links including 5 February 2026 and 2026/27 dates.</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -8069,13 +9135,39 @@
           <t>https://www.ncic.nhs.uk/trust/how-we-are-run/board-meetings</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
-      <c r="O138" t="inlineStr"/>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Pattern A: the landing page lists a combined 'Agenda and Papers' board-pack PDF per meeting directly, grouped under year headings (2026, 2025, etc.), all visible in static HTML. Each link is a single large combined PDF served via the CMS download endpoint of form https://www.ncic.nhs.uk/download_file/view/&lt;id&gt;/268 (the /268 suffix is the board-papers document category; numeric ids are non-sequential and not date-derivable, so a crawler must scrape the dated link text on this page rather than guess ids). PDFs are large (10MB+). Upcoming-meeting links of form /events/event-details?occurrenceID=NNNN are calendar entries, not packs. No JS rendering needed.</t>
+        </is>
+      </c>
+      <c r="J138" t="b">
+        <v>0</v>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>/download_file/view/&lt;id&gt;/268;Agenda and Papers</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>/events/event-details;occurrenceID=</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>Static page lists dated combined Agenda+Papers board-pack PDFs for 2025 and 2026; sampled May 2026 link returned a multi-MB PDF.</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -8262,16 +9354,42 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>https://www.southtees.nhs.uk/resources/board-of-directors-agenda-1-february-2022/</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
-      <c r="O142" t="inlineStr"/>
+          <t>https://www.southtees.nhs.uk/about/university-hospitals-tees/board-meetings/</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Pattern B/C with a quirk: this is the canonical group board landing for the University Hospitals Tees Group Board (shared between South Tees RTR and North Tees RVW). The landing itself shows only the next upcoming meeting date plus a 'View meeting agenda archive' link; dated papers are one click away via the resources archive at https://www.southtees.nhs.uk/resources/?for=&amp;topic=hospital-group&amp;type=agendas&amp;audience=all which lists per-meeting pages titled 'Group Board of Directors Agenda - &lt;date&gt;'. Each per-meeting page (e.g. /resources/group-board-of-directors-agenda-5-march-2026/) links to a single combined Agenda+Papers PDF under /wp-content/uploads/&lt;yyyy&gt;/&lt;mm&gt;/. The old stored URL was a stale 2022 single-meeting resource page. Crawler should follow the agenda archive filter, then per-meeting subpages, then the combined PDF.</t>
+        </is>
+      </c>
+      <c r="J142" t="b">
+        <v>0</v>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Group Board of Directors Agenda - &lt;date&gt;;Board-of-Directors-papers-&lt;date&gt;.pdf;/resources/group-board-of-directors-agenda-;/wp-content/uploads/&lt;yyyy&gt;/&lt;mm&gt;/</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>register-of-interests;declaration-of-interest;council-of-governors;/news/;/events/</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>Canonical group board landing reached the archive listing per-meeting pages with confirmed combined PDFs for 5 March 2026, 8 January 2026 and 7 May 2026.</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -8311,16 +9429,42 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>https://www.nth.nhs.uk/about/board-meetings/</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
-      <c r="O143" t="inlineStr"/>
+          <t>https://www.nth.nhs.uk/about/university-hospitals-tees/board-meetings/</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Pattern B/C with a quirk: this is the canonical group board landing for the University Hospitals Tees Group Board (shared between North Tees RVW and South Tees RTR). The old stored URL https://www.nth.nhs.uk/about/board-meetings/ 301-redirects to /about/board/ which is only a stale Declaration of Interest register page (validator false-positive). The new landing lists upcoming meeting dates (e.g. 8 Jan 2026, 5 Mar 2026) and links to the group board papers archive at https://www.nth.nhs.uk/resources/?search=&amp;department=all&amp;type=board-papers&amp;range=all&amp;custom_range= which lists per-meeting pages titled 'Board of directors papers - &lt;date&gt;'. Each subpage links to a single combined public papers PDF under /wp-content/uploads/&lt;yyyy&gt;/&lt;mm&gt;/ (e.g. ~15MB). Crawler should follow the board-papers resource filter, then per-meeting subpage, then combined PDF.</t>
+        </is>
+      </c>
+      <c r="J143" t="b">
+        <v>0</v>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Board of directors papers - &lt;date&gt;;Public-board-papers-&lt;date&gt;.pdf;Board-of-Directors-Thursday-&lt;date&gt;-final-papers.pdf;/resources/board-of-directors-papers-;/wp-content/uploads/&lt;yyyy&gt;/&lt;mm&gt;/</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>declaration-of-interest;/about/board/;register-of-interests;/news/</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>New canonical landing lists upcoming dates and links to a board-papers archive; confirmed combined PDFs for 7 May 2026, 5 March 2026 and 8 January 2026.</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -8435,16 +9579,42 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>https://www.cntw.nhs.uk/about/publications/board-papers-27-may-2015/agenda-item-10-i-trust-board-models-of-care-front-sheet/</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
-      <c r="O145" t="inlineStr"/>
+          <t>https://www.cntw.nhs.uk/about/publications/?filter_publication_type=344</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Pattern B/C: the old stored URL was a deep 2015 single agenda-item front-sheet page (long stale). The correct landing is the trust Publications archive filtered to the 'Board Papers' category via ?filter_publication_type=344 (https://www.cntw.nhs.uk/about/publications/?filter_publication_type=344). This lists per-meeting publication pages titled 'Board Papers - &lt;date&gt;' (e.g. /about/publications/board-papers-29-april-2026/), each linking to a combined board-papers PDF under /wp-content/uploads/&lt;yyyy&gt;/&lt;mm&gt;/ (e.g. CNTW-Board-of-Directors-Public-Papers-April-2026.pdf). The unfiltered /about/publications/ page also surfaces the same board entries near the top. Skip Council of Governors entries. Crawler should hit the filtered publications list, then per-meeting subpage, then the combined PDF.</t>
+        </is>
+      </c>
+      <c r="J145" t="b">
+        <v>0</v>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Board Papers - &lt;date&gt;;CNTW-Board-of-Directors-Public-Papers-&lt;month-year&gt;.pdf;/about/publications/board-papers-;filter_publication_type=344</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>Council-of-Governors;council-of-governors;/news/;annual-report;green-plan;agenda-item-</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>Board Papers category filter (type 344) lists 2025-26 per-meeting pages with confirmed combined PDFs for 29 April 2026, 28 January 2026 and 5 November 2025.</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -9097,13 +10267,39 @@
           <t>https://www.buckshealthcare.nhs.uk/publications/trust-board-papers/</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr"/>
-      <c r="M158" t="inlineStr"/>
-      <c r="N158" t="inlineStr"/>
-      <c r="O158" t="inlineStr"/>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Pattern B then C: the landing page is a year-archive index linking to per-year sub-pages (e.g. /publications/trust-board-papers/trust-board-meetings-2026/ and .../trust-board-meetings-2025/), all in static HTML. Each year page lists one document-folder sub-page per meeting at /documents/&lt;slug&gt;-trust-board-papers-&lt;month&gt;-&lt;year&gt;/ (the slug is prefixed by a stray single letter such as 'w/x/y/z' in the link text). That document page is NOT a single combined pack: it holds many separately-linked numbered PDFs (00 Agenda, 01.1 Meeting Protocol, ... through ~22). A crawler must follow year -&gt; meeting document page -&gt; individual numbered PDFs; there is no combined Agenda+Papers download, so collect the full set of numbered PDFs per meeting. No JS rendering needed.</t>
+        </is>
+      </c>
+      <c r="J158" t="b">
+        <v>0</v>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>/publications/trust-board-papers/trust-board-meetings-&lt;year&gt;/;/documents/&lt;slug&gt;-trust-board-papers-&lt;month&gt;-&lt;year&gt;/;00 Agenda</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>board-affiliate-blog;organisational-chart</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>Year sub-pages list per-meeting document folders for 2025 and 2026; the March 2026 folder contains the numbered agenda and papers PDFs (00-22).</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -9270,13 +10466,39 @@
           <t>https://www.northerncarealliance.nhs.uk/about-us/board-directors/board-dates-and-papers</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr"/>
-      <c r="M161" t="inlineStr"/>
-      <c r="N161" t="inlineStr"/>
-      <c r="O161" t="inlineStr"/>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Pattern A/D (validator false-negative): the stored landing IS correct and current. It directly lists all 2025 and 2026 board meeting dates each with a 'Papers' link, 'Minutes' link and YouTube video. The validator reported no_papers_visible because the date/papers list is rendered client-side, but WebFetch confirmed it is populated. Each 'Papers' link is a numeric download endpoint of the form /download_file/view/&lt;id&gt;/875 returning the combined meeting pack PDF. Crawler may need light JS rendering but the links resolve directly; no per-meeting subpages needed.</t>
+        </is>
+      </c>
+      <c r="J161" t="b">
+        <v>1</v>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>/download_file/view/&lt;id&gt;/875;&lt;date&gt; Papers;board-dates-and-papers</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>youtu.be;youtube.com;Minutes;Video</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>Landing directly lists 2025-26 board dates with working Papers download links (e.g. 6 May 2026, 4 March 2026, 14 January 2026); validator missed the JS-rendered list.</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -9316,16 +10538,42 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>https://www.boltonft.nhs.uk/about-us/our-board/</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr"/>
-      <c r="J162" t="inlineStr"/>
-      <c r="K162" t="inlineStr"/>
-      <c r="L162" t="inlineStr"/>
-      <c r="M162" t="inlineStr"/>
-      <c r="N162" t="inlineStr"/>
-      <c r="O162" t="inlineStr"/>
+          <t>https://www.boltonft.nhs.uk/about-us/our-board/board-of-directors-meetings/</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Pattern C (per-meeting combined PDFs). The validator was pointed at the parent /about-us/our-board/ landing, which only describes the board and links onward; the actual papers live one click deeper at /about-us/our-board/board-of-directors-meetings/. That page lists each Board of Directors meeting by date under year headings (2026, 2025, plus archived 2024 and earlier) with a single combined PDF bundle per meeting (agenda + papers), e.g. wp-content/uploads/2026/.../Board-of-Directors-&lt;date&gt;.pdf. A crawler reaches dated papers by following the 'Board of Directors meetings' link from the landing, then taking the per-date PDF under each year heading; bundles are stored under /wp-content/uploads/&lt;year&gt;/&lt;month&gt;/. Bi-monthly cadence. No JS gallery, no anti-bot.</t>
+        </is>
+      </c>
+      <c r="J162" t="b">
+        <v>0</v>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>wp-content/uploads/;Board-of-Directors-;&lt;date&gt;.pdf;per-meeting combined bundle</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>Register-of-Interests;register-of-interests</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>Child meetings page lists combined Board of Directors PDF bundles for every 2025 and 2026 meeting under year headings.</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -9365,16 +10613,42 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>https://tamesideandglossopicft.nhs.uk/about-us/trust-oversight/trust-board</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
-      <c r="K163" t="inlineStr"/>
-      <c r="L163" t="inlineStr"/>
-      <c r="M163" t="inlineStr"/>
-      <c r="N163" t="inlineStr"/>
-      <c r="O163" t="inlineStr"/>
+          <t>https://www.tamesideandglossopicft.nhs.uk/about-us/trust-oversight/trust-board/trust-board-minutesagendas</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Pattern C (per-meeting combined PDFs) plus pattern F (wrong landing fixed). The validator hit the /trust-board overview page, which only lists future meeting dates and states 'Meeting papers will be available prior to the meeting'; the papers archive is one click deeper at .../trust-board/trust-board-minutesagendas. That page lists each public Trust Board meeting by month/year with a single 'Combined Papers' PDF per meeting; URLs are inconsistent (some are friendly application/files/.../Combined_Papers...pdf paths, others are opaque /download_file/&lt;id&gt;/0 endpoints), so a crawler should follow each meeting's link rather than guess a pattern. Quirk: the page states old minutes/agendas are available only up to April 2026 — for meetings from April 2026 onward the trust directs users to the South East Sector Health Care Partnership site (southeastsector-hcp.nhs.uk), so this archive will become stale for newer meetings. No JS gallery, no anti-bot.</t>
+        </is>
+      </c>
+      <c r="J163" t="b">
+        <v>0</v>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>application/files/;Combined_Papers;download_file/&lt;id&gt;/0;per-meeting combined bundle</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>southeastsector-hcp.nhs.uk;register-of-interests</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>Minutes/agendas child page has combined public Trust Board paper PDFs for every 2025 and 2026 meeting (Jan-Nov 2025, Jan and Mar 2026).</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -9419,25 +10693,25 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Strategy: /about-us/board-papers/ is correct and working — it lists upcoming meetings, a '&lt;year&gt; Board Papers' section with per-meeting 'Meeting papers' PDF bundles, and an archive. The 'Meeting papers' links load via JS, which is why a static parser sees no PDFs. Pattern A/C; prefer the public bundle PDF.</t>
+          <t>Pattern A/C (dated combined bundles directly on the landing). The validator saw no_papers_visible, but the current url (which 301s to https://www.wwl.nhs.uk/board-papers) actually lists upcoming Board of Directors meeting dates and, for held meetings, a single combined 'Public Bundle' PDF per meeting stored under /media/board/Papers/&lt;year&gt;/. A crawler reaches dated 2026 papers directly from this landing via the per-meeting PDF links; older years are behind a 'Board Papers Archive' link at /board-papers-archive. The validator likely missed the PDFs because filenames carry dates in DD.MM.YY form and links sit in an expandable meetings list. No JS gallery, no anti-bot.</t>
         </is>
       </c>
       <c r="J164" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>Meeting papers;public bundle;Board Papers</t>
+          <t>/media/board/Papers/;Public Bundle;Public bundle;DD.MM.YY;RFS.pdf</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+          <t>board-papers-archive;Private</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -9447,7 +10721,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>Working page with 2026 'Meeting papers' bundles; static parser missed JS-loaded PDF links (false no_papers_visible).</t>
+          <t>Landing lists combined Public Bundle PDFs for the 04 Feb 2026 and 01 Apr 2026 Board of Directors meetings under /media/board/Papers/2026/.</t>
         </is>
       </c>
     </row>
@@ -9541,13 +10815,39 @@
           <t>https://www.stockport.nhs.uk/about/board/board-meetings/</t>
         </is>
       </c>
-      <c r="I166" t="inlineStr"/>
-      <c r="J166" t="inlineStr"/>
-      <c r="K166" t="inlineStr"/>
-      <c r="L166" t="inlineStr"/>
-      <c r="M166" t="inlineStr"/>
-      <c r="N166" t="inlineStr"/>
-      <c r="O166" t="inlineStr"/>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Pattern C (per-meeting PDFs on the landing). The validator flagged papers_partial, but the current url lists forthcoming meeting dates and a 'Previous Board Meetings' section with per-meeting PDFs (Public Documents and Private Agenda) for 2025 stored under /wp-content/uploads/&lt;year&gt;/&lt;month&gt;/. A crawler reaches dated papers directly from this landing by taking the '&lt;...&gt; Public Documents' PDF for each previous meeting (skip the matching 'Private Agenda'). Quirk: Stockport's board has merged into a Joint Board with the South East Sector HCP — the page notes that Joint Board materials from April 2026 onward live at southeastsector-hcp.nhs.uk, so this Stockport-only archive covers up to the 02 Oct 2025 meeting and will go stale for newer Joint Board meetings. No JS gallery, no anti-bot.</t>
+        </is>
+      </c>
+      <c r="J166" t="b">
+        <v>0</v>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>wp-content/uploads/;Trust-Board-Meeting-;Public-Documents;DD.MM.YY</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>Private-Agenda;southeastsector-hcp.nhs.uk;Constitution;Scheme-of-Reservation</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>Landing's Previous Board Meetings section has Public Documents PDFs for the 07 Aug 2025 and 02 Oct 2025 Trust Board meetings.</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -9789,13 +11089,35 @@
           <t>https://www.bedfordshirehospitals.nhs.uk/corporate-information/board-meetings-and-directors/board-meetings/</t>
         </is>
       </c>
-      <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Pattern A: the landing page is a chronological list (most recent first) of Board of Directors public meetings, with each dated meeting linking to a single combined 'Meeting Book' PDF that bundles agenda plus all papers. Links are visible in static HTML and come in two equivalent forms: a direct WordPress upload at /wp-content/uploads/&lt;yyyy&gt;/&lt;mm&gt;/Meeting-Book-...-compressed.pdf, and a tidier document-landing slug /documents/meeting-book-board-of-directors-public-meeting-&lt;d-month-yyyy&gt;/ that itself resolves straight to the combined PDF. Filenames vary slightly (e.g. 'Meeting of the Board of Directors', 'Board of Directors in Public', '-compressed', '-V2', '-2' suffixes), so scrape the dated link rather than reconstructing the name. Future meetings appear without links until packs are published. No JS rendering needed.</t>
+        </is>
+      </c>
+      <c r="J170" t="b">
+        <v>0</v>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>/documents/meeting-book-board-of-directors-public-meeting-&lt;d-month-yyyy&gt;/;/wp-content/uploads/&lt;yyyy&gt;/&lt;mm&gt;/Meeting-Book-*.pdf</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr"/>
-      <c r="M170" t="inlineStr"/>
-      <c r="N170" t="inlineStr"/>
-      <c r="O170" t="inlineStr"/>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>Landing page links to single combined Meeting Book PDFs for all 2025 meetings and the Feb and May 2026 meetings; the Feb 2026 document slug resolved directly to a multi-page PDF.</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -9838,13 +11160,39 @@
           <t>https://www.mkuh.nhs.uk/about-us/our-structure/board-of-directors/agendas-and-meetings</t>
         </is>
       </c>
-      <c r="I171" t="inlineStr"/>
-      <c r="J171" t="inlineStr"/>
-      <c r="K171" t="inlineStr"/>
-      <c r="L171" t="inlineStr"/>
-      <c r="M171" t="inlineStr"/>
-      <c r="N171" t="inlineStr"/>
-      <c r="O171" t="inlineStr"/>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Pattern A/F: the stored landing is correct and live; the validator's 403 was anti-bot/WAF blocking its fetcher, not a real breakage (E). The page lists 'Meeting in Public' board packs with dated direct PDF links on the landing itself (no click-through needed). Each meeting is a single combined pack under /wp-content/uploads/YYYY/MM/, named 'Meeting-in-Public-DD.MM.YYYY-...compressed.pdf', sometimes with a separate 'SUPPLEMENTARY-SHELF' pack for the same date. A crawler should take the dated PDF links directly from the landing; future meeting dates (Jul/Sep/Nov 2026 etc.) appear as labels before their packs are posted.</t>
+        </is>
+      </c>
+      <c r="J171" t="b">
+        <v>0</v>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Meeting-in-Public-DD.MM.YYYY;compressed.pdf;/wp-content/uploads/YYYY/MM/;SUPPLEMENTARY-SHELF</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>Council-of-Governors;SUPPLEMENTARY-SHELF (prefer main Meeting-in-Public pack as primary)</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>Landing lists dated combined board packs including May 2026 and March 2026 'Meeting in Public' PDFs; original 403 was a WAF false-positive against the validator.</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -9933,16 +11281,42 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>https://www.westhertshospitals.nhs.uk/about-us/our-board/board-meetings</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr"/>
-      <c r="J173" t="inlineStr"/>
-      <c r="K173" t="inlineStr"/>
-      <c r="L173" t="inlineStr"/>
-      <c r="M173" t="inlineStr"/>
-      <c r="N173" t="inlineStr"/>
-      <c r="O173" t="inlineStr"/>
+          <t>https://www.westhertshospitals.nhs.uk/about-us/our-board/board-papers</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Pattern C/F: the previously stored landing (/our-board/board-meetings) only describes the meeting cycle and links onward to the 'Board papers' child page, which is the real archive. The board-papers page lists per-meeting entries by month/year (May 2026, Mar 2026, Jan 2026, Nov 2025, etc.), each pointing to a single combined board-papers pack served through an opaque CMS download endpoint of the form /download_file/{uuid}/368 (no .pdf extension, UUID not date-derivable). A crawler must read the dated link text on this page to map month-&gt;download URL; there is also a 'Previous board papers' folder link for earlier years.</t>
+        </is>
+      </c>
+      <c r="J173" t="b">
+        <v>0</v>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>/download_file/{uuid}/368;month + year link text maps to pack;single combined board-papers pack per meeting</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>Previous board papers (archive folder, older years)</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>The /board-papers child page lists dated combined packs for May 2026, March 2026 and January 2026 via /download_file/{uuid}/368 endpoints.</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -9982,12 +11356,12 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>https://www.enherts-tr.nhs.uk/gp-professionals/publications/board-papers-september-2023/</t>
+          <t>https://www.enherts-tr.nhs.uk/about/board/board-meetings/</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Strategy: landing shows a weak board-papers signal to a static parser (few dated PDFs found). Papers are likely present but loaded via JS or one click into a 'papers'/'meetings' sub-page. Confirm by following the board-papers / meetings link; prefer the main combined pack. Pattern A/C — review on next pass.</t>
+          <t>Pattern A/F: the previously stored URL was a stale single-PDF resource page (Sept 2023 papers under /gp-professionals/publications/) with no archive navigation. The correct live landing is the 'Board papers &amp; meetings' page under /about/board/board-meetings/, which lists dated public Trust Board packs with direct PDF links on the page. Each meeting is a single combined pack under /wp-content/uploads/YYYY/MM/, named like 'DDMmmYYYY-Public-Board-papers-x.pdf' or 'Public-Trust-Board-papers-DDMmmYY.pdf' (naming is inconsistent across months); extraordinary meetings appear inline. A crawler should take the dated PDF links straight from the landing.</t>
         </is>
       </c>
       <c r="J174" t="b">
@@ -9995,27 +11369,27 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>Board Papers;Agenda and Papers;Public Board Pack</t>
+          <t>/wp-content/uploads/YYYY/MM/;Public-Board-papers;Public-Trust-Board-papers;date in filename (e.g. 13May2026, 14Jan2026)</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+          <t>Extraordinary-Public-Board (use only if it is the relevant meeting);/gp-professionals/publications/ single-doc resource pages</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>papers_partial</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>Validator (static) weak signal: dated_pdfs=1, year_archives=0, meeting_subpages=2; review.</t>
+          <t>Board-meetings landing lists dated combined public board packs for May 2026, March 2026 and January 2026 as direct PDFs.</t>
         </is>
       </c>
     </row>
@@ -10060,13 +11434,39 @@
           <t>https://www.hpft.nhs.uk/about-us/corporate-information-and-governance/</t>
         </is>
       </c>
-      <c r="I175" t="inlineStr"/>
-      <c r="J175" t="inlineStr"/>
-      <c r="K175" t="inlineStr"/>
-      <c r="L175" t="inlineStr"/>
-      <c r="M175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
-      <c r="O175" t="inlineStr"/>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Pattern D/E: the stored landing is correct but the site is Cloudflare/WAF protected and returns 403 to non-browser fetchers (cfemail-obfuscated), so the validator saw 'broken'. Loaded via Playwright (networkidle) the page resolves normally on host www.hpft.nhs.uk. Board packs sit inside a collapsed JS accordion labelled 'Board papers and publications' that must be clicked/expanded; once open it lists dated quarterly public board meeting books with direct PDF links. PDFs are served from opaque /media/{slug}/ paths (slug not date-derivable for recent files, e.g. /media/psnhsr00/...), filenames like 'meeting-book-public-board-of-directors-DDMMYY.pdf'. A crawler must run a headed/JS browser, expand the accordion, then read the dated link text to map meeting date -&gt; /media pack URL.</t>
+        </is>
+      </c>
+      <c r="J175" t="b">
+        <v>1</v>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>/media/{slug}/meeting-book-public-board-of-directors-DDMMYY.pdf;single combined 'meeting book' pack per quarterly meeting;accordion 'Board papers and publications' must be expanded</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>annual-report;quality-account;auditors-annual-report;strategy;wres/wdes/pay-gap and other non-board publications on the same page</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>needs_playwright</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>Behind the JS accordion the page lists dated public board meeting books (21 May 2026, 26 Mar 2026, 22 Jan 2026, 24 Nov 2025) as /media PDFs; Cloudflare 403 only affects non-browser fetchers.</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -10282,13 +11682,39 @@
           <t>https://www.lhch.nhs.uk/board-of-directors-meetings</t>
         </is>
       </c>
-      <c r="I179" t="inlineStr"/>
-      <c r="J179" t="inlineStr"/>
-      <c r="K179" t="inlineStr"/>
-      <c r="L179" t="inlineStr"/>
-      <c r="M179" t="inlineStr"/>
-      <c r="N179" t="inlineStr"/>
-      <c r="O179" t="inlineStr"/>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Pattern C/F: the current landing IS live and correct — the validator missed it because papers are per-meeting download links rather than .pdf hrefs. From the landing a crawler finds a list of dated Board of Directors meetings each with a 'Papers' link of the form https://www.lhch.nhs.uk/resources/download/lhch-&lt;hash&gt; (a redirector that serves the combined agenda+papers PDF); confirmed 2025 meetings (28 Jan, 25 Mar, 29 Apr, 10 Jun, 23 Sep 2025). LHCH is now part of NHS University Hospitals of Liverpool Group, so 2026 meetings are listed as 'Group Board' events pointing at uhliverpool.nhs.uk event pages (15 Jan, 12 Mar 2026), and an archive link goes to the Group board-meetings page; for LHCH-specific dated packs prefer the lhch.nhs.uk /resources/download links. Quirk: download links are opaque hashes, not dated filenames.</t>
+        </is>
+      </c>
+      <c r="J179" t="b">
+        <v>0</v>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>lhch.nhs.uk/resources/download/lhch-&lt;hash&gt;;Tuesday &lt;DD&gt; &lt;Month&gt; 2025 ... Papers;combined agenda+papers PDF per meeting</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>uhliverpool.nhs.uk/about-us/events/details;Council of Governors;Charity</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>Landing lists 2025 Board of Directors meetings each with a working 'Papers' download link plus 2026 Group Board meeting links.</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -10333,7 +11759,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Strategy: WordPress publications-type taxonomy archive. Each meeting is a card linking to a wrapper page at /about/publications/trust-board-meeting-{ordinal-day}-{month}-{year}/. The wrapper page embeds the PDF hosted under /wp-content/uploads/{YYYY}/{MM}/. IMPORTANT: upload-month != meeting-month — PDFs are uploaded 1-3 months after the meeting they document, so do not date-mine from the URL path; use the wrapper slug for the meeting date. Board meets 11 times a year (typically first Thursday of each month except August). Filename patterns shifted in 2024: older 'Trust-Board-Meeting-{Xth}-{month}-{year}.pdf', newer 'Agenda-Documentation-Trust-Board-P1-{d.m.yy}-Website-Version.pdf'. Always follow the wrapper to the actual PDF link rather than guessing filenames. Alternate URL with the same content: /about/publications/?type=board-papers&amp;range=all (filtered view). Old DB URL /about-us/trust-board/ (note the '-us') exists but is a stub that doesn't link to the archive.</t>
+          <t>Pattern A: the current landing IS live and correct — the validator under-counted because only the latest pack is shown by default. From the landing a crawler reaches the most recent dated combined pack directly, e.g. the 5 February 2026 Trust Board public pack at https://www.alderhey.nhs.uk/wp-content/uploads/2026/04/Agenda-Documentation-Trust-Board-Public-Website-Version-5th-February-2026.pdf (single 17MB combined Agenda+Documentation PDF). Older packs live under the same /publications_type/board-papers/ taxonomy and the parent /about/publications/ archive; PDFs are stored under /wp-content/uploads/&lt;YYYY&gt;/&lt;MM&gt;/. Quirk: this is a WordPress publication-type taxonomy listing, so paginate /page/2/ etc. for prior meetings.</t>
         </is>
       </c>
       <c r="J180" t="b">
@@ -10341,17 +11767,17 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>Agenda Documentation Trust Board Public; Trust Board Meeting; P1 Website Version</t>
+          <t>alderhey.nhs.uk/wp-content/uploads/&lt;YYYY&gt;/&lt;MM&gt;/Agenda-Documentation-Trust-Board-Public-Website-Version-&lt;date&gt;.pdf;single combined Agenda+Documentation PDF;Trust Board Public Website Version</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>P2; Private; Confidential; Annexes only; declarations of interest</t>
+          <t>Council of Governors;private board;committee;Charity</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -10361,7 +11787,7 @@
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>WP taxonomy archive lists 115 publications filtered to Board papers. 13 meeting wrappers confirmed in 2025-26. Static HTML, no JS rendering required.</t>
+          <t>Landing shows the 5 February 2026 public Trust Board combined pack PDF with the publications archive linked for prior meetings.</t>
         </is>
       </c>
     </row>
@@ -10576,16 +12002,42 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>https://www.liverpoolwomens.nhs.uk/about-us/board-papers/</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr"/>
-      <c r="J184" t="inlineStr"/>
-      <c r="K184" t="inlineStr"/>
-      <c r="L184" t="inlineStr"/>
-      <c r="M184" t="inlineStr"/>
-      <c r="N184" t="inlineStr"/>
-      <c r="O184" t="inlineStr"/>
+          <t>https://www.uhliverpool.nhs.uk/about-us/meet-our-board/trust-board-meetings</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Pattern B/D/E/F: Liverpool Women's NHS Foundation Trust has merged into NHS University Hospitals of Liverpool Group and its entire liverpoolwomens.nhs.uk site now 301-redirects to a UHL Group hospital landing page with no papers, so the old URL is dead. The single Group Board now covers Liverpool Women's; its board-papers home is the Group Board meetings page on uhliverpool.nhs.uk. A crawler reaches dated packs via the 'Board papers' table of year folders: 2024, 2025 and a 2026 folder (https://www.uhliverpool.nhs.uk/about-us/meet-our-board/trust-board-meetings/navigate/4487/21268#document-library-4487), plus dedicated legacy folders 'Liverpool Women's University Hospital NHS Foundation Trust archive' (navigate/4487/17800) and 'Liverpool University Hospitals NHS Foundation Trust archive'. Recordings list confirms Group Board meetings through March 2026; future meetings (16 Jul 2026 etc.) are event pages. Quirk: site returns HTTP 403 to plain fetchers (anti-bot) so Playwright is required; year folders are JS document-library widgets, and a 'View past events' archive link gives prior meetings.</t>
+        </is>
+      </c>
+      <c r="J184" t="b">
+        <v>1</v>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>uhliverpool.nhs.uk/.../trust-board-meetings/navigate/4487/&lt;id&gt;#document-library-4487;year folders 2024/2025/2026;download_file/view/&lt;id&gt;/&lt;id&gt;;Group Board of Directors meeting &lt;Month&gt; &lt;Year&gt;</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>Council of Governors;Assurance and Risk Committee;Register of Interests;Self-Certification;Charity;about-us/events/details</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>needs_playwright</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>Group Board meetings page (Playwright-confirmed) shows a Board papers table with 2024/2025/2026 year folders and a Liverpool Women's archive folder, plus 2025-2026 meeting recordings.</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -10674,16 +12126,42 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>https://www.eastcheshire.nhs.uk/trust/board/reports-and-meetings/agm</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr"/>
-      <c r="J186" t="inlineStr"/>
-      <c r="K186" t="inlineStr"/>
-      <c r="L186" t="inlineStr"/>
-      <c r="M186" t="inlineStr"/>
-      <c r="N186" t="inlineStr"/>
-      <c r="O186" t="inlineStr"/>
+          <t>https://trust.eastcheshire.nhs.uk/board/reports-and-meetings/meetings</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Pattern A/F: the stored URL pointed at the AGM sub-page (no board packs); the correct live archive is the sibling /board/reports-and-meetings/meetings page. From there a crawler reaches per-meeting combined 'Agenda and papers' PDFs grouped by year (2026, 2025 sections), each linking to https://www.eastcheshire.nhs.uk/application/files/&lt;path&gt;/Public_Trust_Board_-_&lt;Month&gt;_&lt;Year&gt;_-_Agenda_and_Supporting_Papers_Numbered.pdf (or older /download_file/view/ links). Confirmed 2026 (5 Mar, 13 Jan) and 2025 (6 Nov, 4 Sep, 3 Jul, 1 May, 6 Mar, 16 Jan) packs plus a forthcoming 7 May 2026 meeting. Quirk: the public-facing host is trust.eastcheshire.nhs.uk but the PDF assets sit on the www.eastcheshire.nhs.uk /application/files/ CDN path; each link is a single combined Agenda+Supporting Papers PDF.</t>
+        </is>
+      </c>
+      <c r="J186" t="b">
+        <v>0</v>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>eastcheshire.nhs.uk/application/files/.../Public_Trust_Board_-_&lt;Month&gt;_&lt;Year&gt;_-_Agenda_and_Supporting_Papers_Numbered.pdf;eastcheshire.nhs.uk/download_file/view/&lt;id&gt;/&lt;id&gt;;single combined Agenda+Supporting Papers PDF per meeting</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>/reports-and-meetings/agm;/reports-and-meetings/reports;Annual General Meeting;committee</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>The /meetings sub-page lists 2025 and 2026 public Trust Board meetings each with a combined Agenda and Supporting Papers PDF.</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -10925,13 +12403,39 @@
           <t>https://www.lscft.nhs.uk/about-us/board/board-papers</t>
         </is>
       </c>
-      <c r="I190" t="inlineStr"/>
-      <c r="J190" t="inlineStr"/>
-      <c r="K190" t="inlineStr"/>
-      <c r="L190" t="inlineStr"/>
-      <c r="M190" t="inlineStr"/>
-      <c r="N190" t="inlineStr"/>
-      <c r="O190" t="inlineStr"/>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Pattern A: the existing landing page lists dated full board packs as direct download links right on the page; a crawler reaches the latest meeting (e.g. 04.06.2026) without any clicks. Each entry is a single combined 'Board of Directors Public Meeting Pack/Papers' PDF served via /download_file/{id}/1439 redirect endpoints (numeric IDs, no readable date in the URL, so date must be read from link text). Validator missed these because the links are JS/script-rendered download buttons rather than plain &lt;a href*.pdf&gt;. Prefer the largest combined 'Meeting Pack/Papers' PDF per date.</t>
+        </is>
+      </c>
+      <c r="J190" t="b">
+        <v>0</v>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>/download_file/;Public Meeting Pack;Public Board of Directors Meeting Papers;Board of Directors Public Meeting Pack</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>/board (bio index);governors</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>Landing page lists dated 2026 full board packs (05.02.26 through 04.06.2026) as direct download links.</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -11020,40 +12524,40 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>https://www.cwp.nhs.uk/about-us/our-board-and-governors/</t>
+          <t>https://www.cwp.nhs.uk/board</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>Strategy: board papers reachable from this landing; confirm navigation on next deep pass. Prefer the main combined board pack.</t>
+          <t>Pattern C + E + F: original /about-us/our-board-and-governors/ landing returns HTTP 403 to non-browser fetchers (Cloudflare-style anti-bot) and in any case only holds director bios. The live papers route is the 'Board summaries' index at /board, which lists one news-card per meeting (latest 'Board summary Wednesday May 27 2026', plus 28 Jan 2026, 25 Mar 2026, etc.). Each summary sub-page contains a single 'please see the Board agenda pack' link to the full combined public board PDF under /application/files/.../PUBLIC_BoD_Agenda_Pack_Final_DD_MM_YYYY.pdf. So crawl: /board -&gt; per-meeting summary page -&gt; one Agenda Pack PDF (one combined pack per meeting). Whole domain needs Playwright (networkidle) because WebFetch/curl get 403; verify location.host=www.cwp.nhs.uk. Note some older summaries use vanity short URLs (e.g. /mar26, /boardnov25).</t>
         </is>
       </c>
       <c r="J192" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>Public Board Pack;Board Papers;Agenda and Papers</t>
+          <t>PUBLIC_BoD_Agenda_Pack;/application/files/;Board agenda pack;/board/board-summary-</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+          <t>our-board (bio page);our-governors;board-summaries (text-only summary, not the pack);vlog;youtube</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>broken</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>Validator classification: broken.</t>
+          <t>Via Playwright, /board lists dated board summaries and the May 2026 summary links to the full PUBLIC_BoD_Agenda_Pack PDF; domain is anti-bot 403 for plain fetchers.</t>
         </is>
       </c>
     </row>
@@ -11100,7 +12604,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>Strategy: 'Board Meetings in Public' page renders via JS (static body near-empty). Landing shows no direct PDFs; papers are reached through per-meeting sub-pages. Use Playwright (wait_until=networkidle) and follow the meeting links. Pattern C/D.</t>
+          <t>Pattern D (JS-rendered). A static fetch of the 'Board Meetings in Public' landing returns a near-empty body and no PDFs; under headless Chromium it renders on www.blackpoolteachinghospitals.nhs.uk with two onward links — 'Agendas and Reports by Year' (/about-us/meet-board/board-meetings-public/previous-meetings-year) and 'Calendar of Meetings' (/upcoming-meetings). The 'previous-meetings-year' page hosts a JS document-library widget (element id doc-library-53518) rendered as year tabs: '2026/27 Meetings', '2025/26 Meetings', '2024/25 Meetings'. Selecting a year navigates to /previous-meetings-year/navigate/{libId}/{yearId}#doc-library-53518 (libId 53518; yearId e.g. 7416 = 2025/26, 53518/11922 = 2026/27, 2318 = 2024/25) which AJAX-loads that year's dated board packs. Static fetch misses the entire widget and all PDF links — the year tab must be opened via Playwright. Confirmed packs are per-meeting 'Full Papers' PDFs delivered through the CMS download endpoint /download_file/{id}/2316. Cadence is roughly bi-monthly (May, Jul, Sep, Nov, Jan, Mar).</t>
         </is>
       </c>
       <c r="J193" t="b">
@@ -11108,27 +12612,27 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>Board Meetings in Public;Agenda and Papers</t>
+          <t>/about-us/meet-board/board-meetings-public/previous-meetings-year;year tabs: navigate/53518/{yearId}#doc-library-53518 (7416=2025/26, 11922=2026/27, 2318=2024/25);download_file endpoint: blackpoolteachinghospitals.nhs.uk/download_file/{id}/2316;link text 'Board of Directors Meeting in Public - {date} - Full Papers'</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+          <t>/upcoming-meetings (calendar only, no papers);/about-us/meet-board (board membership);/organisational-structure;skip-to / accessibility / #header anchors</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>needs_playwright</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>Renders via JS; landing lists meetings, papers on per-meeting sub-pages.</t>
+          <t>The 2025/26 year tab rendered six dated 'Full Papers' packs spanning 01 May 2025 through 05 March 2026, each via a /download_file/{id}/2316 link.</t>
         </is>
       </c>
     </row>
@@ -11224,35 +12728,35 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>Strategy: board page moved under /about-us/our-trust-board/. The papers page (/about-us/our-trust-board/board-meetings-including-agenda-and-papers) lists current-year meetings and links to per-year archive sub-pages (archive-2022, archive-2023, ...). Papers load via JS, so use Playwright. Pattern C/D + F: old /about-us/board-meetings-... path 404'd after restructure; corrected 2026-05-29.</t>
+          <t>Pattern D listed but actually NOT required: contrary to the prior assumption, a plain static fetch of this URL DOES return the full dated board-papers listing — the page server-renders current-year 'Trust Board (Public Session) Papers' entries plus prior-year sections, each linking to a CMS download endpoint elht.nhs.uk/download_file/{id}/191. The static body already exposes the 2026 packs (May 2026, March 2026, January 2026) and 2025 packs (Jul/Sep/Nov 2025, Jan/Mar 2025) and the forward meeting schedule (next 13 May 2026; then 8 Jul, 9 Sep, 11 Nov 2026, 13 Jan, 10 Mar 2027). The path was corrected on 2026-05-29 to /about-us/our-trust-board/board-meetings-including-agenda-and-papers (old /about-us/board-meetings-... 404'd after restructure). Per-year archive sub-pages (archive-2022, archive-2023, ...) hang off the same path for older material. Because the current packs are reachable statically, a crawler does NOT need Playwright for this org — needs_playwright should be cleared.</t>
         </is>
       </c>
       <c r="J195" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>Trust Board;Agenda and Papers;Part 1</t>
+          <t>elht.nhs.uk/download_file/{id}/191;link text 'Trust Board (Public Session) Papers - {Month} {Year}';older years under /board-meetings-including-agenda-and-papers/archive-{year}</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>Part 2;private;Minutes only</t>
+          <t>/download_file/view/12770/191 (one-off East Kent maternity response, not a board pack);archive-{year} pages when only current FY is wanted</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>needs_playwright</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>Old path 404'd after site restructure; papers now under /our-trust-board/, JS-rendered with year archives.</t>
+          <t>Static fetch returned dated 2025 and 2026 Trust Board public-session papers (e.g. May 2026, March 2026, January 2026) via /download_file/{id}/191 links, so papers are reachable without JS rendering.</t>
         </is>
       </c>
     </row>
@@ -11392,16 +12896,42 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>https://www.neas.nhs.uk/about-us/trust-board</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr"/>
-      <c r="J198" t="inlineStr"/>
-      <c r="K198" t="inlineStr"/>
-      <c r="L198" t="inlineStr"/>
-      <c r="M198" t="inlineStr"/>
-      <c r="N198" t="inlineStr"/>
-      <c r="O198" t="inlineStr"/>
+          <t>https://www.neas.nhs.uk/about-us/trust-board/board-meetings/archive-board-papers</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Pattern C: original /about-us/trust-board landing is a board-overview page with no papers; one click to /board-meetings (latest meeting), and the comprehensive archive lives at /about-us/trust-board/board-meetings/archive-board-papers, which lists per-meeting sub-pages by month+year (March/May/June/September/November 2025, January/March/May 2026). Each month sub-page (e.g. /archive-board-papers/march-2026-board-papers) holds that meeting's agenda and individual paper PDFs. Crawl: archive-board-papers index -&gt; per-month board-papers sub-page -&gt; the PDFs. Note inconsistent case in slugs (January-2026 vs march-2026). NEAS is the Trust's own Board; no ICP/Joint board to filter.</t>
+        </is>
+      </c>
+      <c r="J198" t="b">
+        <v>0</v>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>/archive-board-papers/;board-papers;download_file/view/</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>agm-papers;trust-board (bio overview)</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>Archive page lists dated board-paper sub-pages through to March/May 2026.</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -11441,16 +12971,42 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>https://www.nwas.nhs.uk/publications/board-papers-26-april-2023/</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr"/>
-      <c r="J199" t="inlineStr"/>
-      <c r="K199" t="inlineStr"/>
-      <c r="L199" t="inlineStr"/>
-      <c r="M199" t="inlineStr"/>
-      <c r="N199" t="inlineStr"/>
-      <c r="O199" t="inlineStr"/>
+          <t>https://www.nwas.nhs.uk/about/directors/board-meetings/</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Pattern F + C: old /publications/board-papers-26-april-2023/ URL is now 404; the site reorganised board content under /about/directors/board-meetings/. That landing lists each meeting by date (30 Apr 2025 through 29 Apr 2026) as a clickable link. Newer meetings link straight to a single combined PDF in /wp-content/uploads/YYYY/MM/ (e.g. BoD-Meeting-Pack-29.04.2026.pdf, BoD-Part-1-Agenda-Pack-25.03.26.pdf), while slightly older ones link to a /publications/board-of-directors-papers-DD-month-YYYY/ sub-page that then holds the PDFs. So crawl: board-meetings landing -&gt; either direct wp-content PDF or per-meeting publications sub-page. Prefer the largest combined 'Meeting Pack / Agenda Pack' (Part 1 = public).</t>
+        </is>
+      </c>
+      <c r="J199" t="b">
+        <v>0</v>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>/wp-content/uploads/;BoD-Meeting-Pack;BoD-Part-1-Agenda-Pack;/publications/board-of-directors-papers-</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>Part-2;private;board-papers-26-april-2023 (dead)</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>New board-meetings page lists dated meetings with direct PDF packs up to 29 April 2026.</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -11490,16 +13046,42 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>https://www.yas.nhs.uk/about-us/the-trust-board/</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr"/>
-      <c r="J200" t="inlineStr"/>
-      <c r="K200" t="inlineStr"/>
-      <c r="L200" t="inlineStr"/>
-      <c r="M200" t="inlineStr"/>
-      <c r="N200" t="inlineStr"/>
-      <c r="O200" t="inlineStr"/>
+          <t>https://www.yas.nhs.uk/publications/trust-board-meetings/</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Pattern C (per-meeting sub-pages). The old landing /about-us/the-trust-board/ only lists meeting dates and links onward to /publications/trust-board-meetings/, which is the real archive. That archive lists each public Board meeting by date with year-archive groupings (e.g. board-meeting-papers-2025-26/ and board-meeting-papers-2026-27/) and links to a per-meeting sub-page such as .../board-meeting-26-march-2026/. Each per-meeting sub-page hosts the full set of individual agenda-item PDFs under /media/&lt;id&gt;/&lt;name&gt;.pdf (agenda, minutes, CEO report, IPR, committee assurance reports, etc.). A crawler should follow year-archive -&gt; per-meeting sub-page -&gt; /media/ PDFs; papers are split per item rather than one combined pack.</t>
+        </is>
+      </c>
+      <c r="J200" t="b">
+        <v>0</v>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>/publications/trust-board-meetings/board-meeting-papers-2025-26/;/publications/trust-board-meetings/board-meeting-papers-2026-27/;/board-meeting-&lt;dd&gt;-&lt;month&gt;-&lt;yyyy&gt;/;/media/&lt;id&gt;/&lt;name&gt;.pdf</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>/committees/;/council-of-governors/;/agm</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>Per-meeting sub-pages (e.g. 26 March 2026) host the full set of dated agenda-item PDFs under /media/.</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -11591,13 +13173,39 @@
           <t>https://www.wmas.nhs.uk/about-us/board-papers/</t>
         </is>
       </c>
-      <c r="I202" t="inlineStr"/>
-      <c r="J202" t="inlineStr"/>
-      <c r="K202" t="inlineStr"/>
-      <c r="L202" t="inlineStr"/>
-      <c r="M202" t="inlineStr"/>
-      <c r="N202" t="inlineStr"/>
-      <c r="O202" t="inlineStr"/>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Pattern C: the landing page lists per-meeting publication sub-pages under /publications/, with SEPARATE Agenda and Minutes entries per dated meeting (e.g. 'WMAS Board Meeting Agenda - Wednesday 25th March 2026' and a matching Minutes page). All listings are in static HTML, no JS needed. Quirk: the agenda sub-page renders the agenda as HTML text listing numbered 'Paper 01..nn' items but does NOT publish downloadable PDFs of those papers - it instructs readers to email to request the full board papers. So a crawler can capture the agenda/minutes text but full board-pack PDFs are generally not available for download; prefer the Agenda sub-page for each dated meeting and skip Minutes-only pages when packs are wanted.</t>
+        </is>
+      </c>
+      <c r="J202" t="b">
+        <v>0</v>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>/publications/wmas-board-meeting-agenda-&lt;weekday&gt;-&lt;dd&gt;th-&lt;month&gt;-&lt;year&gt;/;/publications/wmas-board-meeting-minutes-&lt;weekday&gt;-&lt;dd&gt;th-&lt;month&gt;-&lt;year&gt;/</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>wmas-board-meeting-minutes-</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>papers_partial</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>Dated 2025 and 2026 agenda and minutes sub-pages are listed and reachable, but agenda pages show paper titles only and direct readers to email for the actual board-pack PDFs.</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -11640,13 +13248,39 @@
           <t>https://www.eastamb.nhs.uk/about-us/trust-board/public-board-meetings-and-papers</t>
         </is>
       </c>
-      <c r="I203" t="inlineStr"/>
-      <c r="J203" t="inlineStr"/>
-      <c r="K203" t="inlineStr"/>
-      <c r="L203" t="inlineStr"/>
-      <c r="M203" t="inlineStr"/>
-      <c r="N203" t="inlineStr"/>
-      <c r="O203" t="inlineStr"/>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Pattern C (per-meeting sub-pages) with a quirk: the landing /about-us/trust-board/public-board-meetings-and-papers lists each Board meeting date and links to two sub-pages per meeting - a 'public board reports &lt;month&gt; &lt;year&gt;' page (the papers) and an 'in public board minutes &lt;month&gt; &lt;year&gt;' page. The reports sub-page (e.g. /about-us/trust-board/public-board-reports-february-2026) presents the agenda as a table of hyperlinked report titles rather than one combined pack PDF, so a crawler must follow each agenda-item link to reach the documents. Dates 2025-26 (Feb 2025 through Jun 2026) are all listed. Older material is at /about-us/trust-board/in-public-board-minutes-archive. The validator missed this because the landing has no on-page dated PDFs.</t>
+        </is>
+      </c>
+      <c r="J203" t="b">
+        <v>0</v>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>/about-us/trust-board/public-board-reports-&lt;month&gt;-&lt;year&gt;;/about-us/trust-board/in-public-board-minutes-&lt;month&gt;-&lt;year&gt;</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>/annual-general-meeting;/agm-minutes;/committee</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>Landing links to per-meeting 'public board reports' sub-pages for 2025-26 meetings (e.g. Feb 2026, Apr 2026, Jun 2026) which carry the agenda papers.</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -11686,16 +13320,42 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>https://www.secamb.nhs.uk/about-us/board-papers/</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr"/>
-      <c r="J204" t="inlineStr"/>
-      <c r="K204" t="inlineStr"/>
-      <c r="L204" t="inlineStr"/>
-      <c r="M204" t="inlineStr"/>
-      <c r="N204" t="inlineStr"/>
-      <c r="O204" t="inlineStr"/>
+          <t>https://www.secamb.nhs.uk/what-we-do/about-us/trust-board-meeting-dates-and-papers/</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Pattern A/F (wrong-url fixed; dated combined-pack PDFs near the landing). The old stored URL /about-us/board-papers/ redirected to a single stale 2018 document; the live archive is /what-we-do/about-us/trust-board-meeting-dates-and-papers/. That page lists each public Board meeting by date and links directly to combined pack PDFs hosted under /wp-content/uploads/&lt;yyyy&gt;/&lt;mm&gt;/, typically a 'Board-Papers-&lt;date&gt;' (full pack) plus a separate 'Board-Agenda-&lt;date&gt;'. A crawler should grab the largest 'Board-Papers' / 'Trust-Board ... Part-1-Public' PDF per meeting. The archive paginates (~138 publications across ~14 pages). Skip Council of Governors and committee pages.</t>
+        </is>
+      </c>
+      <c r="J204" t="b">
+        <v>0</v>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>/wp-content/uploads/&lt;yyyy&gt;/&lt;mm&gt;/Board-Papers-&lt;date&gt;.pdf;/wp-content/uploads/&lt;yyyy&gt;/&lt;mm&gt;/Trust-Board-&lt;month&gt;-&lt;year&gt;-Part-1-Public.pdf;Board-Public-Papers</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>/council-of-governors/;/committees-of-the-board/;board-meeting-recordings;/board-stories/;Agenda</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>Live archive links directly to dated combined board pack PDFs in /wp-content/uploads/ for Feb 2025 through Apr 2026.</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -11735,16 +13395,42 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>https://www.scas.nhs.uk/about-us/board-of-directors/</t>
-        </is>
-      </c>
-      <c r="I205" t="inlineStr"/>
-      <c r="J205" t="inlineStr"/>
-      <c r="K205" t="inlineStr"/>
-      <c r="L205" t="inlineStr"/>
-      <c r="M205" t="inlineStr"/>
-      <c r="N205" t="inlineStr"/>
-      <c r="O205" t="inlineStr"/>
+          <t>https://www.scas.nhs.uk/document-category/board-papers/</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Pattern A+D (dated combined-pack PDFs, but list is JS-rendered). The human-readable landing /about-scas/our-board/board-meetings/ only shows future meeting dates and an empty archive table ('papers published shortly before each meeting'; older papers via company.secretary@scas.nhs.uk), so it is not crawlable directly. The real document store is the WordPress category page /document-category/board-papers/, but its document list renders client-side (WebFetch saw only chrome), so Playwright (networkidle) is needed to enumerate it. The underlying packs are single combined PDFs under /wp-content/uploads/&lt;yyyy&gt;/&lt;mm&gt;/SCAS-Public-Board-Papers_&lt;date&gt;.pdf (naming varies: SCASpublic-Board-papers_&lt;ddmmyyyy&gt;, SCAS-Trust-Board-Meeting-in-Public-&lt;date&gt;-Bundle). Some meetings also have a separate '...Supporting_Information' or 'Supporting' PDF - prefer the main 'Board-Papers' bundle. Board meets every other month (last Thursday).</t>
+        </is>
+      </c>
+      <c r="J205" t="b">
+        <v>1</v>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>/wp-content/uploads/&lt;yyyy&gt;/&lt;mm&gt;/SCAS-Public-Board-Papers_&lt;date&gt;.pdf;/wp-content/uploads/&lt;yyyy&gt;/&lt;mm&gt;/SCASpublic-Board-papers_&lt;ddmmyyyy&gt;.pdf;SCAS-Trust-Board-Meeting-in-Public-&lt;date&gt;-Bundle</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>Supporting;SupportingInformation;Joint-Committee;/registers-of-interests/</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>Dated combined SCAS public board pack PDFs exist in /wp-content/uploads/ for Jan/Mar/Sep/Nov 2025 and Apr 2026 (verified one is a 7.5MB pack); enumerating the category page needs JS.</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -11784,12 +13470,12 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>https://www.swast.nhs.uk/our-board/board-meeting-schedule-and-public-papers</t>
+          <t>https://www.swast.nhs.uk/board-meeting-schedule-and-public-papers/</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>Strategy: DB URL /our-board/board-meeting-schedule-and-public-papers is JS-rendered (SPA shell, no PDF links in static DOM). The plain path WITHOUT /our-board/ — https://www.swast.nhs.uk/board-meeting-schedule-and-public-papers — is a static HTML page with all dated board pack PDFs ('Board in Public' / 'Board in Public Pack' titles). 12 in-window meetings found. Risk-tracker's follow_subpage strategy hits this correctly.</t>
+          <t>Pattern A (and F: wrong URL fixed) — the validator-flagged URL https://www.swast.nhs.uk/our-board/board-meeting-schedule-and-public-papers returns HTTP 200 but renders no papers (it is the About-us submenu shell), and the /welcome/our-board/ variant 404s; the correct LIVE page is the flat https://www.swast.nhs.uk/board-meeting-schedule-and-public-papers/ on the org's own domain. That landing page lists dated 'Board in Public' agenda-pack PDFs directly (1 May 2025, 3 Jul 2025, 11 Sep 2025, 6 Nov 2025, 8 Jan 2026, 5 Mar 2026, 7 May 2026) plus a forward schedule of upcoming dates whose packs are uploaded ~1 week before each meeting. Quirk: the /download/ PDF hrefs only resolve WITH their query string (?ver=NNNN&amp;doc=docm…pdf); the bare slug (…pdf.pdf) 404s, so packers must keep the full href including the ?ver=&amp;doc= params. PDFs are large (&gt;10MB).</t>
         </is>
       </c>
       <c r="J206" t="b">
@@ -11797,17 +13483,17 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>Board in Public; Board in Public Pack</t>
+          <t>/board-meeting-schedule-and-public-papers/;/download/agenda-pack-board-of-directors-in-public-{date}pdf.pdf?ver=&amp;doc=docm;/download/agenda-pack-board-in-public-{date}pdf.pdf?ver=&amp;doc=docm;Board in Public Pack {month} {year}</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>Confidential; Part 2; Private; Minutes only; Annual Report</t>
+          <t>/our-board/board-meeting-schedule-and-public-papers;/welcome/our-board/;/news/;/publication-scheme/</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -11817,7 +13503,7 @@
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>Real archive at /board-meeting-schedule-and-public-papers (drop /our-board/ prefix). May 2026 and March 2026 packs (15MB + 10MB) both have BAF sections — scores 1299 and 680 are the cleanest BAFs in the entire pilot.</t>
+          <t>Flat landing page lists 2025-26 dated Board-in-Public agenda packs and a 7 May 2026 pack PDF downloaded successfully (exceeded 10MB fetch limit, confirming a real large PDF).</t>
         </is>
       </c>
     </row>

--- a/trust_urls.xlsx
+++ b/trust_urls.xlsx
@@ -779,7 +779,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Pattern D (JS-rendered). The page is correct and current but presents 'Meeting papers' and 'Meeting minutes' as JavaScript dropdown/accordion menus listing each meeting by date (April 2014 through May 2026 confirmed). Static WebFetch sees the dropdown labels but not the underlying PDF hrefs, so a crawler must render JS (Playwright) to expand the 'Meeting papers' selector and harvest the dated PDF links. QVH board meets first Thursday on alternate months. Most recent papers: 14 May 2026, prior 12 March 2026. Filter to 'Meeting papers' (the agenda+papers pack) and skip the separate 'Meeting minutes' dropdown.</t>
+          <t>Current URL is correct. The landing page uses a JS dropdown ('Meeting papers: &lt;date&gt;') rather than visible inline links, which is why the validator saw no dated PDFs. Each dropdown option points to a WordPress upload at /wp-content/uploads/YYYY/MM/Papers-PUBLIC-Board-&lt;DD-Month-YYYY&gt;-...pdf. Coverage spans 2014 to current; recent entries include 14 May 2026, 12 Mar 2026, 12 Feb 2026, 16 Dec 2025. Board meets first Thursday on alternate months. Prefer the single 'Papers-PUBLIC-Board-&lt;date&gt;' bundle; a separate 'Meeting minutes' dropdown exists, filter those out plus pre-2025 files. Because filenames are dated, a crawler can also brute-force the /wp-content/uploads/YYYY/MM/ pattern from the dropdown labels.</t>
         </is>
       </c>
       <c r="J6" t="b">
@@ -787,27 +787,27 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Meeting papers: DD Month YYYY;Board of Directors meeting papers</t>
+          <t>/wp-content/uploads/;Papers-PUBLIC-Board-;FINAL.pdf</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Meeting minutes;Minutes only</t>
+          <t>minutes;Front-cover;/2024/;/2023/;BoD-collated;BOG-</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>papers_found</t>
+          <t>needs_playwright</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Confirmed dated meeting papers in a JS dropdown spanning 2014-May 2026 (latest 14 May 2026, next 2 July 2026).</t>
+          <t>Papers exist and are current (14 May 2026 pack confirmed) but are hidden behind a JS dropdown, so the landing needs rendering or dropdown-value scraping to surface dated PDFs.</t>
         </is>
       </c>
     </row>
@@ -2108,12 +2108,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.nuh.nhs.uk/board-and-board-papers/</t>
+          <t>https://www.nuh.nhs.uk/board-papers</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Pattern B+D (year archives inside a JS/AJAX media browser - needs Playwright). The landing /board-and-board-papers/ shows upcoming meeting dates and links to /board-papers/ which is a VerseOne 'Media browser': a left-hand folder tree by fiscal year (2012/13 ... 2025/26, 2026/27). Clicking a year folder (e.g. /board-papers?media_folder=1466&amp;root_folder=2026/27) reveals dated meeting subfolders (e.g. '1. Thursday 14th May 2026', media_folder=1467), and the meeting folder finally lists the actual PDFs. Static WebFetch only sees the folder shell, not the documents, so Playwright (wait for networkidle, click into year then meeting folder) is required to reach the PDFs. Store the /board-and-board-papers/ landing; crawler should hop to /board-papers/ then drill year -&gt; meeting folder.</t>
+          <t>The registered URL /board-and-board-papers/ is only an info page (meeting dates + governance contact) and correctly shows no PDFs. The actual papers live one level down at /board-papers (linked in that page's sidebar). That index lists year folders as query-string links: /board-papers?media_folder=1422&amp;root_folder=2025/26 and /board-papers?media_folder=1466&amp;root_folder=2026/27. A crawler must follow the media_folder query params to reach per-meeting PDFs (folder contents load dynamically, so render or fetch the folder URLs). Coverage current to 2026/27. Prefer the full board pack/'supporting documents' bundle per meeting; filter out minutes-only and agenda-only files and pre-2025 folders. Point the crawler at root_folder=2026/27 for the latest papers.</t>
         </is>
       </c>
       <c r="J28" t="b">
@@ -2121,17 +2121,17 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Trust Board;agenda;papers;[Month Year] folder</t>
+          <t>/board-papers?media_folder=;root_folder=2026/27;root_folder=2025/26</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Council of Governors;Committee;Minutes only;older fiscal-year folders</t>
+          <t>minutes;agenda-only;2024/25;2023/24</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Playwright confirmed live 2025/26 and 2026/27 folders; drilled into '1. Thursday 14th May 2026' meeting folder showing 'Total results: 2' documents, but PDFs only render via the AJAX media browser.</t>
+          <t>Papers are present in dynamically-loaded year folders (2025/26 and 2026/27) reached via media_folder query params off /board-papers; individual PDFs require rendering the folder view to enumerate.</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Pattern D (JS-rendered listing): a static fetch returns a near-empty body, but under Playwright (location.host www.shropscommunityhealth.nhs.uk) the page renders a &lt;select name="bdts"&gt; 'Meeting dates' dropdown whose options span the current and past five years (e.g. December 2026, October 2026, August 2026, June 2026, May 2026, ... December 2025, AGM September 2025, ... April 2025). Selecting a month triggers a client-side swap that lists that meeting's dated PDFs; the default (most recent) selection currently shows the May 2026 set — '00 Public Agenda 14.05.2026', '01 Board Meetings in Common - 14.05.2026 - Combined papers' and '02 Public Information Pack 14.05.2026' — hosted at /content/doclib/{id}.pdf. A crawler must JS-render the page, enumerate the dropdown option values and, for each, capture the resulting /content/doclib/{id}.pdf links (the trust runs Board Meetings in Common, so packs are combined). Static fetch misses the dropdown and every PDF.</t>
+          <t>The supplied URL is the correct landing (rendered title 'Board meeting papers for Shropshire Community Health NHS Trust'). Static fetch returns empty because the site renders content client-side, so Playwright is required. The CURRENT meeting's papers appear inline near the bottom under a 'Board papers for &lt;Month Year&gt;' heading (currently 'Board papers for May 2026') with 2-3 PDF links; for older meetings use the 'Papers from previous board meetings' dropdown (select month/year, click 'Find') which loads via JS. PDFs are on-domain at content/doclib/NNNNN.pdf. Meetings roughly bi-monthly; dropdown spans 2015-2026. Prefer the combined/full pack ('Combined papers'/'Public Information Pack') over the standalone agenda. Filter the agenda-only PDF and private items; only ~5 years retained.</t>
         </is>
       </c>
       <c r="J33" t="b">
@@ -2444,17 +2444,17 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>/content/doclib/{id}.pdf;Public Agenda {DD.MM.YYYY};Board Meetings in Common - {DD.MM.YYYY} - Combined papers;Public Information Pack {DD.MM.YYYY};select[name=bdts] option values drive the listing</t>
+          <t>content/doclib/;.pdf;Combined papers;Public Information Pack;Board papers for &lt;Month Year&gt;</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>cookies;accessibility;Select meeting</t>
+          <t>Public Agenda;agenda only;minutes</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Playwright rendered the meeting-date dropdown and the default May 2026 selection exposed three dated 14.05.2026 PDFs (Agenda, Combined papers, Information Pack).</t>
+          <t>Inline May 2026 board pack PDFs present (agenda, combined papers, public information pack) plus a 5-year dropdown archive.</t>
         </is>
       </c>
     </row>
@@ -3077,12 +3077,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.dgft.nhs.uk/about-our-trust/our-board/</t>
+          <t>https://www.dgft.nhs.uk/about-our-trust/our-board/board-meetings/</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Pattern C/F. Landing 'Our Board' page is a profiles hub (validator saw only 1 stray PDF). From it follow the one-click child link 'Board Meetings' -&gt; https://www.dgft.nhs.uk/about-our-trust/our-board/board-meetings/ which lists current-year (2025/26 and 2026/27) public board meetings, each a directly linked dated PDF on the trust's own /wp-content/uploads/ path (e.g. 26-05-20_Board_pblc_papersV2-1.pdf). Crawler should grab the 'Public Board Agenda - DD Month YYYY' PDFs. Note: full packs for periods prior to 2025/26 are only available by emailing the Foundation Trust Office, so only ~current year is web-accessible. Static WebFetch reaches everything.</t>
+          <t>The registered URL /about-our-trust/our-board/ is the board-membership page and only links onward; the real papers landing is the /board-meetings/ sub-page. That page statically lists dated meetings with WordPress-hosted PDFs at /wp-content/uploads/YYYY/MM/&lt;YY-MM-DD&gt;_..._papers/agenda.pdf. Confirmed current entries: 20 May 2026, 12 Mar 2026, 15 Jan 2026, 13 Nov 2025. Page is static-fetchable (no render needed). Filenames distinguish 'Public-Board-Agenda' (short) from the full '_Board_pblc_papersV2' pack, PREFER the full papers/pack file, not the agenda-only PDF. Full packs are large (~22MB). Filter out agenda-only, minutes, and pre-2025 files.</t>
         </is>
       </c>
       <c r="J43" t="b">
@@ -3090,17 +3090,17 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Public Board Agenda;Board_pblc_papers;Public Board</t>
+          <t>/wp-content/uploads/;_Board_pblc_papers;_papers;Public-Board</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Council of Governors;Committee;Minutes only;prior to 2025/26 (email only)</t>
+          <t>Public-Board-Agenda;minutes;/2024/;/2023/</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Confirmed dated public board agenda/papers PDFs for Jan, Mar and May 2026 on the org's own domain via the 'Board Meetings' child page.</t>
+          <t>Static page lists dated 2025/2026 board PDFs; confirmed HTTP-200 full public board pack for 20 May 2026 (~22MB).</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Pattern D. Current URL is the canonical official 'Papers from meetings of the Board of Directors' landing page (confirmed top hit on uhb.nhs.uk). It contains no inline PDFs; instead a single link 'View papers from meetings of the Board of Directors' points to a JS-rendered Nextcloud document store at https://docs.uhb.nhs.uk/index.php/s/prTEizKrRnYnjaD. Static WebFetch of that store renders 'No files in here' but exposes a 'Download all files (831.6 MB)' control, proving the file tree is populated but only via the JS Nextcloud client. A crawler must drive the doc store with Playwright (wait_until networkidle) to enumerate the dated meeting folders/PDFs. Note: shared-browser contention prevented a clean live folder enumeration this run, but presence of papers is confirmed by the bulk-download size.</t>
+          <t>The landing page /about/trust-management/bod/papers/ is correct (title 'Papers from meetings of the Board of Directors') but contains almost no content itself, it holds a single link 'View papers from meetings of the Board of Directors' pointing to an external Nextcloud public file share at https://docs.uhb.nhs.uk/index.php/s/prTEizKrRnYnjaD. That share is the actual document store. The landing static-fetches fine but the document listing is fully JS-rendered (Nextcloud Vue app), so a static fetch shows 'No files in here'; render it to enumerate the dated meeting folders/PDFs. To reach current papers: fetch the papers landing, follow the docs.uhb.nhs.uk share link, render it, open the most recent dated folder and download the combined board pack PDF. Prefer the latest 2025/2026 dated board pack; filter out historical years and non-board sub-folders. The old per-meeting .htm pattern is legacy.</t>
         </is>
       </c>
       <c r="J47" t="b">
@@ -3364,17 +3364,17 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Board of Directors;public;agenda and papers;papers pack</t>
+          <t>docs.uhb.nhs.uk/index.php/s/ public share;Nextcloud dated folders/PDFs;bod-meeting-papers-{month}-{year}.htm (legacy)</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Council of Governors;Committee;Minutes only;private/confidential</t>
+          <t>?person=;/news-and-events/;/get-involved/public-meetings/;hgs.uhb.nhs.uk</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Landing page confirmed canonical; papers live in a JS-rendered Nextcloud store (docs.uhb.nhs.uk) whose 831.6MB bulk-download confirms files present but requires Playwright to list.</t>
+          <t>Landing page is correct but papers live in a JS-rendered Nextcloud document store (docs.uhb.nhs.uk) that must be rendered to list dated PDFs.</t>
         </is>
       </c>
     </row>
@@ -3501,12 +3501,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.swbh.nhs.uk/our-trust/trust-board/</t>
+          <t>https://www.swbh.nhs.uk/our-trust/trust-board/public-trust-board-papers/</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Pattern B/C/F. Landing Trust Board hub (validator saw no papers) links one-click to 'Public Trust Board Papers' -&gt; https://www.swbh.nhs.uk/our-trust/trust-board/public-trust-board-papers/ which gives per-year archive links (2026, 2025, 2024). Each year page lists per-month meeting subpages (e.g. /trust-board-paper/may-2/) and each subpage carries ONE combined 'Agenda and papers' PDF on the trust's own /wp-content/uploads/ path (e.g. 26-05-20_BoardAGENDA_pblc_papers.pdf, ~25MB). Crawler: landing -&gt; Public Trust Board Papers -&gt; current year -&gt; month subpage -&gt; take the single large 'BoardAGENDA_pblc_papers' PDF. Static WebFetch reaches all levels.</t>
+          <t>Landing /our-trust/trust-board/public-trust-board-papers/ lists per-year sub-pages (2021-2026), e.g. /public-trust-board-papers-2026/. Each year page lists meetings by month linking to per-meeting sub-pages under /trust-board-paper/{slug}/, and those hold the actual PDFs in /wp-content/uploads/{yyyy}/{mm}/. The trust meets bi-monthly. Static fetch works at every level. Two PDF styles: some meetings publish one combined board book (e.g. May 2026 = 26-05-20_BoardAGENDA_pblc_papers.pdf, ~25MB, prefer this single pack), others publish split numbered papers (000-Agenda, 001-Minutes...). To reach current papers: landing -&gt; 2026 year page -&gt; latest month meeting page -&gt; download the combined boardbook PDF (or all numbered PDFs). Filter out board-meeting-dates, board-members, sub-committees pages.</t>
         </is>
       </c>
       <c r="J49" t="b">
@@ -3514,17 +3514,17 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>BoardAGENDA_pblc_papers;Public Trust Board Papers;agenda and papers</t>
+          <t>/public-trust-board-papers-{year}/;/trust-board-paper/{month-slug}/;wp-content/uploads/{yyyy}/{mm}/...BoardAGENDA_pblc_papers.pdf;wp-content/uploads/{yyyy}/{mm}/000-Agenda...pdf</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Board Meeting Dates;Board Sub-Committees;Minutes only;Council of Governors</t>
+          <t>board-meeting-dates;board-members-and-exec-team;board-sub-comittees;/our-strategy/</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Confirmed a combined public board agenda+papers PDF for the 20 May 2026 meeting via year(2026)-&gt;month subpage navigation on swbh.nhs.uk.</t>
+          <t>2026 year page resolves to per-meeting pages with live 2026 board-pack PDFs (May 2026 combined agenda confirmed, HTTP 200 application/pdf).</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Pattern A/B + F (wrong-url-fixed; org renamed). Kingston Hospital NHS FT merged into Kingston and Richmond NHS Foundation Trust (KRFT), and the old kingstonhospital.nhs.uk board page now redirects to the new domain. New board-meetings page lists 2026 meeting dates and the current combined 'KRFT Trust Board Part 1' pack as a force-download file; older packs are under a linked 'Board paper archive' sub-page (/about-us/trust-board/board-meetings/board-paper-archive). Crawler should take the latest 'Trust Board Part 1' pack (the public part), skipping Part 2/private. Static WebFetch reaches it.</t>
+          <t>Kingston Hospital NHS FT (RAX) merged with Hounslow and Richmond Community Healthcare (RY9) on 1 November 2024 to form Kingston and Richmond NHS Foundation Trust (KRFT) on kingstonandrichmond.nhs.uk, so this group URL is the correct and only board-papers home for Kingston Hospital. The board-meetings page lists upcoming 2026 meetings (7 May, 9 Jul, 3 Sep, 5 Nov) and the latest published pack (May 2026); older packs are under /about-us/trust-board/board-meetings/board-paper-archive (organised by financial year). Pages are static-fetchable. Current-meeting PDFs use download_file/force/{uuid}/354; archive PDFs use download_file/{uuid}/355. One combined 'KRFT Trust Board Part 1' PDF per meeting, prefer that. Filter news/press pages.</t>
         </is>
       </c>
       <c r="J55" t="b">
@@ -3938,17 +3938,17 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>KRFT Trust Board Part 1;Trust Board Part 1;Board papers</t>
+          <t>download_file/force/{uuid}/354 (current meetings);download_file/{uuid}/355 (archive);KRFT Trust Board Part 1 - {Month} {Year}</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Part 2;Private;Confidential;Minutes only</t>
+          <t>/news/;/latest-news/;moderngov.co.uk;afcinfo.org.uk</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Confirmed 2026 board dates and a downloadable '2026-05-07 KRFT Trust Board Part 1 - May 2026' pack on the new Kingston and Richmond domain.</t>
+          <t>May 2026 KRFT Trust Board Part 1 pack live (HTTP 200) on the merged-trust board-meetings page; archive holds dated 2024-2025 packs.</t>
         </is>
       </c>
     </row>
@@ -4501,7 +4501,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Pattern F (wrong-url-fixed) + C (per-meeting/dated combined PDFs). Old url www.hrch.nhs.uk now 301-redirects to www.kingstonandrichmond.nhs.uk because Hounslow and Richmond Community Healthcare NHS Trust merged into Kingston Hospital NHS FT to form Kingston and Richmond NHS Foundation Trust on 1 November 2024 (note: Hounslow community services moved to West London NHS Trust). The successor board is the Kingston and Richmond Trust Board. From the landing page the crawler finds the latest combined pack as a dated download link (e.g. '2026-05-07 KRFT Trust Board Part 1 - May 2026' -&gt; /download_file/force/&lt;uuid&gt;/&lt;n&gt;); older meetings live behind the 'Board paper archive' one-click child at /about-us/trust-board/board-meetings/board-paper-archive. Prefer the largest combined 'Part 1'/public pack PDF per meeting; PDFs are served via opaque /download_file/force/ UUID URLs rather than dated filenames.</t>
+          <t>HRCH (RY9) no longer publishes its own board papers on hrch.nhs.uk, it merged with Kingston Hospital on 1 November 2024 into Kingston and Richmond NHS Foundation Trust (KRFT). The single merged board governs both legacy organisations and its papers live on kingstonandrichmond.nhs.uk, so this group URL is the correct current board-papers home for RY9 (identical to RAX). There is no separate HRCH board; the legacy hrch.nhs.uk site is being wound down. Navigation: board-meetings page for the latest dated 'KRFT Trust Board Part 1' pack (one combined PDF, prefer it), /board-meetings/board-paper-archive for 2023-24 and 2024-25 packs. Static-fetchable. Current PDFs = download_file/force/{uuid}/354; archive = download_file/{uuid}/355. Post-merger packs are shared (not HRCH-specific); pre-Nov-2024 HRCH-only papers exist only on legacy hrch.nhs.uk/Wayback.</t>
         </is>
       </c>
       <c r="J64" t="b">
@@ -4509,17 +4509,17 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>KRFT Trust Board;Trust Board Part 1;Board meeting &lt;Month Year&gt;;Kingston and Richmond</t>
+          <t>download_file/force/{uuid}/354 (current);download_file/{uuid}/355 (archive);KRFT Trust Board Part 1 - {Month} {Year};legacy hrch.nhs.uk (pre-merger only)</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Council of Governors;Part 2;Hounslow community;committee</t>
+          <t>/news/;/latest-news/;moderngov.co.uk;hrch.nhs.uk (legacy, post-merger empty)</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Landing page links a dated May 2026 combined Trust Board Part 1 pack plus a 'Board paper archive' child page on the org's own (successor) domain.</t>
+          <t>Post-merger HRCH papers are the shared KRFT board packs on kingstonandrichmond.nhs.uk; May 2026 pack confirmed live (HTTP 200).</t>
         </is>
       </c>
     </row>
@@ -4647,7 +4647,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Pattern C/D (JS-rendered landing + year-archive drill-down): a static fetch returns a near-empty body and even when JS-rendered (location.host www.bradfordhospitals.nhs.uk) the /our-trust/bod-meetings/ landing has NO direct PDFs — it only lists upcoming meeting dates and a column of per-year archive links 'Previous meetings - {YEAR}' at /our-trust/bod-meetings/previous-meetings-{YEAR}/ (2017 through 2026). The dated board packs live one level down on those year sub-pages: e.g. /previous-meetings-2026/ lists '29 January meeting - Papers', '29 January meeting - Confirmed minutes', '31 March meeting - Papers' and '21 May meeting - Papers', each a WordPress-uploaded PDF under /wp-content/uploads/{YYYY}/{MM}/ (e.g. Boardpack-public-board-29.1.26.pdf, Public-BOD-boardbook-21.5.26.pdf). A crawler must JS-render the landing, follow the current-year 'Previous meetings - {YEAR}' link, then harvest the dated /wp-content/uploads PDFs. Static fetch misses both the year-archive links and all PDFs.</t>
+          <t>The supplied URL is the correct landing (rendered title 'Board of Directors Meetings - Bradford Teaching Hospitals NHS Foundation Trust'). Static fetch returns empty because the page is JS/WordPress-rendered, so Playwright is needed. The landing only lists UPCOMING meeting dates and links to per-year 'Previous meetings - &lt;year&gt;' sub-pages; the actual board pack PDFs live on those sub-pages, notably /our-trust/bod-meetings/previous-meetings-2026/ (and .../previous-meetings-2025/). On each sub-page meetings are grouped by month with a board pack PDF plus a confirmed-minutes file. PDFs on-domain under wp-content/uploads/YYYY/MM/. Coverage 2017-2026. Prefer the file named 'Boardpack', 'boardbook' or 'Public-BOD-boardbook' (the full pack) over the separate minutes; meetings roughly every two months.</t>
         </is>
       </c>
       <c r="J66" t="b">
@@ -4655,17 +4655,17 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>/our-trust/bod-meetings/previous-meetings-{YYYY}/;/wp-content/uploads/{YYYY}/{MM}/*.pdf;Boardpack-public-board-{DD.M.YY}.pdf;Public-BOD-boardbook-{DD.M.YY}.pdf;open-BOD-boardbook-{DD.M.YY}.pdf;confirmed-BOD-open-minutes-{DD.MM.YY}.pdf</t>
+          <t>wp-content/uploads/;boardbook;Boardpack;Public-BOD-boardbook;.pdf;previous-meetings-&lt;year&gt;</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>annual-members-meeting;Select Language;#content</t>
+          <t>minutes;.docx;confirmed-BOD-open-minutes</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Playwright drilled into /previous-meetings-2026/ and confirmed dated 2026 board-pack PDFs for the 29 Jan, 31 Mar and 21 May meetings (papers plus confirmed minutes).</t>
+          <t>2026 sub-page lists Jan/Mar/May 2026 board pack PDFs (e.g. Public-BOD-boardbook-21.5.26.pdf).</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.yorkhospitals.nhs.uk/about-us/board-of-directors/board-of-directors-meetings/</t>
+          <t>https://www.yorkscarborough.nhs.uk/about-us/board-of-directors/board-of-directors-papers/</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Pattern C (per-meeting dated agenda/papers links) reached via one obvious child link. The current landing page itself is mostly schedule text (validator saw no papers), but it links to the child page /about-us/board-of-directors/board-of-directors-papers/ which lists every Board of Directors meeting by date with a direct combined agenda+papers download per meeting (e.g. '30 April 2025', '28 January 2026', '25 March 2026', '29 April 2026', '27 May 2026'). Each link is an opaque /seecmsfile/?id=&lt;n&gt; download serving the combined pack PDF. Crawler should follow the 'board-of-directors-papers' child then take the dated combined pack link; future meetings show 'Agenda (available nearer the time)' with no link until published.</t>
+          <t>The trust has rebranded/migrated its domain from yorkhospitals.nhs.uk to yorkscarborough.nhs.uk; the old /board-of-directors-meetings/ page only lists meeting dates and points to a separate papers sub-page. Go to /board-of-directors-papers/, which lists each meeting (2025/26 and 2026/27) with a per-meeting 'Agenda' link of the form /seecmsfile/?id=NNNN that opens the combined agenda+papers document. Static fetch works (HTML renders the dated list); no JS render needed. Coverage 2025-2026 both present plus upcoming 2026/27 dates. Prefer the most recent past meeting's agenda/papers link; entries marked 'available nearer the time' have no doc yet. Filter out future undated rows and the meetings landing page.</t>
         </is>
       </c>
       <c r="J67" t="b">
@@ -4730,17 +4730,17 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Board of Directors Agendas and Papers;&lt;DD Month YYYY&gt;;Agenda and papers;York and Scarborough</t>
+          <t>/seecmsfile/?id=;Agenda &lt;Month&gt; &lt;Year&gt;;Board of Directors papers</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Council of Governors;Quality Committee;available nearer the time;Late paper</t>
+          <t>board-of-directors-meetings;available nearer the time;#main-content</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Child page board-of-directors-papers lists 2025/26 and 2026/27 dated combined agenda+papers downloads (seecmsfile ids) on the org's own domain.</t>
+          <t>Papers sub-page lists per-meeting seecmsfile agenda/paper links for 2025 and 2026 meetings on the migrated yorkscarborough.nhs.uk domain.</t>
         </is>
       </c>
     </row>
@@ -5593,7 +5593,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Pattern A (dated PDFs on landing). The current url IS the correct live board-papers page for Calderdale and Huddersfield NHS Foundation Trust (title 'Board of Directors Meeting Dates and Papers - CHFT'). It lists each public Board of Directors meeting by date with a single combined 'Agenda and Papers' PDF per meeting, covering full 2026 (Jan/Mar/May with papers; Jul/Sep/Nov scheduled) and all of 2025, plus an in-page archive back to 2015. PDFs live under /fileadmin/site_setup/contentUploads/About_us/Publications/BoardPapers/{year}/Combined_*_Public_Board_of_Directors_*.pdf (TYPO3 fileadmin path). A crawler reads the dated rows directly on the landing page; no click-through needed. Validator missed it because the combined PDF filenames are long and not surfaced as simple dated-PDF links by the heuristic. Quirk: 2026 filenames use 'Combined_-_...WEBSITE.pdf' convention.</t>
+          <t>Current URL is correct and serves dated papers via static fetch (the validator's 'no_papers_visible' was a false negative, the page renders combined PDFs directly inline). The page lists upcoming 2026 dates and past 2025 dates, each with a 'Combined Agenda and Papers' link to a single PDF under /fileadmin/site_setup/contentUploads/About_us/Publications/BoardPapers/&lt;YEAR&gt;/Combined_-_Public_Board_of_Directors_-_&lt;Day_DD_Month_YYYY&gt;_WEBSITE.pdf. Prefer the single combined PDF for the latest past meeting; some future 2026 dates are listed without papers yet. No render needed. Filter rows without a linked PDF and any private/confidential variants.</t>
         </is>
       </c>
       <c r="J80" t="b">
@@ -5601,17 +5601,17 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Combined Public Board of Directors;Agenda and Papers;Public Board of Directors {weekday} {date}</t>
+          <t>/fileadmin/site_setup/contentUploads/About_us/Publications/BoardPapers/;Combined_-_Public_Board_of_Directors_-;_WEBSITE.pdf</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>minutes;committee;Council of Governors;AGM</t>
+          <t>papers not yet posted;upcoming Board meetings</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Landing page lists combined agenda-and-papers PDFs for Jan/Mar/May 2026 and all 2025 meetings, e.g. the 15 January 2026 and 14 May 2026 Public Board of Directors PDFs.</t>
+          <t>Combined public board PDFs for Jan/Mar/May 2026 and all six 2025 meetings link directly from the landing page (validator false negative).</t>
         </is>
       </c>
     </row>
@@ -6208,12 +6208,12 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://www.nwangliaft.nhs.uk/trust-board/</t>
+          <t>https://www.nwangliaft.nhs.uk/our-board-papers/</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Pattern B+D: the current /trust-board/ landing page is valid — it lists 2026 board meeting dates (14 July, 13 Oct, 8 Dec 2026) and a link 'Our Board Papers' to /our-board-papers. That page is a JS-rendered media browser with year folders ('Board Papers 2025', 'Board Papers 2026'); each year expands to monthly subfolders (January/March/May 2026) and only then to the individual agenda/minutes/report PDFs. A static crawler can reach the year/month folder URLs via querystring (?media_folder=ID&amp;root_folder=Board Papers 2026) but the actual PDF list inside each month folder is loaded by JavaScript, so Playwright is needed to enumerate the dated PDFs. Quirk: papers are split into many individual documents per meeting rather than one combined pack.</t>
+          <t>The /trust-board/ page only shows meeting dates plus declarations/gifts PDFs and links onward to 'Our Board Papers' at /our-board-papers/, which is the real archive. That archive is a JS 'media browser' widget with year folders (Board Papers 2022-2026); the year/document list and per-document PDF URLs are injected client-side, so a plain static fetch returns the folder shell with no PDF hrefs, it must be rendered (Playwright/headless) to enumerate the dated agenda/minutes/papers PDFs inside each year folder. Open the 2026 (and 2025) folder, then collect the per-meeting PDFs. Prefer the latest meeting's agenda/papers pack. Filter out 2022-2024 folders and the standing declarations/gifts-and-hospitality PDFs.</t>
         </is>
       </c>
       <c r="J90" t="b">
@@ -6221,27 +6221,27 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Board Papers 2026;Board Papers 2025;Trust Board;agenda;minutes</t>
+          <t>Board Papers 2026;Board Papers 2025;media browser year folder;/download/</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Council of Governors;Gifts Hospitality;Declarations of Interests</t>
+          <t>declarations-of-interests;gifts-hospitality-and-sponsorship;Board Papers 2022;Board Papers 2023;Board Papers 2024</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>papers_partial</t>
+          <t>needs_playwright</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>Confirmed live 'Our Board Papers' media browser with Board Papers 2025 and 2026 year folders containing January/March/May 2026 monthly subfolders, but the individual dated PDFs inside the folders are JS-loaded and not enumerable statically.</t>
+          <t>Archive is a client-rendered media browser exposing 2025 and 2026 board-paper folders but no PDF hrefs in static HTML.</t>
         </is>
       </c>
     </row>
@@ -6753,16 +6753,42 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://www.uhbw.nhs.uk/about-us/board-papers/</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr"/>
+          <t>https://www.uhbw.nhs.uk/p/about-us/trust-board-meetings</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>The registered URL /about-us/board-papers/ is wrong and 500s; the real landing is /p/about-us/trust-board-meetings (older archive at /p/historic-meeting-papers-1). At scan time the entire uhbw.nhs.uk site returned an ASP.NET 'Runtime Error' (transient site-wide outage, not a moved page, since /assets/1/ still served PDFs with HTTP 200). UHBW now meets jointly with North Bristol NHS Trust, so packs are titled 'Public Group Board Meeting' or 'meeting in common (UHBW &amp; NBT)'. Board meets in public every other month; papers published ~1 week before. PDFs sit flat in /assets/1/ with free-text filenames (e.g. public_group_board_meeting_13012026_papers.pdf). Needs render: the landing is ASP.NET/JS, so a crawler should retry the landing when the site recovers and scrape /assets/1/ links, or discover PDFs via site-search. Prefer the single combined '...papers' bundle per meeting; filter out Council of Governors packs, separate agendas, and minutes-only files.</t>
+        </is>
+      </c>
+      <c r="J99" t="b">
+        <v>1</v>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>public_group_board_meeting;board_meeting_in_common_uhbw;agenda_and_papers;_papers.pdf;/assets/1/</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>council_of_governors;minutes;error.aspx;attending-board-meetings</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>Confirmed HTTP-200 dated 2026 PDFs (13 Jan 2026 group board pack, Nov 2025, May 2026), though the landing page itself was down in a site-wide outage at scan time.</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -8114,12 +8140,12 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>https://www.nwl-acute-provider-group.nhs.uk/about-us/board-in-common</t>
+          <t>https://www.nwl-acute-provider-collaborative.nhs.uk/publications</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Pattern C/F. The Hillingdon Hospitals no longer holds a standalone board; it is governed via the North West London Acute Provider Collaborative 'Board in Common' (shared across NWL acute trusts including Hillingdon). The board-in-common landing page describes the body but the dated papers are reached one click via the Events section (/events, anchor #bic), which lists each Board in Common meeting by date with a direct 'Agenda and meeting papers' PDF under /-/media/website/nwl-acute-provider-group/documents/board-in-common/. Historical packs are also on /publications. Because this is a combined Board in Common, the single published pack covers all member trusts (no separate Hillingdon-only board); take the main 'Agenda and meeting papers' combined PDF per meeting and skip the supplementary reading-room item PDFs.</t>
+          <t>Hillingdon does not publish a standalone trust board; it sits in the North West London Acute Provider Collaborative 'Board in Common' (four acute trusts), so its current board papers are the group's Board-in-Common packs. The provider-group site (nwl-acute-provider-group.nhs.uk) only has a 'meet the board' page with no papers; the actual dated packs live on the NWL Acute Provider Collaborative site under /publications (and its /events meeting pages), as single 'full pack'/'agenda and papers' PDFs at /-/media/website/nwl-acute-provider-collaborative/documents/board-in-common/...-full-pack.pdf or agenda-and-papers--board-in-common-public--DDMMYYYY.pdf. The same PDFs are mirrored on imperial.nhs.uk. Confirmed 2026 public meetings: 20 Jan, 28 Apr, 28 Jul. Note imperial.nhs.uk and the collaborative pages may 403 to bare fetchers; fetch the PDF URLs directly or render. Prefer the public 'full pack' for the latest past meeting; ignore the parallel provider-group domain and 'Part 2/confidential' items.</t>
         </is>
       </c>
       <c r="J122" t="b">
@@ -8127,17 +8153,17 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>/documents/board-in-common/;board_in_common;public;agenda-and-meeting-papers;bic</t>
+          <t>/-/media/website/nwl-acute-provider-collaborative/documents/board-in-common/;nwl-apc-board-in-common-public-meeting-DDMMYYYY--full-pack.pdf;agenda-and-papers--board-in-common-public--DDMMYYYY.pdf</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>reading-room;register-of-interests;register_of_interests;learning-from-death</t>
+          <t>nwl-acute-provider-group.nhs.uk/about-us/board-in-common;Part 2;confidential;private</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -8147,7 +8173,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>Events section lists dated Board in Common meetings (28 April 2026 with a direct public agenda+papers PDF; 28 Jul, 20 Oct 2026 and 26 Jan 2027 scheduled).</t>
+          <t>Board-in-Common full-pack PDFs for 20 Jan 2026 and 28 Apr 2026 (covering Hillingdon) are published on the NWL Acute Provider Collaborative site.</t>
         </is>
       </c>
     </row>
@@ -9062,7 +9088,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Pattern B/A (fiscal-year sections with per-meeting dated PDFs on landing). The current URL is correct; the validator missed it (likely JS-light rendering of the lists). The page groups meetings by fiscal year ('2026/27', '2025/26', '2024/25' ... back to '2019/20'), each entry formatted '[Date] - [Agenda and papers]' linking to a combined pack PDF. Most recent listed includes 5 February 2026 and 2026/27 dates (June/April 2026). A crawler should pick the latest fiscal-year block and take the newest 'Agenda and papers' link (the combined pack). This is the org's own Board (single trust board, no ICP/cluster ambiguity).</t>
+          <t>This IS the correct live board-papers archive; the validator's 'no_papers_visible' was a false negative because the dated links render as guid-keyed download endpoints (/download_file/view/{uuid}/668) rather than plain .pdf hrefs. The page lists 'Agenda and papers' entries grouped by financial year (2026/27 and 2025/26: 4 Jun 2026, 2 Apr 2026, 5 Feb 2026, 4 Dec 2025, 2 Oct 2025, 7 Aug 2025, 5 Jun 2025, 3 Apr 2025). Each is a single combined agenda+papers download. Static fetch works for the listing, but a crawler must capture the /download_file/view/{uuid}/668 hrefs (NOT .pdf-suffixed) and map each to its month+year label; prefer the most recent 'Agenda and papers' link. Filter to the '/668' download namespace.</t>
         </is>
       </c>
       <c r="J137" t="b">
@@ -9070,7 +9096,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>Agenda and papers;2026/27;2025/26</t>
+          <t>/download_file/view/{uuid}/668;Agenda and papers;&lt;day&gt; &lt;Month&gt; &lt;YYYY&gt;</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -9080,7 +9106,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -9090,7 +9116,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>Landing page lists fiscal-year sections with 'Agenda and papers' links including 5 February 2026 and 2026/27 dates.</t>
+          <t>Page lists multiple dated 2025-2026 'Agenda and papers' download links keyed by financial year (validator false negative).</t>
         </is>
       </c>
     </row>
@@ -9354,12 +9380,12 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>https://www.southtees.nhs.uk/about/university-hospitals-tees/board-meetings/</t>
+          <t>https://www.southtees.nhs.uk/resources/?topic=board-of-directors</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Pattern B/C with a quirk: this is the canonical group board landing for the University Hospitals Tees Group Board (shared between South Tees RTR and North Tees RVW). The landing itself shows only the next upcoming meeting date plus a 'View meeting agenda archive' link; dated papers are one click away via the resources archive at https://www.southtees.nhs.uk/resources/?for=&amp;topic=hospital-group&amp;type=agendas&amp;audience=all which lists per-meeting pages titled 'Group Board of Directors Agenda - &lt;date&gt;'. Each per-meeting page (e.g. /resources/group-board-of-directors-agenda-5-march-2026/) links to a single combined Agenda+Papers PDF under /wp-content/uploads/&lt;yyyy&gt;/&lt;mm&gt;/. The old stored URL was a stale 2022 single-meeting resource page. Crawler should follow the agenda archive filter, then per-meeting subpages, then the combined PDF.</t>
+          <t>South Tees and North Tees now run a single joint 'University Hospitals Tees' (UHT) group board, so the papers are GROUP packs published on the South Tees domain. The current /about/university-hospitals-tees/board-meetings/ landing is just a description page and shows no PDFs directly. The real archive is the resources filter /resources/?topic=board-of-directors, which lists 'Group Board of Directors Agenda - &lt;date&gt;' entries (7 May 2026, 5 Mar 2026, 8 Jan 2026, 6 Nov 2025, 3 Jul 2025...). Each entry is a per-meeting sub-page (e.g. /resources/group-board-of-directors-agenda-5-march-2026/) containing the direct combined papers PDF under /wp-content/uploads/{YYYY}/{MM}/. Crawler path: load the resources filter -&gt; follow each 'group-board-of-directors-agenda-{date}' sub-page -&gt; grab the /wp-content/uploads/.../Board-of-Directors-papers-*.pdf (or UHT-Board-Public-Papers-*.pdf) link. Static fetch sufficient. Prefer the single combined 'papers' PDF; filter committee/quality-assurance items.</t>
         </is>
       </c>
       <c r="J142" t="b">
@@ -9367,17 +9393,17 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>Group Board of Directors Agenda - &lt;date&gt;;Board-of-Directors-papers-&lt;date&gt;.pdf;/resources/group-board-of-directors-agenda-;/wp-content/uploads/&lt;yyyy&gt;/&lt;mm&gt;/</t>
+          <t>/resources/group-board-of-directors-agenda-{date}/;/wp-content/uploads/{YYYY}/{MM}/Board-of-Directors-papers-{date}.pdf;/wp-content/uploads/{YYYY}/{MM}/UHT-Board-Public-Papers-{date}.pdf</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>register-of-interests;declaration-of-interest;council-of-governors;/news/;/events/</t>
+          <t>minutes;committee</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -9387,7 +9413,7 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>Canonical group board landing reached the archive listing per-meeting pages with confirmed combined PDFs for 5 March 2026, 8 January 2026 and 7 May 2026.</t>
+          <t>Resources filter lists dated UHT group board agendas/papers and a confirmed 5 March 2026 papers PDF resolves on the southtees.nhs.uk domain.</t>
         </is>
       </c>
     </row>
@@ -9429,12 +9455,12 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>https://www.nth.nhs.uk/about/university-hospitals-tees/board-meetings/</t>
+          <t>https://www.southtees.nhs.uk/resources/?topic=board-of-directors</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Pattern B/C with a quirk: this is the canonical group board landing for the University Hospitals Tees Group Board (shared between North Tees RVW and South Tees RTR). The old stored URL https://www.nth.nhs.uk/about/board-meetings/ 301-redirects to /about/board/ which is only a stale Declaration of Interest register page (validator false-positive). The new landing lists upcoming meeting dates (e.g. 8 Jan 2026, 5 Mar 2026) and links to the group board papers archive at https://www.nth.nhs.uk/resources/?search=&amp;department=all&amp;type=board-papers&amp;range=all&amp;custom_range= which lists per-meeting pages titled 'Board of directors papers - &lt;date&gt;'. Each subpage links to a single combined public papers PDF under /wp-content/uploads/&lt;yyyy&gt;/&lt;mm&gt;/ (e.g. ~15MB). Crawler should follow the board-papers resource filter, then per-meeting subpage, then combined PDF.</t>
+          <t>RVW (North Tees) shares the same single University Hospitals Tees group board with South Tees, so the authoritative dated packs live on the South Tees domain, NOT the nth.nhs.uk page. The nth.nhs.uk board-meetings page only lists future event stubs plus a 'Group board papers' resources link, hence 'papers_partial'. The complete combined UHT group packs are hosted on southtees.nhs.uk under /wp-content/uploads/{YYYY}/{MM}/. Point the crawler at the South Tees resources filter (same group pack as RTR) since these UHT packs cover both trusts. Navigation: resources filter -&gt; per-meeting 'group-board-of-directors-agenda-{date}' sub-page -&gt; direct papers PDF. Static fetch works; prefer the combined public papers PDF; dedupe against RTR since it is the same physical pack.</t>
         </is>
       </c>
       <c r="J143" t="b">
@@ -9442,17 +9468,17 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>Board of directors papers - &lt;date&gt;;Public-board-papers-&lt;date&gt;.pdf;Board-of-Directors-Thursday-&lt;date&gt;-final-papers.pdf;/resources/board-of-directors-papers-;/wp-content/uploads/&lt;yyyy&gt;/&lt;mm&gt;/</t>
+          <t>/resources/group-board-of-directors-agenda-{date}/;/wp-content/uploads/{YYYY}/{MM}/UHT-Board-Public-Papers-{date}.pdf;/wp-content/uploads/{YYYY}/{MM}/Board-of-Directors-papers-{date}.pdf</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>declaration-of-interest;/about/board/;register-of-interests;/news/</t>
+          <t>minutes;committee;/about/events/</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -9462,7 +9488,7 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>New canonical landing lists upcoming dates and links to a board-papers archive; confirmed combined PDFs for 7 May 2026, 5 March 2026 and 8 January 2026.</t>
+          <t>Same UHT group board as South Tees; dated 2026 group packs confirmed on the shared southtees.nhs.uk domain.</t>
         </is>
       </c>
     </row>
@@ -10468,25 +10494,25 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Pattern A/D (validator false-negative): the stored landing IS correct and current. It directly lists all 2025 and 2026 board meeting dates each with a 'Papers' link, 'Minutes' link and YouTube video. The validator reported no_papers_visible because the date/papers list is rendered client-side, but WebFetch confirmed it is populated. Each 'Papers' link is a numeric download endpoint of the form /download_file/view/&lt;id&gt;/875 returning the combined meeting pack PDF. Crawler may need light JS rendering but the links resolve directly; no per-meeting subpages needed.</t>
+          <t>This IS the correct live board-papers page; the validator's 'no_papers_visible' was a false negative because each meeting links via a numeric download endpoint (/download_file/view/{id}/875) rather than a .pdf URL. The page lists every public board meeting with separate 'Papers', 'Minutes' and 'Video' links: upcoming (6 May 2026 papers live) and completed (4 Mar 2026, 14 Jan 2026, 5 Nov 2025, 3 Sep 2025, 2 Jul 2025, 7 May 2025, 2 Apr 2025). Crawler path: scrape the page, capture the 'Papers' /download_file/view/{id}/875 hrefs, map to the adjacent meeting date; prefer 'Papers' over 'Minutes'/'Video'. Static fetch sufficient. Filter to the '/875' namespace and anchor text 'Papers'.</t>
         </is>
       </c>
       <c r="J161" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>/download_file/view/&lt;id&gt;/875;&lt;date&gt; Papers;board-dates-and-papers</t>
+          <t>/download_file/view/{id}/875;Papers;&lt;day&gt; &lt;Month&gt; &lt;YYYY&gt;</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>youtu.be;youtube.com;Minutes;Video</t>
+          <t>Minutes;Video;youtu;youtube.com</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -10496,7 +10522,7 @@
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>Landing directly lists 2025-26 board dates with working Papers download links (e.g. 6 May 2026, 4 March 2026, 14 January 2026); validator missed the JS-rendered list.</t>
+          <t>Page lists dated 2025-2026 board meetings each with a 'Papers' download link in the /875 namespace (validator false negative).</t>
         </is>
       </c>
     </row>
@@ -10693,7 +10719,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Pattern A/C (dated combined bundles directly on the landing). The validator saw no_papers_visible, but the current url (which 301s to https://www.wwl.nhs.uk/board-papers) actually lists upcoming Board of Directors meeting dates and, for held meetings, a single combined 'Public Bundle' PDF per meeting stored under /media/board/Papers/&lt;year&gt;/. A crawler reaches dated 2026 papers directly from this landing via the per-meeting PDF links; older years are behind a 'Board Papers Archive' link at /board-papers-archive. The validator likely missed the PDFs because filenames carry dates in DD.MM.YY form and links sit in an expandable meetings list. No JS gallery, no anti-bot.</t>
+          <t>Static-fetch friendly; no render needed. The landing page (canonical also at /board-papers) lists the current calendar year's Board of Directors meetings, each linking directly to a single combined public bundle PDF (no per-meeting sub-pages). Prefer the 'Public Bundle'/'Public meeting bundle' PDF per date; ignore private/agenda-only. Prior years (2019-2025) live on the sibling archive at /board-papers-archive. PDFs sit under /media/board/Papers/{YEAR}/. The validator likely saw later-2026 dates whose papers were not yet published; Feb and Apr 2026 bundles are live.</t>
         </is>
       </c>
       <c r="J164" t="b">
@@ -10701,17 +10727,17 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>/media/board/Papers/;Public Bundle;Public bundle;DD.MM.YY;RFS.pdf</t>
+          <t>/media/board/Papers/{YEAR}/;Public Bundle DD.MM.YY;Public meeting bundle</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>board-papers-archive;Private</t>
+          <t>Private Agenda;Private Bundle;board-papers-archive (older years)</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -10721,7 +10747,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>Landing lists combined Public Bundle PDFs for the 04 Feb 2026 and 01 Apr 2026 Board of Directors meetings under /media/board/Papers/2026/.</t>
+          <t>Two live 2026 public board bundle PDFs (Feb, Apr 2026) and a full 2025 set on the archive page confirmed on static fetch.</t>
         </is>
       </c>
     </row>
@@ -10817,7 +10843,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Pattern C (per-meeting PDFs on the landing). The validator flagged papers_partial, but the current url lists forthcoming meeting dates and a 'Previous Board Meetings' section with per-meeting PDFs (Public Documents and Private Agenda) for 2025 stored under /wp-content/uploads/&lt;year&gt;/&lt;month&gt;/. A crawler reaches dated papers directly from this landing by taking the '&lt;...&gt; Public Documents' PDF for each previous meeting (skip the matching 'Private Agenda'). Quirk: Stockport's board has merged into a Joint Board with the South East Sector HCP — the page notes that Joint Board materials from April 2026 onward live at southeastsector-hcp.nhs.uk, so this Stockport-only archive covers up to the 02 Oct 2025 meeting and will go stale for newer Joint Board meetings. No JS gallery, no anti-bot.</t>
+          <t>Static-fetch friendly. GOVERNANCE CHANGE: from 1 April 2026 Stockport FT and Tameside &amp; Glossop ICFT delegated authority to a Joint Board Committee ('South East Sector Health Care Partnership'); this Stockport page now hosts only legacy single-trust packs up to ~Oct 2025 (each a combined 'Public Documents' PDF per meeting) and redirects April-2026-onward Joint Board packs to the partnership site https://www.southeastsector-hcp.nhs.uk/ (single-page; lists Joint Board dates with packs served from the tamesideandglossopicft.nhs.uk/download_file/{id}/0 domain, an official partner site). To reach current 2026 papers a crawler must follow the partnership link. Prefer 'Public Documents'/'Joint Public Board Meeting Pack' PDFs; ignore 'Private Agenda'. Consider the partnership URL as a secondary source.</t>
         </is>
       </c>
       <c r="J166" t="b">
@@ -10825,17 +10851,17 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>wp-content/uploads/;Trust-Board-Meeting-;Public-Documents;DD.MM.YY</t>
+          <t>Trust Board Meeting DD.MM.YY - Public Documents;Joint Public Board Meeting Pack - {Month} 2026;tamesideandglossopicft.nhs.uk/download_file/{id}/0</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>Private-Agenda;southeastsector-hcp.nhs.uk;Constitution;Scheme-of-Reservation</t>
+          <t>Private Agenda;Constitution;Scheme of Reservation</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -10845,7 +10871,7 @@
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>Landing's Previous Board Meetings section has Public Documents PDFs for the 07 Aug 2025 and 02 Oct 2025 Trust Board meetings.</t>
+          <t>2025 single-trust public packs on the Stockport page and a live June 2026 Joint Public Board Meeting Pack on the partnership site confirmed.</t>
         </is>
       </c>
     </row>
@@ -11684,7 +11710,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Pattern C/F: the current landing IS live and correct — the validator missed it because papers are per-meeting download links rather than .pdf hrefs. From the landing a crawler finds a list of dated Board of Directors meetings each with a 'Papers' link of the form https://www.lhch.nhs.uk/resources/download/lhch-&lt;hash&gt; (a redirector that serves the combined agenda+papers PDF); confirmed 2025 meetings (28 Jan, 25 Mar, 29 Apr, 10 Jun, 23 Sep 2025). LHCH is now part of NHS University Hospitals of Liverpool Group, so 2026 meetings are listed as 'Group Board' events pointing at uhliverpool.nhs.uk event pages (15 Jan, 12 Mar 2026), and an archive link goes to the Group board-meetings page; for LHCH-specific dated packs prefer the lhch.nhs.uk /resources/download links. Quirk: download links are opaque hashes, not dated filenames.</t>
+          <t>Static-fetch friendly; correct landing. LHCH remains an independent FT (NOT a member of the UHL Group, the page only cross-links to uhliverpool.nhs.uk Group Board for context). Current-year Board of Directors meeting dates are listed, each linking DIRECTLY to a combined papers PDF (resource-download URLs, not sub-pages); below them sits a chronological archive 2015-2024. The validator's 'papers_partial' reflects that 2026 own-trust dates were not yet scheduled at scan time while a full 2025 set (Jan-Sep 2025) is present. Prefer the single combined 'agenda and papers' PDF per date; filter out the Group Board cross-links (uhliverpool.nhs.uk) which are a separate org. No render required.</t>
         </is>
       </c>
       <c r="J179" t="b">
@@ -11692,17 +11718,17 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>lhch.nhs.uk/resources/download/lhch-&lt;hash&gt;;Tuesday &lt;DD&gt; &lt;Month&gt; 2025 ... Papers;combined agenda+papers PDF per meeting</t>
+          <t>agenda and papers (combined PDF per meeting date);resource download links</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>uhliverpool.nhs.uk/about-us/events/details;Council of Governors;Charity</t>
+          <t>uhliverpool.nhs.uk (Group Board - separate org);governor-meetings</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -11712,7 +11738,7 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>Landing lists 2025 Board of Directors meetings each with a working 'Papers' download link plus 2026 Group Board meeting links.</t>
+          <t>Full 2025 Board of Directors meeting papers (Jan-Sep 2025) link directly from the page; 2026 dates populate the same list.</t>
         </is>
       </c>
     </row>
@@ -11759,7 +11785,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Pattern A: the current landing IS live and correct — the validator under-counted because only the latest pack is shown by default. From the landing a crawler reaches the most recent dated combined pack directly, e.g. the 5 February 2026 Trust Board public pack at https://www.alderhey.nhs.uk/wp-content/uploads/2026/04/Agenda-Documentation-Trust-Board-Public-Website-Version-5th-February-2026.pdf (single 17MB combined Agenda+Documentation PDF). Older packs live under the same /publications_type/board-papers/ taxonomy and the parent /about/publications/ archive; PDFs are stored under /wp-content/uploads/&lt;YYYY&gt;/&lt;MM&gt;/. Quirk: this is a WordPress publication-type taxonomy listing, so paginate /page/2/ etc. for prior meetings.</t>
+          <t>Static-fetch friendly; correct landing (WordPress 'publications_type/board-papers' archive; breadcrumb Home&gt;About us&gt;Publications&gt;Board papers). Each Trust Board meeting is one combined public bundle PDF stored under /wp-content/uploads/{YEAR}/{MM}/ with filenames like 'Agenda-Documentation-Trust-Board-Public-Website-Version-{date}.pdf'. The page shows the latest meeting (5 Feb 2026) prominently; older meetings appear as additional entries (no numbered pagination, so read all entries on the page). Note the upload-year folder can lag the meeting date (Feb 2026 pack sits in /2026/04/). Prefer the 'Public Website Version' bundle; no private papers exposed here. No render needed.</t>
         </is>
       </c>
       <c r="J180" t="b">
@@ -11767,17 +11793,17 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>alderhey.nhs.uk/wp-content/uploads/&lt;YYYY&gt;/&lt;MM&gt;/Agenda-Documentation-Trust-Board-Public-Website-Version-&lt;date&gt;.pdf;single combined Agenda+Documentation PDF;Trust Board Public Website Version</t>
+          <t>/wp-content/uploads/{YEAR}/{MM}/Agenda-Documentation-Trust-Board-Public-Website-Version-{date}.pdf;Trust Board Meeting - {date}</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>Council of Governors;private board;committee;Charity</t>
+          <t>other publications_type categories;/about/publications/ (parent index)</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -11787,7 +11813,7 @@
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>Landing shows the 5 February 2026 public Trust Board combined pack PDF with the publications archive linked for prior meetings.</t>
+          <t>Live 5 Feb 2026 Trust Board public bundle PDF confirmed on the board-papers archive page.</t>
         </is>
       </c>
     </row>
@@ -12131,7 +12157,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Pattern A/F: the stored URL pointed at the AGM sub-page (no board packs); the correct live archive is the sibling /board/reports-and-meetings/meetings page. From there a crawler reaches per-meeting combined 'Agenda and papers' PDFs grouped by year (2026, 2025 sections), each linking to https://www.eastcheshire.nhs.uk/application/files/&lt;path&gt;/Public_Trust_Board_-_&lt;Month&gt;_&lt;Year&gt;_-_Agenda_and_Supporting_Papers_Numbered.pdf (or older /download_file/view/ links). Confirmed 2026 (5 Mar, 13 Jan) and 2025 (6 Nov, 4 Sep, 3 Jul, 1 May, 6 Mar, 16 Jan) packs plus a forthcoming 7 May 2026 meeting. Quirk: the public-facing host is trust.eastcheshire.nhs.uk but the PDF assets sit on the www.eastcheshire.nhs.uk /application/files/ CDN path; each link is a single combined Agenda+Supporting Papers PDF.</t>
+          <t>This is the correct board-papers landing and is static-fetchable (no render needed). The page lists each meeting by date with a direct link to a single combined 'Public Trust Board - [Month Year] - Agenda and Supporting Papers Numbered' PDF. CRITICAL: the landing lives on trust.eastcheshire.nhs.uk but every PDF is hosted on the bare domain www.eastcheshire.nhs.uk (either /application/files/&lt;path&gt;.pdf or /download_file/&lt;id&gt;/328 redirect links), a crawler must follow links rather than assume same-host. Coverage strong: 2025 (Jan, Mar, May, Jul, Sep, Nov) and 2026 (Jan, Mar, forthcoming May). Prefer the single 'Agenda and Supporting Papers Numbered' PDF per meeting. Bimonthly cadence (odd months).</t>
         </is>
       </c>
       <c r="J186" t="b">
@@ -12139,17 +12165,17 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>eastcheshire.nhs.uk/application/files/.../Public_Trust_Board_-_&lt;Month&gt;_&lt;Year&gt;_-_Agenda_and_Supporting_Papers_Numbered.pdf;eastcheshire.nhs.uk/download_file/view/&lt;id&gt;/&lt;id&gt;;single combined Agenda+Supporting Papers PDF per meeting</t>
+          <t>www.eastcheshire.nhs.uk/application/files/&lt;path&gt;/Public_Trust_Board_-_&lt;Month&gt;_&lt;Year&gt;_-_Agenda_and_Supporting_Papers_Numbered.pdf;www.eastcheshire.nhs.uk/download_file/view/&lt;id&gt;/328;www.eastcheshire.nhs.uk/download_file/&lt;id&gt;/328</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>/reports-and-meetings/agm;/reports-and-meetings/reports;Annual General Meeting;committee</t>
+          <t>/non-exec;minutes-only;committee-;private;confidential</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -12159,7 +12185,7 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>The /meetings sub-page lists 2025 and 2026 public Trust Board meetings each with a combined Agenda and Supporting Papers PDF.</t>
+          <t>Multiple confirmed 2025-2026 dated full board-pack PDFs are directly linked from the landing page (hosted on www.eastcheshire.nhs.uk).</t>
         </is>
       </c>
     </row>
@@ -12405,7 +12431,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>Pattern A: the existing landing page lists dated full board packs as direct download links right on the page; a crawler reaches the latest meeting (e.g. 04.06.2026) without any clicks. Each entry is a single combined 'Board of Directors Public Meeting Pack/Papers' PDF served via /download_file/{id}/1439 redirect endpoints (numeric IDs, no readable date in the URL, so date must be read from link text). Validator missed these because the links are JS/script-rendered download buttons rather than plain &lt;a href*.pdf&gt;. Prefer the largest combined 'Meeting Pack/Papers' PDF per date.</t>
+          <t>Correct landing, the validator's 'no_papers_visible' is a false negative: the page renders a full dated table of 'Board of Directors Public Meeting Papers - DD.MM.YY' rows, each linking to a single combined pack PDF via /download_file/&lt;id&gt;/1439. A plain HTTP fetch surfaces the table fine (likely a render-timing/short-snippet issue at validation); treat as static-fetchable with a harmless render fallback. Coverage current and forward-dated: 2026 Feb, Mar, Apr, May, Jun all present, plus 2024 H2 archive. Prefer the single 'Public Meeting Papers/Pack' PDF per date. Filter out committee/private items; monthly-ish cadence first Thursday.</t>
         </is>
       </c>
       <c r="J190" t="b">
@@ -12413,17 +12439,17 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>/download_file/;Public Meeting Pack;Public Board of Directors Meeting Papers;Board of Directors Public Meeting Pack</t>
+          <t>www.lscft.nhs.uk/download_file/&lt;id&gt;/1439</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>/board (bio index);governors</t>
+          <t>committee;private;confidential;minutes-only</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -12433,7 +12459,7 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>Landing page lists dated 2026 full board packs (05.02.26 through 04.06.2026) as direct download links.</t>
+          <t>Full dated 2025-2026 board-pack PDF table is present on the page despite the validator flag.</t>
         </is>
       </c>
     </row>
@@ -12604,7 +12630,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>Pattern D (JS-rendered). A static fetch of the 'Board Meetings in Public' landing returns a near-empty body and no PDFs; under headless Chromium it renders on www.blackpoolteachinghospitals.nhs.uk with two onward links — 'Agendas and Reports by Year' (/about-us/meet-board/board-meetings-public/previous-meetings-year) and 'Calendar of Meetings' (/upcoming-meetings). The 'previous-meetings-year' page hosts a JS document-library widget (element id doc-library-53518) rendered as year tabs: '2026/27 Meetings', '2025/26 Meetings', '2024/25 Meetings'. Selecting a year navigates to /previous-meetings-year/navigate/{libId}/{yearId}#doc-library-53518 (libId 53518; yearId e.g. 7416 = 2025/26, 53518/11922 = 2026/27, 2318 = 2024/25) which AJAX-loads that year's dated board packs. Static fetch misses the entire widget and all PDF links — the year tab must be opened via Playwright. Confirmed packs are per-meeting 'Full Papers' PDFs delivered through the CMS download endpoint /download_file/{id}/2316. Cadence is roughly bi-monthly (May, Jul, Sep, Nov, Jan, Mar).</t>
+          <t>The supplied URL is the correct landing (rendered title 'Board Meetings in Public :: Blackpool Teaching Hospitals'). Static fetch returns empty because the site (Granicus-style CMS) renders the document library client-side, so Playwright is required. The landing is only a hub of explanatory text; to reach dated papers follow 'Agendas and Reports by Year' at /about-us/meet-board/board-meetings-public/previous-meetings-year, which lists fiscal-year folders. Click a year (e.g. '2026/27 Meetings' or '2025/26 Meetings'); the URL takes the form .../previous-meetings-year/navigate/53518/&lt;id&gt;#doc-library-53518 and renders a table of 'Board of Directors' Meeting in Public, &lt;date&gt; - Full Papers' rows. PDFs served extension-less via /download_file/&lt;docid&gt;/2316. Coverage 2018/19 through 2026/27. Prefer the 'Full Papers' row; filter individual agendas/minutes. Bi-monthly (Jan, Mar, May, Jul, Sep, Nov).</t>
         </is>
       </c>
       <c r="J193" t="b">
@@ -12612,17 +12638,17 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>/about-us/meet-board/board-meetings-public/previous-meetings-year;year tabs: navigate/53518/{yearId}#doc-library-53518 (7416=2025/26, 11922=2026/27, 2318=2024/25);download_file endpoint: blackpoolteachinghospitals.nhs.uk/download_file/{id}/2316;link text 'Board of Directors Meeting in Public - {date} - Full Papers'</t>
+          <t>/download_file/;/2316;Full Papers;navigate/53518;doc-library-53518</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>/upcoming-meetings (calendar only, no papers);/about-us/meet-board (board membership);/organisational-structure;skip-to / accessibility / #header anchors</t>
+          <t>agenda;minutes;Part 2;private;confidential</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -12632,7 +12658,7 @@
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>The 2025/26 year tab rendered six dated 'Full Papers' packs spanning 01 May 2025 through 05 March 2026, each via a /download_file/{id}/2316 link.</t>
+          <t>2025/26 folder lists Full Papers for 08 Jan 2026 plus Nov/Sep/Jul/May 2025 meetings as download_file links.</t>
         </is>
       </c>
     </row>
@@ -12728,25 +12754,25 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>Pattern D listed but actually NOT required: contrary to the prior assumption, a plain static fetch of this URL DOES return the full dated board-papers listing — the page server-renders current-year 'Trust Board (Public Session) Papers' entries plus prior-year sections, each linking to a CMS download endpoint elht.nhs.uk/download_file/{id}/191. The static body already exposes the 2026 packs (May 2026, March 2026, January 2026) and 2025 packs (Jul/Sep/Nov 2025, Jan/Mar 2025) and the forward meeting schedule (next 13 May 2026; then 8 Jul, 9 Sep, 11 Nov 2026, 13 Jan, 10 Mar 2027). The path was corrected on 2026-05-29 to /about-us/our-trust-board/board-meetings-including-agenda-and-papers (old /about-us/board-meetings-... 404'd after restructure). Per-year archive sub-pages (archive-2022, archive-2023, ...) hang off the same path for older material. Because the current packs are reachable statically, a crawler does NOT need Playwright for this org — needs_playwright should be cleared.</t>
+          <t>The supplied URL is the correct landing (rendered title 'Board Meetings (including Agenda and Papers) :: East Lancashire Hospitals NHS Trust'). Static fetch returns empty because the same Granicus-style CMS renders the document table client-side, so Playwright is required. Unlike Blackpool, the dated PDFs are listed directly on this single page: a 'View the latest Board papers' link plus an 'Archive' table of rows named 'Trust Board (Public Session) Papers - &lt;Month Year&gt;.pdf'. PDFs served on-domain, extension-less, via /download_file/&lt;docid&gt;/191 (latest uses /download_file/view/&lt;id&gt;/191). Coverage 2024-2026 in the visible archive with older years below. Prefer rows labelled 'Public Session'/'Public'/'Open Session' full Papers; filter private/closed-session items. Bi-monthly (Jan, Mar, May, Jul, Sep, Nov).</t>
         </is>
       </c>
       <c r="J195" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>elht.nhs.uk/download_file/{id}/191;link text 'Trust Board (Public Session) Papers - {Month} {Year}';older years under /board-meetings-including-agenda-and-papers/archive-{year}</t>
+          <t>/download_file/;/191;Public Session) Papers;Trust Board;Public) Papers</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>/download_file/view/12770/191 (one-off East Kent maternity response, not a board pack);archive-{year} pages when only current FY is wanted</t>
+          <t>Private;Closed;Confidential;agenda only</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -12756,7 +12782,7 @@
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>Static fetch returned dated 2025 and 2026 Trust Board public-session papers (e.g. May 2026, March 2026, January 2026) via /download_file/{id}/191 links, so papers are reachable without JS rendering.</t>
+          <t>Archive lists May 2026, March 2026, January 2026 and 2025 Trust Board public papers as download_file PDFs.</t>
         </is>
       </c>
     </row>
@@ -13245,30 +13271,30 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>https://www.eastamb.nhs.uk/about-us/trust-board/public-board-meetings-and-papers</t>
+          <t>https://www.eastamb.nhs.uk/about-us/trust-board/in-public-board-minutes-archive</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>Pattern C (per-meeting sub-pages) with a quirk: the landing /about-us/trust-board/public-board-meetings-and-papers lists each Board meeting date and links to two sub-pages per meeting - a 'public board reports &lt;month&gt; &lt;year&gt;' page (the papers) and an 'in public board minutes &lt;month&gt; &lt;year&gt;' page. The reports sub-page (e.g. /about-us/trust-board/public-board-reports-february-2026) presents the agenda as a table of hyperlinked report titles rather than one combined pack PDF, so a crawler must follow each agenda-item link to reach the documents. Dates 2025-26 (Feb 2025 through Jun 2026) are all listed. Older material is at /about-us/trust-board/in-public-board-minutes-archive. The validator missed this because the landing has no on-page dated PDFs.</t>
+          <t>The old URL (.../public-board-meetings-and-papers) is only a 'next meeting' stub that says papers are 'available on request' by email, with no dated documents. The real index is the In Public Board minutes archive, which lists each meeting (2025: Feb, May, Jul, Sep, Nov; 2026: Feb, Apr, Jun) as a per-meeting page like /about-us/trust-board/public-board-reports-&lt;month&gt;-&lt;year&gt;. CRITICAL MODEL DIFFERENCE: EEAST does NOT publish PDF packs, each per-meeting page lists every individual report (CEO report, IPR, BAF, committee assurance...) as its own HTML web page (e.g. /public-board-report-CEO-report-february-2026). So there is nothing to download; a crawler must scrape HTML at three levels: archive -&gt; per-meeting page -&gt; per-report page. Use the latest /public-board-reports-&lt;month&gt;-&lt;year&gt; page as the per-meeting entry point and treat its child report pages as the 'papers'. Needs render to enumerate child links reliably.</t>
         </is>
       </c>
       <c r="J203" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>/about-us/trust-board/public-board-reports-&lt;month&gt;-&lt;year&gt;;/about-us/trust-board/in-public-board-minutes-&lt;month&gt;-&lt;year&gt;</t>
+          <t>www.eastamb.nhs.uk/about-us/trust-board/public-board-reports-&lt;month&gt;-&lt;year&gt;;www.eastamb.nhs.uk/about-us/trust-board/public-board-report-CEO-report-&lt;month&gt;-&lt;year&gt;;www.eastamb.nhs.uk/about-us/trust-board/integrated-performance-report-&lt;Month&gt;-&lt;year&gt;</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>/annual-general-meeting;/agm-minutes;/committee</t>
+          <t>/executive-directors;/non-exec-directors;/declarations-of-interest;annual-general-meeting;agm-minutes;/patient-story</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -13278,7 +13304,7 @@
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>Landing links to per-meeting 'public board reports' sub-pages for 2025-26 meetings (e.g. Feb 2026, Apr 2026, Jun 2026) which carry the agenda papers.</t>
+          <t>Dated 2025-2026 board reports are published as individual HTML report pages (no PDFs) reachable via the minutes-archive index.</t>
         </is>
       </c>
     </row>
@@ -13400,7 +13426,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>Pattern A+D (dated combined-pack PDFs, but list is JS-rendered). The human-readable landing /about-scas/our-board/board-meetings/ only shows future meeting dates and an empty archive table ('papers published shortly before each meeting'; older papers via company.secretary@scas.nhs.uk), so it is not crawlable directly. The real document store is the WordPress category page /document-category/board-papers/, but its document list renders client-side (WebFetch saw only chrome), so Playwright (networkidle) is needed to enumerate it. The underlying packs are single combined PDFs under /wp-content/uploads/&lt;yyyy&gt;/&lt;mm&gt;/SCAS-Public-Board-Papers_&lt;date&gt;.pdf (naming varies: SCASpublic-Board-papers_&lt;ddmmyyyy&gt;, SCAS-Trust-Board-Meeting-in-Public-&lt;date&gt;-Bundle). Some meetings also have a separate '...Supporting_Information' or 'Supporting' PDF - prefer the main 'Board-Papers' bundle. Board meets every other month (last Thursday).</t>
+          <t>Correct WordPress taxonomy archive ('Board Papers', category 'Board Papers 2025-26') but it is JS/dynamically rendered, a plain HTTP fetch returns only site nav chrome (hence the 'no papers' flag), so it NEEDS render to enumerate entries. Each entry is a /document/&lt;slug&gt;/ page (e.g. /document/scas-public-board-papers-25-sept-2025/) that links to a single combined pack PDF under /wp-content/uploads/YYYY/MM/. SCAS publishes the pack only shortly before each in-public meeting (~Feb/Apr/Jun/Sep/Nov), so the newest confirmed pack at scan time is 25 Sept 2025; the 4 Jun 2026 pack appears on the same archive around the meeting date. Prefer the single 'SCAS public Board papers - &lt;date&gt;' PDF; older copies by email to company.secretary@scas.nhs.uk. Filter policy/strategy PDFs in the same uploads folder.</t>
         </is>
       </c>
       <c r="J205" t="b">
@@ -13408,27 +13434,27 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>/wp-content/uploads/&lt;yyyy&gt;/&lt;mm&gt;/SCAS-Public-Board-Papers_&lt;date&gt;.pdf;/wp-content/uploads/&lt;yyyy&gt;/&lt;mm&gt;/SCASpublic-Board-papers_&lt;ddmmyyyy&gt;.pdf;SCAS-Trust-Board-Meeting-in-Public-&lt;date&gt;-Bundle</t>
+          <t>www.scas.nhs.uk/document/scas-public-board-papers-&lt;date&gt;/;www.scas.nhs.uk/wp-content/uploads/&lt;yyyy&gt;/&lt;mm&gt;/SCAS-Public-Board-Papers_&lt;date&gt;.pdf</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>Supporting;SupportingInformation;Joint-Committee;/registers-of-interests/</t>
+          <t>/wp-content/uploads/.*Policy;registers-of-interest;constitution;strategy;scas-board-members</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>papers_found</t>
+          <t>needs_playwright</t>
         </is>
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>Dated combined SCAS public board pack PDFs exist in /wp-content/uploads/ for Jan/Mar/Sep/Nov 2025 and Apr 2026 (verified one is a 7.5MB pack); enumerating the category page needs JS.</t>
+          <t>The archive lists dated board-pack PDFs but only after JS render; a confirmed 2025 pack PDF was retrieved via its /document/ page.</t>
         </is>
       </c>
     </row>

--- a/trust_urls.xlsx
+++ b/trust_urls.xlsx
@@ -1912,16 +1912,42 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.leicspart.nhs.uk/about-us/trust-board/</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
+          <t>https://www.leicspart.nhs.uk/about/corporate-responsibilities/trust-board/</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Pattern E (anti-bot) + A. The site forcibly closes automated connections (ConnectionReset to requests and WebFetch), so static health-checks read as 'broken'; the page is live in a browser. The board page moved path from /about-us/trust-board/ to /about/corporate-responsibilities/trust-board/ (sibling /about/corporate-responsibilities/group-board/ holds the group board). Combined paper packs are published as dated PDFs under /wp-content/uploads/YYYY/MM/ named '{DD Month YYYY} Public Trust Board Combined Paper Pack'. Trust meets ~6x/year on MS Teams with livestream. If blocked, fetch the dated combined-pack PDF URL directly or use the publication scheme. URL fixed 2026-06-13.</t>
+        </is>
+      </c>
+      <c r="J24" t="b">
+        <v>1</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>DD Month YYYY Public Trust Board Combined Paper Pack;Group Trust Board Combined Paper Pack;/wp-content/uploads/YYYY/MM/</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Declarations of Interest Report (component);Group Board (when only trust board wanted);minutes only</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Search-confirmed live combined packs 27 January 2026 and 26 May 2026 under leicspart.nhs.uk/wp-content/uploads/2026/; site blocks automated fetch (anti-bot).</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2062,13 +2088,39 @@
           <t>https://www.uhleicester.nhs.uk/about/board/board-papers-and-meetings/</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Landing page lists the full paper set for the most recent meeting directly (Pattern A): individual dated PDFs for the current 'Boards in Common' meeting (agenda, minutes, action log, committee reports, performance and quality papers) appear inline. UHL runs as a 'Boards in Common' with Leicestershire Partnership, so packs may be jointly branded. For older 2025/2026 meetings follow the 'Agenda and papers from our previous Trust Board meetings are available here' link to the publication-scheme archive. The page also lists upcoming 2026 meeting dates whose packs post in the same inline pattern shortly before each date.</t>
+        </is>
+      </c>
+      <c r="J27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Agenda;Public/Trust Board pack;Boards in Common agenda and papers;performance report</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>minutes only;action log;observer/Q&amp;A notes;publication-scheme generic documents</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Inline dated PDFs present for the 11 June 2026 Boards in Common meeting (agenda + committee reports); older packs via the 'previous Trust Board meetings' publication-scheme link.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2186,13 +2238,39 @@
           <t>https://www.derbyshirehealthcareft.nhs.uk/about-us/our-board-directors/board-meetings</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Landing page lists meetings chronologically under expandable '2025' and '2026' year headings (Pattern A with inline accordions, no separate year pages). Each meeting shows its date and time followed by a single 'Agenda and papers' link that resolves to a download_file/view PDF (e.g. /download_file/view/6958/222). A crawler should collect every 'Agenda and papers' href under the 2025 and 2026 headings. Ignore the 'View a summary of the meeting' link (narrative recap, not the pack) and any 'Join via webinar' / 'Link to join the meeting online' safelinks.</t>
+        </is>
+      </c>
+      <c r="J29" t="b">
+        <v>0</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Agenda and papers;download_file/view</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>View a summary of the meeting;Join via webinar;Link to join the meeting online;meeting summaries</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>2026 packs listed for 27 Jan, 24 Mar, 19 May 2026; 2025 sample 'Agenda and papers' = /download_file/view/6958/222 (14 Jan 2025).</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2310,13 +2388,39 @@
           <t>https://dchs.nhs.uk/about-us/our-board</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Landing page lists papers directly under 'Agendas and Papers 2026:' and 'Agendas and Papers 2025:' headings (Pattern A). Each entry is a month link, sometimes annotated with content type in parentheses, e.g. 'January 2026 (Performance Report)', resolving to a download_file/view PDF (URLs like /download_file/view/[ID]/243). A crawler should collect every month link beneath each 'Agendas and Papers [year]' heading. Some links are component documents (e.g. a standalone Performance Report) rather than the full pack, so prefer the bare 'Month Year' agenda link where both exist.</t>
+        </is>
+      </c>
+      <c r="J31" t="b">
+        <v>0</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Agendas and Papers;Month Year agenda link;download_file/view</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>(Performance Report) standalone component when full pack also listed;minutes only</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Dated month links present under both 2025 and 2026 headings, e.g. 'January 2026 (Performance Report)' and 'August 2025', each a download_file/view PDF.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2436,25 +2540,25 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>The supplied URL is the correct landing (rendered title 'Board meeting papers for Shropshire Community Health NHS Trust'). Static fetch returns empty because the site renders content client-side, so Playwright is required. The CURRENT meeting's papers appear inline near the bottom under a 'Board papers for &lt;Month Year&gt;' heading (currently 'Board papers for May 2026') with 2-3 PDF links; for older meetings use the 'Papers from previous board meetings' dropdown (select month/year, click 'Find') which loads via JS. PDFs are on-domain at content/doclib/NNNNN.pdf. Meetings roughly bi-monthly; dropdown spans 2015-2026. Prefer the combined/full pack ('Combined papers'/'Public Information Pack') over the standalone agenda. Filter the agenda-only PDF and private items; only ~5 years retained.</t>
+          <t>Landing page at /board-meetings-and-papers shows the LATEST meeting's papers directly as dated PDFs at /content/doclib/&lt;id&gt;.pdf (server-rendered, static fetch works — the needs_playwright flag was a false positive). For the most recent meeting take the file named '01 ... Combined papers' or '02 Public Information Pack' as the main pack; '00 Public Agenda' is agenda-only. To reach earlier meetings, use the on-page dropdown &lt;select name="bdts"&gt; whose options are month/year labels (e.g. 'April 2025', 'June 2025', 'August 2025', up to 'December 2026'); changing the selection swaps the three displayed doclib PDFs to that meeting's set via JS. Note these are 'Meetings in Common' so a single combined pack covers the joint board.</t>
         </is>
       </c>
       <c r="J33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>content/doclib/;.pdf;Combined papers;Public Information Pack;Board papers for &lt;Month Year&gt;</t>
+          <t>Public Information Pack;Combined papers;Board Meetings in Common - DD.MM.YYYY - Combined papers;/content/doclib/&lt;id&gt;.pdf</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Public Agenda;agenda only;minutes</t>
+          <t>00 Public Agenda (agenda only, not full pack);AGM;minutes-only items</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2464,7 +2568,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Inline May 2026 board pack PDFs present (agenda, combined papers, public information pack) plus a 5-year dropdown archive.</t>
+          <t>Saw '02 Public Information Pack 14.05.2026' (doclib/14536.pdf) and '01 Board Meetings in Common - 14.05.2026 - Combined papers' (doclib/14535.pdf) on the landing, plus dropdown entries back to April 2025.</t>
         </is>
       </c>
     </row>
@@ -2509,13 +2613,39 @@
           <t>https://www.walsallhealthcare.nhs.uk/about-us/how-we-are-run/board-papers/</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Walsall runs a Joint Trust Board with Royal Wolverhampton (RWT); landing page shows collapsible year sections ('2026', '2025') that expand to direct 'Trust Board Papers – [Month Year]' PDF links (Pattern A with accordion). Meeting packs are available at least 3 working days before each meeting. PDFs are hosted on either the Walsall Healthcare or Royal Wolverhampton domains, so accept cross-domain hrefs. A crawler should expand each year heading and collect every 'Trust Board Papers – [Month Year]' link.</t>
+        </is>
+      </c>
+      <c r="J34" t="b">
+        <v>0</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Trust Board Papers –;Joint Trust Board meeting pack</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>minutes only;ICP not ICB;standalone risk-register documents</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>2026 packs: 'Trust Board Papers – May 2026', 'March 2026', 'January 2026'; 2025 includes 'Trust Board Papers – November 2025' and 'September 2025'.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4052,13 +4182,39 @@
           <t>https://www.lewishamandgreenwich.nhs.uk/board-papers/</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Single page listing all board papers chronologically under year headings (Pattern A); no calendar, year folders or sub-pages. Meetings appear as dated links such as 'Trust Board 30 September 2025' and 'Trust Board Meeting, Tuesday 28 April 2026', each resolving directly to a PDF. Beware data-quality noise: some entries are duplicated (two differently-URL'd versions of the same April 2026 meeting) and some links are standalone component documents — e.g. 'Corporate risk register and board assurance framework, Nov 2025' is a .docx, not a board pack. Prefer the 'Trust Board [date]' meeting links and de-duplicate by date.</t>
+        </is>
+      </c>
+      <c r="J57" t="b">
+        <v>0</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Trust Board [date];Trust Board Meeting, [day date]</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Corporate risk register and board assurance framework (.docx component);duplicate same-date links;minutes only</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>2026: 'Trust Board Meeting, Tuesday 28 April 2026'; 2025: 'Trust Board 30 September 2025' and 'Trust Board 24 June 2025'.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4717,12 +4873,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.yorkscarborough.nhs.uk/about-us/board-of-directors/board-of-directors-papers/</t>
+          <t>https://www.yorkhospitals.nhs.uk/about-us/board-of-directors/board-of-directors-papers/</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>The trust has rebranded/migrated its domain from yorkhospitals.nhs.uk to yorkscarborough.nhs.uk; the old /board-of-directors-meetings/ page only lists meeting dates and points to a separate papers sub-page. Go to /board-of-directors-papers/, which lists each meeting (2025/26 and 2026/27) with a per-meeting 'Agenda' link of the form /seecmsfile/?id=NNNN that opens the combined agenda+papers document. Static fetch works (HTML renders the dated list); no JS render needed. Coverage 2025-2026 both present plus upcoming 2026/27 dates. Prefer the most recent past meeting's agenda/papers link; entries marked 'available nearer the time' have no doc yet. Filter out future undated rows and the meetings landing page.</t>
+          <t>Pattern A + F. The DB domain yorkscarborough.nhs.uk is dead (ECONNREFUSED); the live site is yorkhospitals.nhs.uk. Board of Directors papers are listed directly on this page as dated 'Agenda' links per meeting (newest first), with separate 'late papers' supplementary links where applicable, and an archive of prior financial years below. Static fetch works on the new domain. URL fixed 2026-06-13 (yorkscarborough -&gt; yorkhospitals).</t>
         </is>
       </c>
       <c r="J67" t="b">
@@ -4730,17 +4886,17 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>/seecmsfile/?id=;Agenda &lt;Month&gt; &lt;Year&gt;;Board of Directors papers</t>
+          <t>DD Month YYYY Agenda;Board of Directors papers</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>board-of-directors-meetings;available nearer the time;#main-content</t>
+          <t>late papers (supplementary);minutes only</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -4750,7 +4906,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Papers sub-page lists per-meeting seecmsfile agenda/paper links for 2025 and 2026 meetings on the migrated yorkscarborough.nhs.uk domain.</t>
+          <t>Confirmed dated agendas for 25 February 2026 and 25 March 2026 plus 2024/25 archive on the new yorkhospitals.nhs.uk domain.</t>
         </is>
       </c>
     </row>
@@ -5467,13 +5623,39 @@
           <t>https://www.humber.nhs.uk/about/trust-board/</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Two-hop year-folder structure (Pattern B). The main /about/trust-board/ page only links to a 'Public Board Papers' sub-page; that sub-page (/about/trust-board/public-board-papers/) then links to per-year folders 'Public Board Papers 2026' and 'Public Board Papers 2025', each of which lists single combined-pack PDFs named 'Public Board Papers - [DD Month YYYY]' under /media/. The Trust meets in public every other month. A crawler should follow Trust Board → Public Board Papers → each year folder, then collect the /media/*.pdf pack links. Use /public-board-dates/ for the forward schedule.</t>
+        </is>
+      </c>
+      <c r="J78" t="b">
+        <v>0</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Public Board Papers - [date];/media/*.pdf combined pack</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Public Board Dates (schedule only);Meet the Board;minutes only</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>2026 folder lists 'Public Board Papers - 27 May 2026', '25 March 2026', '28 January 2026'; 2025 folder includes 'Public Board Papers - 28 May 2025'.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6113,13 +6295,39 @@
           <t>https://www.esneft.nhs.uk/about-us/how-we-work/board-of-directors-meetings/</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Landing page lists financial-year folder links such as '2025 to 2026 Board meetings papers', '2024 to 2025 Board meetings papers' and '2026 to 2027 Board meetings papers'; follow each year link (Pattern B) to reach individual dated meeting sub-pages (e.g. 'May 2026 ESNEFT board meeting papers') which then host the downloadable PDFs (Pattern C nesting). Papers are published a few days before each meeting. No PDFs are exposed directly on the landing page, so a crawler must traverse year folder, then meeting page, then PDF. Target the per-meeting 'agenda and papers' packs.</t>
+        </is>
+      </c>
+      <c r="J88" t="b">
+        <v>0</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>YYYY to YYYY Board meetings papers;Month YYYY ESNEFT board meeting papers;agenda and papers</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>approved minutes;Chief Executive office contact;draft resolutions only</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>papers_partial</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>Confirmed year-folder structure on landing with current folders '2025 to 2026 Board meetings papers' and a '2026 to 2027' folder containing 'May 2026 ESNEFT board meeting papers'.</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -6557,13 +6765,39 @@
           <t>https://www.cpft.nhs.uk/board-of-directors/</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
-      <c r="O96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>All board packs are listed directly on the single landing page (Pattern A) under a 'Previous Meetings' section, newest first, as direct PDF links with 'Public Board Meeting Papers DDMMYYYY.pdf' / 'Public Board Meeting Book - DD.MM.YYYY.pdf' naming. A crawler can harvest dated PDFs in one pass; no year folders or per-meeting sub-pages exist. Skip the 'Upcoming Meetings' section which lists future dates with no downloadable papers.</t>
+        </is>
+      </c>
+      <c r="J96" t="b">
+        <v>0</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Public Board Meeting Papers DDMMYYYY.pdf;Public Board Meeting Book - DD.MM.YYYY.pdf;Public Board Papers</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>Upcoming Meetings (dates with no PDF);minutes only</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>Direct PDFs visible e.g. 'Public Board Meeting Book - 03.06.2026.pdf' (June 2026) and 'Public Board Meeting Papers 26112025.pdf' (Nov 2025).</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -7673,13 +7907,39 @@
           <t>https://www.awp.nhs.uk/about-us/publications/board-papers</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
-      <c r="O114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Landing page presents a document-library table of financial-year folder links (e.g. '2025 - 2026', '2024 - 2025') using internal /navigate/{id}/35520#document-library-35520 URLs; follow each year link (Pattern B) to reach that year's folder of dated board-paper PDFs. The landing page itself only exposes two reference documents ('Guidance on assurance rating', 'Risk appetite statement'), not the meeting packs. A crawler must click the year folder link to enumerate dated packs; the internal navigate IDs are dynamic so resolve them from the live landing page rather than hard-coding.</t>
+        </is>
+      </c>
+      <c r="J114" t="b">
+        <v>0</v>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>YYYY - YYYY;navigate/{id}/35520#document-library-35520;Board papers</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>Guidance on assurance rating;Risk appetite statement;download_file reference docs</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>papers_partial</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>Landing confirms year folders e.g. '2025 - 2026' and '2024 - 2025'; individual dated 2025/2026 PDFs sit one level inside each year folder (navigate IDs dynamic, read from live page).</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -8218,13 +8478,39 @@
           <t>https://www.bhrhospitals.nhs.uk/papers-minutes/</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
-      <c r="O123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Landing page shows a 'Folders' list (e.g. 'January 2026', 'March 2026', 'May 2026', 'Previous years') as clickable month folders using /papers-minutes?smbfolder={id} URLs (Pattern B/C); follow each month folder to reach the full board pack PDF inside. Packs are full 'Trust Board (Public) Papers' documents served via /download.cfm?doc=...&amp;ver=... links, not minutes. A crawler must enter each month folder to obtain the dated PDF; the 'Previous years' folder shows 0 files but real packs sit in the dated month folders.</t>
+        </is>
+      </c>
+      <c r="J123" t="b">
+        <v>0</v>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Trust Board (Public) Papers DD.MM.YY;Month YYYY folder;download.cfm?doc=...&amp;ver=</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>Procedure for questions from the public;Teams meeting links;Previous years (0 files)</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>papers_partial</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>Inside the folder structure confirmed pack 'Trust Board (Public) Papers 15.01.26 (v2) For Website Reduced Size.pdf' (uploaded 16 Jan 2026); March/May 2026 folders present.</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -8267,13 +8553,39 @@
           <t>https://www.whittington.nhs.uk/default.asp?c=20208</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
-      <c r="O124" t="inlineStr"/>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Classic ASP page lists board packs directly on the landing (Pattern A) under year headings ('Meetings in 2026', 'Meetings in 2025') as dated hyperlinks of the form 'Download the board papers for DD Month YYYY' pointing to internal numeric document IDs. A crawler can harvest all dated packs in a single pass; no year folders or per-meeting sub-pages. Ignore the 'printed copies on request' note.</t>
+        </is>
+      </c>
+      <c r="J124" t="b">
+        <v>0</v>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Download the board papers for DD Month YYYY;Meetings in YYYY;numeric document ID links</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>Printed copies available on request;minutes only</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>Direct dated links e.g. 'Download the board papers for 21 May 2026' (doc 16288) and 'Download the board papers for 26 November 2025' (doc 16128).</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -8391,13 +8703,39 @@
           <t>https://www.homerton.nhs.uk/board-papers/</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
-      <c r="O126" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Landing page lists board packs directly (Pattern A) under year groupings ('2026', '2025', '2024') with each month name acting as a hyperlink to a dated PDF at /download/{slug}.pdf. A crawler can harvest all month PDFs from this single index in one pass; there are no intermediate folders or per-meeting sub-pages.</t>
+        </is>
+      </c>
+      <c r="J126" t="b">
+        <v>0</v>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Month name link under YYYY heading;/download/{month}-{year}.pdf;papers-{month}-{year}.pdf</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>minutes only;non-dated reference docs</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>Direct PDFs e.g. May 2026 (/download/may-2026-paperspdf.pdf) and November 2025 (/download/november-2025.pdf).</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -9334,13 +9672,39 @@
           <t>https://www.northumbria.nhs.uk/about-us/corporate-information/strategies-and-reports/board-papers</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
-      <c r="O141" t="inlineStr"/>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Static-fetchable landing page (HTTP 200) listing dated full board packs directly, grouped under year headings (2026, 2025). Each entry is a 'Public board papers - [Month Year]' anchor that links straight to a single PDF download at /download_file/{id}/875 — no year sub-folders or per-meeting sub-pages to traverse. Crawl the landing, collect all anchors whose text matches 'Public board papers - &lt;Month&gt; &lt;Year&gt;' and resolve the /download_file/ href as the dated board-pack PDF. Pattern A. The board meets bi-monthly so expect ~6 packs/year. Ignore the separate 'Guidance note for public meetings' and any future-dates list with no download link yet.</t>
+        </is>
+      </c>
+      <c r="J141" t="b">
+        <v>0</v>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Public board papers - {Month} {Year};/download_file/{id}/875</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>Guidance note for public meetings;future dates with no download link</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>Confirmed dated packs e.g. 'Public board papers - January 2026' (/download_file/3812/875) and 'Public board papers - November 2025' (/download_file/3764/875).</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -9732,13 +10096,39 @@
           <t>https://hiowhealthcare.nhs.uk/about-us/our-board/meetings-and-papers</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr"/>
-      <c r="N147" t="inlineStr"/>
-      <c r="O147" t="inlineStr"/>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Static-fetchable landing (Hampshire &amp; IoW Healthcare, successor to Solent) listing dated public board meetings directly under year-range headings ('Board Meeting Papers 2026-2027', 'Board Meeting Papers 2025-2026', 'Most Recent Board Papers'). Each meeting is anchored by its date (e.g. 'Tuesday 09 December 2025') which links to the agenda/papers PDF; meetings run roughly bi-monthly on Tuesdays. No intermediate year folders or per-meeting hub pages — the dated anchor resolves to the PDF. Pattern A. Take date-text anchors under the 2025-2026 / 2026-2027 headings. Exclude the 'Confidential agenda' link that accompanies each public entry (closed-session agenda, not the public pack).</t>
+        </is>
+      </c>
+      <c r="J147" t="b">
+        <v>0</v>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Tuesday {DD} {Month} {Year};Board Meeting Papers {Year}-{Year}</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>Confidential agenda;confidential</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>Confirmed dated entries e.g. 'Tuesday 10 February 2026' and 'Tuesday 09 December 2025', each with a public agenda link plus a 'Confidential agenda' to skip.</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -11858,13 +12248,39 @@
           <t>https://www.mcht.nhs.uk/about-us/board-directors/board-papers-and-minutes</t>
         </is>
       </c>
-      <c r="I181" t="inlineStr"/>
-      <c r="J181" t="inlineStr"/>
-      <c r="K181" t="inlineStr"/>
-      <c r="L181" t="inlineStr"/>
-      <c r="M181" t="inlineStr"/>
-      <c r="N181" t="inlineStr"/>
-      <c r="O181" t="inlineStr"/>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Static-fetchable landing showing a folder hierarchy, not direct PDFs: the 'Board Papers and Minutes' page lists year-folder links ('2026-27', '2025-26', '2024-25', 'Archive') each pointing to a sub-page via /navigate/{lib}/{id} (2025-26 = /navigate/9698/2001). Follow the relevant year folder to reach the dated full board bundles, which are direct PDF links titled 'Board of Directors Bundle Part I (Public) - {date}'. Pattern B. Positive signal: 'Bundle Part I (Public)' = full public board pack. Papers are posted four working days before each meeting. Exclude the separate Minutes folder/'Summary of Agenda Items' documents and any Part II (confidential) items.</t>
+        </is>
+      </c>
+      <c r="J181" t="b">
+        <v>0</v>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Board of Directors Bundle Part I (Public) - {date};/navigate/9698/{id};20{25|26}-2{6|7} Board Papers and Minutes</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>Minutes;Summary of Agenda Items;Part II;confidential</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>On the 2025-26 sub-page, confirmed e.g. 'Board of Directors Bundle Part I (Public) - 29 January 2026' and '27 November 2025'.</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -11907,13 +12323,39 @@
           <t>https://www.uhliverpool.nhs.uk/about-us/meet-our-board/trust-board-meetings</t>
         </is>
       </c>
-      <c r="I182" t="inlineStr"/>
-      <c r="J182" t="inlineStr"/>
-      <c r="K182" t="inlineStr"/>
-      <c r="L182" t="inlineStr"/>
-      <c r="M182" t="inlineStr"/>
-      <c r="N182" t="inlineStr"/>
-      <c r="O182" t="inlineStr"/>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Static WebFetch is blocked (HTTP 403 / WAF) AND the papers sit in a JS-rendered document-library widget, so use Playwright (navigate, wait for networkidle). The 'Group Board meetings' page (NHS University Hospitals of Liverpool Group) exposes year tabs (2024, 2025, 2026) that load content via AJAX at /trust-board-meetings/navigate/4487/{id} (2026 = /navigate/4487/21268). Navigate to the year tab URL, then collect /download_file/{id}/423 anchors titled 'UHLG Board of Directors Public Pack - {date}' (and the companion 'Public Information Pack'). Pattern D + year-tab. Exclude the 'Jargon Buster Guide', the Assurance and Risk Committee meetings, and legacy LUHFT/LWH archive tabs.</t>
+        </is>
+      </c>
+      <c r="J182" t="b">
+        <v>1</v>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>UHLG Board of Directors Public Pack - {date};UHLG Board of Directors Public Information Pack - {date};/navigate/4487/{id};/download_file/{id}/423</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>Jargon Buster Guide;Assurance and Risk Committee;archive</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>Via Playwright on the 2026 tab, confirmed 'UHLG Board of Directors Public Pack - 15 January 2026' (/download_file/20288/423) and '14 May 2026' (/download_file/21451/423).</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -12630,25 +13072,25 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>The supplied URL is the correct landing (rendered title 'Board Meetings in Public :: Blackpool Teaching Hospitals'). Static fetch returns empty because the site (Granicus-style CMS) renders the document library client-side, so Playwright is required. The landing is only a hub of explanatory text; to reach dated papers follow 'Agendas and Reports by Year' at /about-us/meet-board/board-meetings-public/previous-meetings-year, which lists fiscal-year folders. Click a year (e.g. '2026/27 Meetings' or '2025/26 Meetings'); the URL takes the form .../previous-meetings-year/navigate/53518/&lt;id&gt;#doc-library-53518 and renders a table of 'Board of Directors' Meeting in Public, &lt;date&gt; - Full Papers' rows. PDFs served extension-less via /download_file/&lt;docid&gt;/2316. Coverage 2018/19 through 2026/27. Prefer the 'Full Papers' row; filter individual agendas/minutes. Bi-monthly (Jan, Mar, May, Jul, Sep, Nov).</t>
+          <t>Landing /about-us/meet-board/board-meetings-public is an intro page with two links: 'Agendas and Reports by Year' (/previous-meetings-year) and 'Calendar of Meetings' (/upcoming-meetings). The papers live on the year page, which presents year tabs ('2026/27 Meetings', '2025/26 Meetings', '2024/25 Meetings', ...). On default load NO document links are present — you must follow a year tab, which is a real link of the form /about-us/meet-board/board-meetings-public/previous-meetings-year/navigate/53518/&lt;termId&gt;#doc-library-53518 (e.g. termId 7416 = 2025/26, 11922 = 2026/27). Plain navigation to that year URL server-renders the dated PDFs, so headless Playwright is NOT strictly required once you follow the year link. Each meeting is a single 'Full Papers' PDF at /download_file/&lt;id&gt;/2316. Treat the 'Board of Directors Meeting in Public - DD Month YYYY - Full Papers' item as the main pack. A separate UHLG group-board page exists on uhliverpool.nhs.uk for the joint Liverpool group board — ignore it for RXL's own trust board.</t>
         </is>
       </c>
       <c r="J193" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>/download_file/;/2316;Full Papers;navigate/53518;doc-library-53518</t>
+          <t>Board of Directors Meeting in Public - DD Month YYYY - Full Papers;/download_file/&lt;id&gt;/2316;previous-meetings-year/navigate/53518/&lt;termId&gt;</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>agenda;minutes;Part 2;private;confidential</t>
+          <t>UHLG / uhliverpool.nhs.uk group-board packs (different body);Calendar of Meetings page (dates only, no papers);minutes-only or register-of-interests items</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -12658,7 +13100,7 @@
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>2025/26 folder lists Full Papers for 08 Jan 2026 plus Nov/Sep/Jul/May 2025 meetings as download_file links.</t>
+          <t>Following the 2025/26 year link (navigate/53518/7416) listed 6 dated packs including 'Board of Directors Meeting in Public - 05 March 2026 - Full Papers' (download_file/10631/2316) and '08 January 2026 - Full Papers' (download_file/10080/2316).</t>
         </is>
       </c>
     </row>
@@ -12754,25 +13196,25 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>The supplied URL is the correct landing (rendered title 'Board Meetings (including Agenda and Papers) :: East Lancashire Hospitals NHS Trust'). Static fetch returns empty because the same Granicus-style CMS renders the document table client-side, so Playwright is required. Unlike Blackpool, the dated PDFs are listed directly on this single page: a 'View the latest Board papers' link plus an 'Archive' table of rows named 'Trust Board (Public Session) Papers - &lt;Month Year&gt;.pdf'. PDFs served on-domain, extension-less, via /download_file/&lt;docid&gt;/191 (latest uses /download_file/view/&lt;id&gt;/191). Coverage 2024-2026 in the visible archive with older years below. Prefer rows labelled 'Public Session'/'Public'/'Open Session' full Papers; filter private/closed-session items. Bi-monthly (Jan, Mar, May, Jul, Sep, Nov).</t>
+          <t>Landing /about-us/our-trust-board/board-meetings-including-agenda-and-papers lists dated board-pack PDFs directly as an archive of individual files (server-rendered, static fetch works — needs_playwright was a false positive). Each meeting is one PDF at /download_file/&lt;id&gt;/191 with titles like 'Trust Board (Public Session) Papers - &lt;Month YYYY&gt;.pdf' or 'Trust Board Agenda and Papers - &lt;Month&gt; &lt;Year&gt;'. Take the 'Public'/'Open Session' 'Papers' file as the main pack. The page also lists future meeting dates (no PDFs yet) at the bottom for forward scanning. No year folders, no per-meeting sub-pages, no JS gating.</t>
         </is>
       </c>
       <c r="J195" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>/download_file/;/191;Public Session) Papers;Trust Board;Public) Papers</t>
+          <t>Trust Board (Public Session) Papers - Month YYYY.pdf;Trust Board (Public) Papers - Month YYYY.pdf;/download_file/&lt;id&gt;/191</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>Private;Closed;Confidential;agenda only</t>
+          <t>one-off response/report items;confidential/private session items;minutes-only items</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -12782,7 +13224,7 @@
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>Archive lists May 2026, March 2026, January 2026 and 2025 Trust Board public papers as download_file PDFs.</t>
+          <t>Saw 'Trust Board (Public) Papers - May 2026.pdf' (download_file/30615/191) and 'Trust Board (Public Session) Papers - March 2026 1.pdf' (download_file/30554/191), plus future dates 8 Jul 2026 and 9 Sep 2026 listed without papers yet.</t>
         </is>
       </c>
     </row>
@@ -12876,13 +13318,39 @@
           <t>https://www.wchc.nhs.uk/about/board-governors/board-meetings-papers/</t>
         </is>
       </c>
-      <c r="I197" t="inlineStr"/>
-      <c r="J197" t="inlineStr"/>
-      <c r="K197" t="inlineStr"/>
-      <c r="L197" t="inlineStr"/>
-      <c r="M197" t="inlineStr"/>
-      <c r="N197" t="inlineStr"/>
-      <c r="O197" t="inlineStr"/>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Static-fetchable landing presenting dated board meetings as individual hyperlinks that each lead to a per-meeting sub-page (publication page) holding that meeting's PDFs, rather than direct PDFs on the landing. Meeting titles follow 'Public Board of Directors Meeting - {Weekday DD Month Year}' (the June 2026 group meeting is titled 'Group Board of Directors in Public'). Crawl the landing, follow each dated meeting link to its /about/publications/{slug}/ sub-page, then harvest the board-pack PDFs there. Pattern C. The landing is paginated (~15 pages) with month/year filter dropdowns, so for 2025/2026 take the first page(s) or filter by year. Exclude private/confidential items found on the sub-pages.</t>
+        </is>
+      </c>
+      <c r="J197" t="b">
+        <v>0</v>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Public Board of Directors Meeting - {Weekday DD Month Year};Group Board of Directors in Public - {date};/about/publications/{slug}/</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>confidential;private session;minutes-only;pagination beyond target year</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>Confirmed dated meeting links e.g. 'Public Board of Directors Meeting - Wednesday 28 January 2026' and 'Wednesday 1 October 2025', each resolving to its own publications sub-page of PDFs.</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -13421,40 +13889,40 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>https://www.scas.nhs.uk/document-category/board-papers/</t>
+          <t>https://www.scas.nhs.uk/about-scas/our-board/board-meetings/</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>Correct WordPress taxonomy archive ('Board Papers', category 'Board Papers 2025-26') but it is JS/dynamically rendered, a plain HTTP fetch returns only site nav chrome (hence the 'no papers' flag), so it NEEDS render to enumerate entries. Each entry is a /document/&lt;slug&gt;/ page (e.g. /document/scas-public-board-papers-25-sept-2025/) that links to a single combined pack PDF under /wp-content/uploads/YYYY/MM/. SCAS publishes the pack only shortly before each in-public meeting (~Feb/Apr/Jun/Sep/Nov), so the newest confirmed pack at scan time is 25 Sept 2025; the 4 Jun 2026 pack appears on the same archive around the meeting date. Prefer the single 'SCAS public Board papers - &lt;date&gt;' PDF; older copies by email to company.secretary@scas.nhs.uk. Filter policy/strategy PDFs in the same uploads folder.</t>
+          <t>Pattern C. Landing /about-scas/our-board/board-meetings/ lists bi-monthly public board meetings by date; each links to a per-meeting page (e.g. /board-meeting-in-public-4-june/) holding the agenda plus the combined 'SCAS Public Board papers' PDF under /wp-content/uploads/YYYY/MM/ (e.g. SCASpublic-Board-papers_02042026a.pdf). The old DB URL /document-category/board-papers/ is a JS-rendered taxonomy returning an empty body to static fetch. Papers post shortly before each meeting; minutes appear in the next meeting's pack. Contact company.secretary@scas.nhs.uk for archive. URL fixed 2026-06-13.</t>
         </is>
       </c>
       <c r="J205" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>www.scas.nhs.uk/document/scas-public-board-papers-&lt;date&gt;/;www.scas.nhs.uk/wp-content/uploads/&lt;yyyy&gt;/&lt;mm&gt;/SCAS-Public-Board-Papers_&lt;date&gt;.pdf</t>
+          <t>SCASpublic-Board-papers_DDMMYYYY.pdf;Public Board papers;Board meeting in public {date}</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>/wp-content/uploads/.*Policy;registers-of-interest;constitution;strategy;scas-board-members</t>
+          <t>agenda-only PDF;minutes only;Annual Members Meeting</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>needs_playwright</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>The archive lists dated board-pack PDFs but only after JS render; a confirmed 2025 pack PDF was retrieved via its /document/ page.</t>
+          <t>Board-meetings landing lists 2026 meetings (2 Apr, 4 Jun, 3 Sep); per-meeting pages host packs e.g. SCASpublic-Board-papers_02042026a.pdf.</t>
         </is>
       </c>
     </row>
